--- a/data/catalog/datacenter.xlsx
+++ b/data/catalog/datacenter.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="750">
   <si>
     <t>family</t>
   </si>
@@ -1391,10 +1391,7 @@
     <t>N9K-C9348GC-FX3</t>
   </si>
   <si>
-    <t>0.01, 0.1, 1</t>
-  </si>
-  <si>
-    <t>1, 10, 25, 40, 100</t>
+    <t>0.01, 0.1, 1, 10, 25</t>
   </si>
   <si>
     <t>DC-data.csv row 37</t>
@@ -1406,7 +1403,7 @@
     <t>N9K-C9348GC-FX3PH</t>
   </si>
   <si>
-    <t>0.1, 1</t>
+    <t>0.1, 1, 10, 25</t>
   </si>
   <si>
     <t>DC-data.csv row 38</t>
@@ -6754,7 +6751,7 @@
         <v>458</v>
       </c>
       <c r="AH37" t="s">
-        <v>459</v>
+        <v>374</v>
       </c>
       <c r="AJ37">
         <v>696</v>
@@ -6766,10 +6763,10 @@
         <v>351</v>
       </c>
       <c r="AM37" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="AN37" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="AN37" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1" t="s">
@@ -6781,7 +6778,7 @@
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B38" t="s">
         <v>97</v>
@@ -6796,10 +6793,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -6834,10 +6831,10 @@
         <v>1</v>
       </c>
       <c r="AG38" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AH38" t="s">
-        <v>459</v>
+        <v>374</v>
       </c>
       <c r="AJ38">
         <v>696</v>
@@ -6849,14 +6846,14 @@
         <v>351</v>
       </c>
       <c r="AM38" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="AN38" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="AN38" s="1" t="s">
-        <v>465</v>
       </c>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AQ38" s="1" t="s">
         <v>3</v>
@@ -6864,13 +6861,13 @@
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B39" t="s">
         <v>97</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D39" t="s">
         <v>27</v>
@@ -6879,10 +6876,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -6900,7 +6897,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
@@ -6932,10 +6929,10 @@
         <v>351</v>
       </c>
       <c r="AM39" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="AN39" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="AN39" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1" t="s">
@@ -6947,13 +6944,13 @@
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D40" t="s">
         <v>27</v>
@@ -6962,10 +6959,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -6983,7 +6980,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
@@ -7015,10 +7012,10 @@
         <v>351</v>
       </c>
       <c r="AM40" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="AN40" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="AN40" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1" t="s">
@@ -7030,13 +7027,13 @@
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B41" t="s">
         <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D41" t="s">
         <v>27</v>
@@ -7045,10 +7042,10 @@
         <v>28</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -7066,7 +7063,7 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
@@ -7083,7 +7080,7 @@
         <v>2</v>
       </c>
       <c r="AG41" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AH41" t="s">
         <v>374</v>
@@ -7098,10 +7095,10 @@
         <v>351</v>
       </c>
       <c r="AM41" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="AN41" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="AN41" s="1" t="s">
-        <v>478</v>
       </c>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1" t="s">
@@ -7113,13 +7110,13 @@
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B42" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D42" t="s">
         <v>27</v>
@@ -7128,10 +7125,10 @@
         <v>28</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -7149,7 +7146,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
@@ -7166,7 +7163,7 @@
         <v>1.2</v>
       </c>
       <c r="AG42" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AH42" t="s">
         <v>374</v>
@@ -7181,10 +7178,10 @@
         <v>351</v>
       </c>
       <c r="AM42" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="AN42" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="AN42" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1" t="s">
@@ -7196,13 +7193,13 @@
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B43" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D43" t="s">
         <v>27</v>
@@ -7211,10 +7208,10 @@
         <v>28</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -7232,7 +7229,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -7264,10 +7261,10 @@
         <v>289</v>
       </c>
       <c r="AM43" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="AN43" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="AN43" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1" t="s">
@@ -7279,13 +7276,13 @@
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B44" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
@@ -7294,10 +7291,10 @@
         <v>28</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -7315,7 +7312,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -7332,10 +7329,10 @@
         <v>1</v>
       </c>
       <c r="AG44" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AH44" t="s">
-        <v>459</v>
+        <v>374</v>
       </c>
       <c r="AJ44">
         <v>696</v>
@@ -7344,17 +7341,17 @@
         <v>46</v>
       </c>
       <c r="AL44" t="s">
+        <v>487</v>
+      </c>
+      <c r="AM44" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="AM44" s="1" t="s">
+      <c r="AN44" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="AN44" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AQ44" s="1" t="s">
         <v>3</v>
@@ -7362,13 +7359,13 @@
     </row>
     <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B45" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
@@ -7377,10 +7374,10 @@
         <v>28</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -7391,17 +7388,17 @@
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="O45" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>373</v>
       </c>
       <c r="Q45" s="1"/>
       <c r="S45" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="T45" t="s">
         <v>108</v>
@@ -7409,7 +7406,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
@@ -7441,10 +7438,10 @@
         <v>314</v>
       </c>
       <c r="AM45" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="AN45" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="AN45" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1" t="s">
@@ -7454,13 +7451,13 @@
     </row>
     <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B46" t="s">
         <v>97</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D46" t="s">
         <v>27</v>
@@ -7469,10 +7466,10 @@
         <v>28</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -7490,7 +7487,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -7522,14 +7519,14 @@
         <v>149</v>
       </c>
       <c r="AM46" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="AN46" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="AN46" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AQ46" s="1" t="s">
         <v>3</v>
@@ -7537,13 +7534,13 @@
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B47" t="s">
         <v>97</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D47" t="s">
         <v>27</v>
@@ -7552,10 +7549,10 @@
         <v>28</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -7570,7 +7567,7 @@
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="S47" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="T47" t="s">
         <v>108</v>
@@ -7578,7 +7575,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -7595,10 +7592,10 @@
         <v>1</v>
       </c>
       <c r="AG47" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AH47" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AJ47">
         <v>960</v>
@@ -7607,10 +7604,10 @@
         <v>46</v>
       </c>
       <c r="AM47" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="AN47" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="AN47" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
@@ -7618,13 +7615,13 @@
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B48" t="s">
         <v>97</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D48" t="s">
         <v>27</v>
@@ -7633,10 +7630,10 @@
         <v>28</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -7651,7 +7648,7 @@
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="S48" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="T48" t="s">
         <v>108</v>
@@ -7659,7 +7656,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
@@ -7676,10 +7673,10 @@
         <v>1</v>
       </c>
       <c r="AG48" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AH48" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AJ48">
         <v>480</v>
@@ -7688,10 +7685,10 @@
         <v>46</v>
       </c>
       <c r="AM48" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="AN48" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="AN48" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
@@ -7699,13 +7696,13 @@
     </row>
     <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B49" t="s">
         <v>97</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D49" t="s">
         <v>27</v>
@@ -7714,10 +7711,10 @@
         <v>28</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -7735,7 +7732,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
@@ -7752,10 +7749,10 @@
         <v>9</v>
       </c>
       <c r="AG49" t="s">
+        <v>518</v>
+      </c>
+      <c r="AH49" t="s">
         <v>519</v>
-      </c>
-      <c r="AH49" t="s">
-        <v>520</v>
       </c>
       <c r="AI49">
         <v>4</v>
@@ -7767,17 +7764,17 @@
         <v>92</v>
       </c>
       <c r="AL49" t="s">
+        <v>520</v>
+      </c>
+      <c r="AM49" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="AM49" s="1" t="s">
+      <c r="AN49" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="AN49" s="1" t="s">
-        <v>523</v>
       </c>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AQ49" s="1" t="s">
         <v>3</v>
@@ -7785,13 +7782,13 @@
     </row>
     <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B50" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
@@ -7800,10 +7797,10 @@
         <v>28</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -7821,7 +7818,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
@@ -7838,10 +7835,10 @@
         <v>14</v>
       </c>
       <c r="AG50" t="s">
+        <v>518</v>
+      </c>
+      <c r="AH50" t="s">
         <v>519</v>
-      </c>
-      <c r="AH50" t="s">
-        <v>520</v>
       </c>
       <c r="AI50">
         <v>8</v>
@@ -7853,17 +7850,17 @@
         <v>92</v>
       </c>
       <c r="AL50" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AM50" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="AN50" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="AN50" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AQ50" s="1" t="s">
         <v>3</v>
@@ -7871,13 +7868,13 @@
     </row>
     <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B51" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
@@ -7886,10 +7883,10 @@
         <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -7907,7 +7904,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -7924,10 +7921,10 @@
         <v>26</v>
       </c>
       <c r="AG51" t="s">
+        <v>518</v>
+      </c>
+      <c r="AH51" t="s">
         <v>519</v>
-      </c>
-      <c r="AH51" t="s">
-        <v>520</v>
       </c>
       <c r="AI51">
         <v>16</v>
@@ -7939,17 +7936,17 @@
         <v>92</v>
       </c>
       <c r="AL51" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AM51" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="AN51" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="AN51" s="1" t="s">
-        <v>534</v>
       </c>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AQ51" s="1" t="s">
         <v>3</v>
@@ -7957,13 +7954,13 @@
     </row>
     <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B52" t="s">
         <v>97</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D52" t="s">
         <v>27</v>
@@ -7972,10 +7969,10 @@
         <v>28</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -7993,7 +7990,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
       <c r="W52" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
@@ -8010,26 +8007,26 @@
         <v>2</v>
       </c>
       <c r="AG52" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AH52" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AK52" t="s">
         <v>92</v>
       </c>
       <c r="AL52" t="s">
+        <v>539</v>
+      </c>
+      <c r="AM52" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="AM52" s="1" t="s">
+      <c r="AN52" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="AN52" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AQ52" s="1" t="s">
         <v>3</v>
@@ -8037,13 +8034,13 @@
     </row>
     <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B53" t="s">
         <v>97</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D53" t="s">
         <v>27</v>
@@ -8052,10 +8049,10 @@
         <v>28</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -8073,7 +8070,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
@@ -8090,26 +8087,26 @@
         <v>2</v>
       </c>
       <c r="AG53" t="s">
+        <v>546</v>
+      </c>
+      <c r="AH53" t="s">
         <v>547</v>
-      </c>
-      <c r="AH53" t="s">
-        <v>548</v>
       </c>
       <c r="AK53" t="s">
         <v>92</v>
       </c>
       <c r="AL53" t="s">
+        <v>548</v>
+      </c>
+      <c r="AM53" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="AM53" s="1" t="s">
+      <c r="AN53" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="AN53" s="1" t="s">
-        <v>551</v>
       </c>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AQ53" s="1" t="s">
         <v>3</v>
@@ -8117,13 +8114,13 @@
     </row>
     <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B54" t="s">
         <v>97</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D54" t="s">
         <v>27</v>
@@ -8132,10 +8129,10 @@
         <v>28</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -8153,7 +8150,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
@@ -8170,26 +8167,26 @@
         <v>1</v>
       </c>
       <c r="AG54" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AH54" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AK54" t="s">
         <v>92</v>
       </c>
       <c r="AL54" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AM54" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="AN54" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="AN54" s="1" t="s">
-        <v>558</v>
       </c>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AQ54" s="1" t="s">
         <v>3</v>
@@ -8197,13 +8194,13 @@
     </row>
     <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B55" t="s">
         <v>97</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -8212,10 +8209,10 @@
         <v>28</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -8233,7 +8230,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
@@ -8250,26 +8247,26 @@
         <v>1</v>
       </c>
       <c r="AG55" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AH55" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AK55" t="s">
         <v>92</v>
       </c>
       <c r="AL55" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AM55" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="AN55" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="AN55" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AQ55" s="1" t="s">
         <v>3</v>
@@ -8277,13 +8274,13 @@
     </row>
     <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B56" t="s">
         <v>97</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -8292,10 +8289,10 @@
         <v>28</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -8313,7 +8310,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
@@ -8330,26 +8327,26 @@
         <v>1</v>
       </c>
       <c r="AG56" t="s">
+        <v>546</v>
+      </c>
+      <c r="AH56" t="s">
         <v>547</v>
-      </c>
-      <c r="AH56" t="s">
-        <v>548</v>
       </c>
       <c r="AK56" t="s">
         <v>92</v>
       </c>
       <c r="AL56" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AM56" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="AN56" s="1" t="s">
         <v>567</v>
-      </c>
-      <c r="AN56" s="1" t="s">
-        <v>568</v>
       </c>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AQ56" s="1" t="s">
         <v>3</v>
@@ -8357,13 +8354,13 @@
     </row>
     <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B57" t="s">
         <v>97</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -8372,10 +8369,10 @@
         <v>28</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -8393,7 +8390,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
@@ -8410,26 +8407,26 @@
         <v>1</v>
       </c>
       <c r="AG57" t="s">
+        <v>546</v>
+      </c>
+      <c r="AH57" t="s">
         <v>547</v>
-      </c>
-      <c r="AH57" t="s">
-        <v>548</v>
       </c>
       <c r="AK57" t="s">
         <v>92</v>
       </c>
       <c r="AL57" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AM57" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="AN57" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="AN57" s="1" t="s">
-        <v>572</v>
       </c>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AQ57" s="1" t="s">
         <v>3</v>
@@ -8437,13 +8434,13 @@
     </row>
     <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B58" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D58" t="s">
         <v>27</v>
@@ -8452,10 +8449,10 @@
         <v>28</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -8473,7 +8470,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
@@ -8487,26 +8484,26 @@
         <v>1</v>
       </c>
       <c r="AG58" t="s">
+        <v>576</v>
+      </c>
+      <c r="AH58" t="s">
         <v>577</v>
-      </c>
-      <c r="AH58" t="s">
-        <v>578</v>
       </c>
       <c r="AK58" t="s">
         <v>92</v>
       </c>
       <c r="AL58" t="s">
+        <v>578</v>
+      </c>
+      <c r="AM58" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="AM58" s="1" t="s">
+      <c r="AN58" s="1" t="s">
         <v>580</v>
-      </c>
-      <c r="AN58" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AQ58" s="1" t="s">
         <v>3</v>
@@ -8514,13 +8511,13 @@
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B59" t="s">
         <v>97</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
@@ -8529,10 +8526,10 @@
         <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -8550,7 +8547,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
@@ -8582,16 +8579,16 @@
         <v>50</v>
       </c>
       <c r="AM59" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="AN59" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="AN59" s="1" t="s">
+      <c r="AO59" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="AO59" s="1" t="s">
+      <c r="AP59" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="AP59" s="1" t="s">
-        <v>589</v>
       </c>
       <c r="AQ59" s="1" t="s">
         <v>3</v>
@@ -8599,13 +8596,13 @@
     </row>
     <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B60" t="s">
         <v>97</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -8614,10 +8611,10 @@
         <v>28</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -8635,7 +8632,7 @@
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
@@ -8652,7 +8649,7 @@
         <v>1</v>
       </c>
       <c r="AG60" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AH60" t="s">
         <v>276</v>
@@ -8667,16 +8664,16 @@
         <v>50</v>
       </c>
       <c r="AM60" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="AN60" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="AN60" s="1" t="s">
+      <c r="AO60" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="AO60" s="1" t="s">
+      <c r="AP60" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="AP60" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="AQ60" s="1" t="s">
         <v>3</v>
@@ -8684,13 +8681,13 @@
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B61" t="s">
         <v>97</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
@@ -8699,10 +8696,10 @@
         <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -8720,7 +8717,7 @@
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
@@ -8749,16 +8746,16 @@
         <v>103</v>
       </c>
       <c r="AM61" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="AN61" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="AN61" s="1" t="s">
+      <c r="AO61" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="AO61" s="1" t="s">
+      <c r="AP61" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="AP61" s="1" t="s">
-        <v>600</v>
       </c>
       <c r="AQ61" s="1" t="s">
         <v>3</v>
@@ -8823,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -8838,10 +8835,10 @@
         <v>238</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>602</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>603</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>6</v>
@@ -8900,7 +8897,7 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
@@ -8915,10 +8912,10 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H2">
         <v>36</v>
@@ -8937,20 +8934,20 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>605</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>606</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
@@ -8965,10 +8962,10 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H3">
         <v>36</v>
@@ -8987,20 +8984,20 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>610</v>
       </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
@@ -9015,10 +9012,10 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H4">
         <v>14</v>
@@ -9037,20 +9034,20 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>612</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>613</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B5" t="s">
         <v>97</v>
@@ -9065,10 +9062,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -9081,20 +9078,20 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>615</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>616</v>
       </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
@@ -9109,10 +9106,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -9125,20 +9122,20 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="X6" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>619</v>
       </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
@@ -9153,10 +9150,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -9169,20 +9166,20 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="X7" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>622</v>
       </c>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B8" t="s">
         <v>97</v>
@@ -9197,10 +9194,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -9213,20 +9210,20 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="X8" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>625</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B9" t="s">
         <v>97</v>
@@ -9241,10 +9238,10 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H9">
         <v>16</v>
@@ -9263,20 +9260,20 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="X9" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>628</v>
       </c>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B10" t="s">
         <v>97</v>
@@ -9291,10 +9288,10 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H10">
         <v>36</v>
@@ -9313,20 +9310,20 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="X10" s="1" t="s">
         <v>630</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>631</v>
       </c>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B11" t="s">
         <v>97</v>
@@ -9341,10 +9338,10 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H11">
         <v>36</v>
@@ -9357,27 +9354,27 @@
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="O11" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="P11" s="1"/>
       <c r="R11" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
@@ -9387,7 +9384,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B12" t="s">
         <v>97</v>
@@ -9402,10 +9399,10 @@
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H12">
         <v>32</v>
@@ -9418,30 +9415,30 @@
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="O12" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="P12" s="1"/>
       <c r="R12" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="X12" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="X12" s="1" t="s">
+      <c r="Y12" s="1" t="s">
         <v>642</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>643</v>
       </c>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1" t="s">
@@ -9450,7 +9447,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B13" t="s">
         <v>97</v>
@@ -9465,16 +9462,16 @@
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H13">
         <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -9487,20 +9484,20 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="X13" s="1" t="s">
         <v>646</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>647</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
@@ -9515,16 +9512,16 @@
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H14">
         <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -9537,20 +9534,20 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="X14" s="1" t="s">
         <v>649</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>650</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
@@ -9565,10 +9562,10 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H15">
         <v>24</v>
@@ -9587,20 +9584,20 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="X15" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>653</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B16" t="s">
         <v>97</v>
@@ -9615,10 +9612,10 @@
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H16">
         <v>36</v>
@@ -9637,20 +9634,20 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="X16" s="1" t="s">
         <v>655</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>656</v>
       </c>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B17" t="s">
         <v>97</v>
@@ -9665,10 +9662,10 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H17">
         <v>36</v>
@@ -9687,20 +9684,20 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="X17" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="X17" s="1" t="s">
-        <v>659</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B18" t="s">
         <v>97</v>
@@ -9715,16 +9712,16 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H18">
         <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -9737,20 +9734,20 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="X18" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>663</v>
       </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B19" t="s">
         <v>97</v>
@@ -9765,10 +9762,10 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H19">
         <v>32</v>
@@ -9787,20 +9784,20 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="X19" s="1" t="s">
         <v>665</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>666</v>
       </c>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B20" t="s">
         <v>97</v>
@@ -9815,10 +9812,10 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -9831,20 +9828,20 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="X20" s="1" t="s">
         <v>668</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>669</v>
       </c>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B21" t="s">
         <v>97</v>
@@ -9859,10 +9856,10 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -9875,20 +9872,20 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="X21" s="1" t="s">
         <v>671</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>672</v>
       </c>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B22" t="s">
         <v>97</v>
@@ -9903,10 +9900,10 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -9919,20 +9916,20 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="X22" s="1" t="s">
         <v>674</v>
-      </c>
-      <c r="X22" s="1" t="s">
-        <v>675</v>
       </c>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
@@ -9947,10 +9944,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -9963,20 +9960,20 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="X23" s="1" t="s">
         <v>677</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>678</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
@@ -9991,10 +9988,10 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -10007,20 +10004,20 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="X24" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>681</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B25" t="s">
         <v>97</v>
@@ -10035,10 +10032,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -10051,20 +10048,20 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="X25" s="1" t="s">
         <v>683</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>684</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B26" t="s">
         <v>97</v>
@@ -10079,10 +10076,10 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -10095,20 +10092,20 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="X26" s="1" t="s">
         <v>686</v>
-      </c>
-      <c r="X26" s="1" t="s">
-        <v>687</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
@@ -10123,10 +10120,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -10139,20 +10136,20 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="X27" s="1" t="s">
         <v>689</v>
-      </c>
-      <c r="X27" s="1" t="s">
-        <v>690</v>
       </c>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B28" t="s">
         <v>97</v>
@@ -10167,10 +10164,10 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -10183,20 +10180,20 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="X28" s="1" t="s">
         <v>692</v>
-      </c>
-      <c r="X28" s="1" t="s">
-        <v>693</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B29" t="s">
         <v>97</v>
@@ -10211,10 +10208,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -10227,20 +10224,20 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="X29" s="1" t="s">
         <v>695</v>
-      </c>
-      <c r="X29" s="1" t="s">
-        <v>696</v>
       </c>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B30" t="s">
         <v>97</v>
@@ -10255,10 +10252,10 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H30">
         <v>8</v>
@@ -10277,20 +10274,20 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="X30" s="1" t="s">
         <v>698</v>
-      </c>
-      <c r="X30" s="1" t="s">
-        <v>699</v>
       </c>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B31" t="s">
         <v>97</v>
@@ -10305,16 +10302,16 @@
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H31">
         <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -10327,20 +10324,20 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="X31" s="1" t="s">
         <v>702</v>
-      </c>
-      <c r="X31" s="1" t="s">
-        <v>703</v>
       </c>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B32" t="s">
         <v>97</v>
@@ -10355,16 +10352,16 @@
         <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H32">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -10377,20 +10374,20 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="X32" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="X32" s="1" t="s">
-        <v>707</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
@@ -10405,16 +10402,16 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H33">
         <v>24</v>
       </c>
       <c r="I33" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -10427,20 +10424,20 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="X33" s="1" t="s">
         <v>710</v>
-      </c>
-      <c r="X33" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B34" t="s">
         <v>97</v>
@@ -10455,16 +10452,16 @@
         <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H34">
         <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -10477,20 +10474,20 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="X34" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="X34" s="1" t="s">
-        <v>714</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B35" t="s">
         <v>97</v>
@@ -10505,16 +10502,16 @@
         <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H35">
         <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -10527,20 +10524,20 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="X35" s="1" t="s">
         <v>716</v>
-      </c>
-      <c r="X35" s="1" t="s">
-        <v>717</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
@@ -10555,16 +10552,16 @@
         <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H36">
         <v>48</v>
       </c>
       <c r="I36" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -10577,20 +10574,20 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="X36" s="1" t="s">
         <v>719</v>
-      </c>
-      <c r="X36" s="1" t="s">
-        <v>720</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B37" t="s">
         <v>97</v>
@@ -10605,16 +10602,16 @@
         <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H37">
         <v>48</v>
       </c>
       <c r="I37" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -10627,20 +10624,20 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="X37" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="X37" s="1" t="s">
-        <v>723</v>
       </c>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B38" t="s">
         <v>97</v>
@@ -10655,10 +10652,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -10671,20 +10668,20 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="X38" s="1" t="s">
         <v>725</v>
-      </c>
-      <c r="X38" s="1" t="s">
-        <v>726</v>
       </c>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B39" t="s">
         <v>97</v>
@@ -10699,10 +10696,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -10715,20 +10712,20 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="X39" s="1" t="s">
         <v>728</v>
-      </c>
-      <c r="X39" s="1" t="s">
-        <v>729</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
@@ -10743,10 +10740,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -10759,15 +10756,15 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="X40" s="1" t="s">
         <v>731</v>
-      </c>
-      <c r="X40" s="1" t="s">
-        <v>732</v>
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -10808,827 +10805,827 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>734</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>271</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>281</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>271</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>281</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>271</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>281</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>271</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>281</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>271</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>281</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>271</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>281</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>271</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>281</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>293</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
   </sheetData>
@@ -11663,10 +11660,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>749</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11674,7 +11671,7 @@
         <v>97</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -11690,7 +11687,7 @@
         <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -11706,7 +11703,7 @@
         <v>97</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -11722,7 +11719,7 @@
         <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
@@ -11738,7 +11735,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -11786,7 +11783,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -11834,7 +11831,7 @@
         <v>97</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -11866,7 +11863,7 @@
         <v>97</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
@@ -11994,7 +11991,7 @@
         <v>97</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>

--- a/data/catalog/datacenter.xlsx
+++ b/data/catalog/datacenter.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="756">
   <si>
     <t>family</t>
   </si>
@@ -359,90 +359,96 @@
     <t>dc</t>
   </si>
   <si>
+    <t>tor</t>
+  </si>
+  <si>
+    <t>hypershield</t>
+  </si>
+  <si>
+    <t>advanced_malware_protection</t>
+  </si>
+  <si>
+    <t>evpn</t>
+  </si>
+  <si>
+    <t>san</t>
+  </si>
+  <si>
+    <t>pim</t>
+  </si>
+  <si>
+    <t>internal_optional_kit</t>
+  </si>
+  <si>
+    <t>redundant_psu</t>
+  </si>
+  <si>
+    <t>rf_asic</t>
+  </si>
+  <si>
+    <t>app_hosting</t>
+  </si>
+  <si>
+    <t>fcoe</t>
+  </si>
+  <si>
+    <t>nim</t>
+  </si>
+  <si>
     <t>services</t>
   </si>
   <si>
-    <t>hypershield</t>
-  </si>
-  <si>
-    <t>advanced_malware_protection</t>
-  </si>
-  <si>
-    <t>evpn</t>
-  </si>
-  <si>
-    <t>san</t>
-  </si>
-  <si>
-    <t>pim</t>
-  </si>
-  <si>
-    <t>internal_optional_kit</t>
+    <t>security_radio</t>
+  </si>
+  <si>
+    <t>battery_backup</t>
+  </si>
+  <si>
+    <t>fibre_channel</t>
+  </si>
+  <si>
+    <t>sm</t>
+  </si>
+  <si>
+    <t>multiservice</t>
+  </si>
+  <si>
+    <t>smart_managed</t>
+  </si>
+  <si>
+    <t>urwb</t>
+  </si>
+  <si>
+    <t>bits_1pps_10mhz_tod_gps</t>
+  </si>
+  <si>
+    <t>ficon</t>
+  </si>
+  <si>
+    <t>im</t>
   </si>
   <si>
     <t>san_fabric</t>
   </si>
   <si>
-    <t>redundant_psu</t>
-  </si>
-  <si>
-    <t>rf_asic</t>
-  </si>
-  <si>
-    <t>app_hosting</t>
-  </si>
-  <si>
-    <t>fcoe</t>
-  </si>
-  <si>
-    <t>nim</t>
+    <t>smb</t>
+  </si>
+  <si>
+    <t>uwb</t>
+  </si>
+  <si>
+    <t>bits_gps</t>
+  </si>
+  <si>
+    <t>ivr</t>
+  </si>
+  <si>
+    <t>other</t>
   </si>
   <si>
     <t>san_director</t>
   </si>
   <si>
-    <t>security_radio</t>
-  </si>
-  <si>
-    <t>battery_backup</t>
-  </si>
-  <si>
-    <t>fibre_channel</t>
-  </si>
-  <si>
-    <t>sm</t>
-  </si>
-  <si>
-    <t>smart_managed</t>
-  </si>
-  <si>
-    <t>urwb</t>
-  </si>
-  <si>
-    <t>bits_1pps_10mhz_tod_gps</t>
-  </si>
-  <si>
-    <t>ficon</t>
-  </si>
-  <si>
-    <t>im</t>
-  </si>
-  <si>
-    <t>smb</t>
-  </si>
-  <si>
-    <t>uwb</t>
-  </si>
-  <si>
-    <t>bits_gps</t>
-  </si>
-  <si>
-    <t>ivr</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
     <t>stacking</t>
   </si>
   <si>
@@ -452,6 +458,9 @@
     <t>line_rate_macsec_all_ports</t>
   </si>
   <si>
+    <t>san_extension</t>
+  </si>
+  <si>
     <t>stackpower</t>
   </si>
   <si>
@@ -1268,6 +1277,9 @@
     <t>N9348Y12C-SE1</t>
   </si>
   <si>
+    <t>leaf, tor</t>
+  </si>
+  <si>
     <t>DC-data.csv row 29</t>
   </si>
   <si>
@@ -1523,6 +1535,9 @@
     <t>https://www.cisco.com/c/en/us/products/collateral/switches/nexus-3000-series-switches/datasheet-c78-739189.html#Productoverview</t>
   </si>
   <si>
+    <t>access, aggregation</t>
+  </si>
+  <si>
     <t>DC-data.csv row 46</t>
   </si>
   <si>
@@ -1743,6 +1758,9 @@
   </si>
   <si>
     <t>https://www.cisco.com/c/en/us/products/collateral/storage-networking/mds-9200-series-multiservice-switches/datasheet-c78-744805.html</t>
+  </si>
+  <si>
+    <t>multiservice, san_extension</t>
   </si>
   <si>
     <t>1, 8, 10, 16, 25, 32, 40</t>
@@ -3062,19 +3080,19 @@
         <v>112</v>
       </c>
       <c r="U7" t="s">
+        <v>102</v>
+      </c>
+      <c r="W7" t="s">
         <v>121</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>122</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>123</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>124</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="8" spans="5:26" x14ac:dyDescent="0.25">
@@ -3082,26 +3100,29 @@
         <v>103</v>
       </c>
       <c r="F8" t="s">
+        <v>125</v>
+      </c>
+      <c r="U8" t="s">
         <v>126</v>
-      </c>
-      <c r="U8" t="s">
-        <v>127</v>
       </c>
       <c r="W8" t="s">
         <v>85</v>
       </c>
       <c r="X8" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y8" t="s">
         <v>128</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="Z8" t="s">
         <v>129</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="9" spans="6:26" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
+        <v>130</v>
+      </c>
+      <c r="U9" t="s">
         <v>131</v>
       </c>
       <c r="W9" t="s">
@@ -3121,42 +3142,51 @@
       <c r="F10" t="s">
         <v>136</v>
       </c>
+      <c r="U10" t="s">
+        <v>137</v>
+      </c>
       <c r="W10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="X10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Y10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Z10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="6:26" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="U11" t="s">
+        <v>143</v>
       </c>
       <c r="W11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Y11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Z11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="12" spans="23:26" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="21:26" x14ac:dyDescent="0.25">
+      <c r="U12" t="s">
+        <v>147</v>
+      </c>
       <c r="W12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Y12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Z12" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="23:26" x14ac:dyDescent="0.25">
@@ -3164,74 +3194,74 @@
         <v>101</v>
       </c>
       <c r="Y13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Z13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y14" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Z14" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Z15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y16" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="Z16" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y17" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Z17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y18" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Z18" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Z19" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y20" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Z20" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y21" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Z21" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="25:26" x14ac:dyDescent="0.25">
@@ -3239,224 +3269,224 @@
         <v>117</v>
       </c>
       <c r="Z22" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y23" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Z23" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y24" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Z24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y25" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Z25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y26" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Z26" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y27" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y28" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y29" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y30" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y31" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y32" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y33" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y34" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y35" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y36" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y37" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y38" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y39" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y40" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y41" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y42" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y43" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y44" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y45" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y46" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y47" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y48" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y49" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y50" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="51" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y51" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="52" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y52" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="53" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y53" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y54" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="55" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y55" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y56" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="57" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y57" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="58" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y58" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="59" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y59" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="60" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y60" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y61" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y62" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="63" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y63" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="25:25" x14ac:dyDescent="0.25">
@@ -3466,122 +3496,122 @@
     </row>
     <row r="65" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y66" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y67" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y68" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="69" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y69" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y70" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y71" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y72" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="73" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y73" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y74" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y75" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y76" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y77" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y78" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="79" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y79" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="80" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y80" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="81" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y81" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y82" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="83" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y83" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y84" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y85" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="86" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y86" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y87" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="88" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y88" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" spans="25:25" x14ac:dyDescent="0.25">
@@ -3591,12 +3621,12 @@
     </row>
     <row r="90" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y90" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="91" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y91" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3638,13 +3668,13 @@
   <sheetData>
     <row r="1" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -3653,22 +3683,22 @@
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>3</v>
@@ -3677,105 +3707,105 @@
         <v>54</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AJ1" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AK1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="AL1" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -3784,10 +3814,10 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3805,7 +3835,7 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
@@ -3816,16 +3846,16 @@
         <v>69</v>
       </c>
       <c r="AE2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AF2">
         <v>16</v>
       </c>
       <c r="AG2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AH2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AI2">
         <v>8</v>
@@ -3837,17 +3867,17 @@
         <v>46</v>
       </c>
       <c r="AL2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AO2" s="1"/>
       <c r="AP2" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AQ2" s="1" t="s">
         <v>3</v>
@@ -3855,13 +3885,13 @@
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
@@ -3870,10 +3900,10 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -3891,7 +3921,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -3902,16 +3932,16 @@
         <v>69</v>
       </c>
       <c r="AE3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AF3">
         <v>10</v>
       </c>
       <c r="AG3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AH3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AI3">
         <v>4</v>
@@ -3923,17 +3953,17 @@
         <v>46</v>
       </c>
       <c r="AL3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AO3" s="1"/>
       <c r="AP3" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AQ3" s="1" t="s">
         <v>3</v>
@@ -3941,13 +3971,13 @@
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
@@ -3956,10 +3986,10 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -3977,7 +4007,7 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
@@ -3994,29 +4024,29 @@
         <v>7</v>
       </c>
       <c r="AG4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AH4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AI4">
         <v>4</v>
       </c>
       <c r="AK4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AM4" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AN4" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AO4" s="1"/>
       <c r="AP4" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AQ4" s="1" t="s">
         <v>3</v>
@@ -4024,13 +4054,13 @@
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B5" t="s">
         <v>97</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D5" t="s">
         <v>27</v>
@@ -4039,10 +4069,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -4060,7 +4090,7 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -4077,29 +4107,29 @@
         <v>13</v>
       </c>
       <c r="AG5" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AH5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AI5">
         <v>8</v>
       </c>
       <c r="AK5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AM5" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AN5" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AQ5" s="1" t="s">
         <v>3</v>
@@ -4107,13 +4137,13 @@
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
@@ -4122,10 +4152,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -4143,7 +4173,7 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
@@ -4160,10 +4190,10 @@
         <v>21</v>
       </c>
       <c r="AG6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AH6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AI6">
         <v>16</v>
@@ -4172,20 +4202,20 @@
         <v>172800</v>
       </c>
       <c r="AK6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AN6" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AQ6" s="1" t="s">
         <v>3</v>
@@ -4193,13 +4223,13 @@
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -4208,10 +4238,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -4229,7 +4259,7 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
@@ -4240,16 +4270,16 @@
         <v>69</v>
       </c>
       <c r="AE7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AF7">
         <v>4</v>
       </c>
       <c r="AG7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AH7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AI7">
         <v>8</v>
@@ -4258,20 +4288,20 @@
         <v>25600</v>
       </c>
       <c r="AK7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AO7" s="1"/>
       <c r="AP7" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AQ7" s="1" t="s">
         <v>3</v>
@@ -4279,13 +4309,13 @@
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B8" t="s">
         <v>97</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
@@ -4294,10 +4324,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -4315,7 +4345,7 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
@@ -4326,16 +4356,16 @@
         <v>44</v>
       </c>
       <c r="AE8" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF8">
         <v>2</v>
       </c>
       <c r="AG8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AH8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AJ8">
         <v>51200</v>
@@ -4344,17 +4374,17 @@
         <v>46</v>
       </c>
       <c r="AL8" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN8" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AQ8" s="1" t="s">
         <v>3</v>
@@ -4362,13 +4392,13 @@
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B9" t="s">
         <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -4377,10 +4407,10 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -4398,7 +4428,7 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
@@ -4409,16 +4439,16 @@
         <v>44</v>
       </c>
       <c r="AE9" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF9">
         <v>2</v>
       </c>
       <c r="AG9" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AH9" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AJ9">
         <v>51200</v>
@@ -4427,17 +4457,17 @@
         <v>46</v>
       </c>
       <c r="AL9" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AM9" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AN9" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AQ9" s="1" t="s">
         <v>3</v>
@@ -4445,13 +4475,13 @@
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B10" t="s">
         <v>97</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
@@ -4460,10 +4490,10 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -4481,7 +4511,7 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
@@ -4492,16 +4522,16 @@
         <v>44</v>
       </c>
       <c r="AE10" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF10">
         <v>2</v>
       </c>
       <c r="AG10" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AH10" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AJ10">
         <v>51200</v>
@@ -4510,19 +4540,19 @@
         <v>46</v>
       </c>
       <c r="AL10" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AN10" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AO10" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AP10" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AQ10" s="1" t="s">
         <v>3</v>
@@ -4530,13 +4560,13 @@
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
         <v>97</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D11" t="s">
         <v>27</v>
@@ -4545,10 +4575,10 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -4566,7 +4596,7 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
@@ -4577,16 +4607,16 @@
         <v>44</v>
       </c>
       <c r="AE11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF11">
         <v>2</v>
       </c>
       <c r="AG11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AH11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AJ11">
         <v>51200</v>
@@ -4595,19 +4625,19 @@
         <v>46</v>
       </c>
       <c r="AL11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AN11" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="AO11" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="AP11" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="AO11" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="AP11" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="AQ11" s="1" t="s">
         <v>3</v>
@@ -4615,13 +4645,13 @@
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B12" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
@@ -4630,10 +4660,10 @@
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -4651,7 +4681,7 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
@@ -4668,10 +4698,10 @@
         <v>3</v>
       </c>
       <c r="AG12" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AH12" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AJ12">
         <v>102400</v>
@@ -4680,17 +4710,17 @@
         <v>46</v>
       </c>
       <c r="AL12" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AN12" s="1" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AQ12" s="1" t="s">
         <v>3</v>
@@ -4698,13 +4728,13 @@
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B13" t="s">
         <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -4713,10 +4743,10 @@
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -4734,7 +4764,7 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
@@ -4751,10 +4781,10 @@
         <v>3</v>
       </c>
       <c r="AG13" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AH13" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AJ13">
         <v>102400</v>
@@ -4763,17 +4793,17 @@
         <v>46</v>
       </c>
       <c r="AL13" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AN13" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AQ13" s="1" t="s">
         <v>3</v>
@@ -4781,13 +4811,13 @@
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
@@ -4796,10 +4826,10 @@
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -4817,7 +4847,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
@@ -4828,16 +4858,16 @@
         <v>44</v>
       </c>
       <c r="AE14" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF14">
         <v>2</v>
       </c>
       <c r="AG14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AH14" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AJ14">
         <v>51200</v>
@@ -4846,17 +4876,17 @@
         <v>46</v>
       </c>
       <c r="AL14" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN14" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AQ14" s="1" t="s">
         <v>3</v>
@@ -4864,13 +4894,13 @@
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
@@ -4879,10 +4909,10 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -4900,7 +4930,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
@@ -4911,35 +4941,35 @@
         <v>44</v>
       </c>
       <c r="AE15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF15">
         <v>1</v>
       </c>
       <c r="AG15" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AH15" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AJ15">
         <v>25600</v>
       </c>
       <c r="AK15" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL15" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AN15" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ15" s="1" t="s">
         <v>3</v>
@@ -4947,13 +4977,13 @@
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B16" t="s">
         <v>97</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
@@ -4962,10 +4992,10 @@
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -4983,7 +5013,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
@@ -4994,35 +5024,35 @@
         <v>44</v>
       </c>
       <c r="AE16" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF16">
         <v>1</v>
       </c>
       <c r="AG16" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AH16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AJ16">
         <v>25600</v>
       </c>
       <c r="AK16" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL16" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AN16" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ16" s="1" t="s">
         <v>3</v>
@@ -5030,13 +5060,13 @@
     </row>
     <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B17" t="s">
         <v>97</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D17" t="s">
         <v>27</v>
@@ -5045,10 +5075,10 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -5066,7 +5096,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
@@ -5077,35 +5107,35 @@
         <v>44</v>
       </c>
       <c r="AE17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF17">
         <v>2</v>
       </c>
       <c r="AG17" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AH17" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AJ17">
         <v>38400</v>
       </c>
       <c r="AK17" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL17" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AN17" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ17" s="1" t="s">
         <v>3</v>
@@ -5113,13 +5143,13 @@
     </row>
     <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B18" t="s">
         <v>97</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
@@ -5128,10 +5158,10 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -5149,7 +5179,7 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
@@ -5160,35 +5190,35 @@
         <v>44</v>
       </c>
       <c r="AE18" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF18">
         <v>2</v>
       </c>
       <c r="AG18" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AH18" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AJ18">
         <v>51200</v>
       </c>
       <c r="AK18" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL18" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM18" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN18" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ18" s="1" t="s">
         <v>3</v>
@@ -5196,13 +5226,13 @@
     </row>
     <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B19" t="s">
         <v>97</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
@@ -5211,10 +5241,10 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -5232,7 +5262,7 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
@@ -5243,35 +5273,35 @@
         <v>44</v>
       </c>
       <c r="AE19" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF19">
         <v>1</v>
       </c>
       <c r="AG19" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AH19" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AJ19">
         <v>12800</v>
       </c>
       <c r="AK19" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL19" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AN19" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ19" s="1" t="s">
         <v>3</v>
@@ -5279,13 +5309,13 @@
     </row>
     <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B20" t="s">
         <v>97</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
@@ -5294,10 +5324,10 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -5315,7 +5345,7 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
@@ -5326,35 +5356,35 @@
         <v>44</v>
       </c>
       <c r="AE20" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF20">
         <v>1</v>
       </c>
       <c r="AG20" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AH20" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AJ20">
         <v>12000</v>
       </c>
       <c r="AK20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL20" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM20" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AN20" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ20" s="1" t="s">
         <v>3</v>
@@ -5362,13 +5392,13 @@
     </row>
     <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B21" t="s">
         <v>97</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
@@ -5377,10 +5407,10 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -5398,7 +5428,7 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
@@ -5409,35 +5439,35 @@
         <v>44</v>
       </c>
       <c r="AE21" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF21">
         <v>2</v>
       </c>
       <c r="AG21" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AH21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AJ21">
         <v>12800</v>
       </c>
       <c r="AK21" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL21" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AN21" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ21" s="1" t="s">
         <v>3</v>
@@ -5445,13 +5475,13 @@
     </row>
     <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B22" t="s">
         <v>97</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D22" t="s">
         <v>27</v>
@@ -5460,10 +5490,10 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5481,7 +5511,7 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
@@ -5492,16 +5522,16 @@
         <v>44</v>
       </c>
       <c r="AE22" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF22">
         <v>1</v>
       </c>
       <c r="AG22" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AH22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AJ22">
         <v>25600</v>
@@ -5510,17 +5540,17 @@
         <v>46</v>
       </c>
       <c r="AL22" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AM22" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AN22" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AQ22" s="1" t="s">
         <v>3</v>
@@ -5528,13 +5558,13 @@
     </row>
     <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
@@ -5543,10 +5573,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -5564,7 +5594,7 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
@@ -5581,26 +5611,26 @@
         <v>1</v>
       </c>
       <c r="AG23" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AH23" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AK23" t="s">
         <v>46</v>
       </c>
       <c r="AL23" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AM23" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AN23" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AQ23" s="1" t="s">
         <v>3</v>
@@ -5608,13 +5638,13 @@
     </row>
     <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
@@ -5623,10 +5653,10 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -5644,7 +5674,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
@@ -5655,16 +5685,16 @@
         <v>44</v>
       </c>
       <c r="AE24" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF24">
         <v>2</v>
       </c>
       <c r="AG24" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AH24" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AJ24">
         <v>12800</v>
@@ -5673,17 +5703,17 @@
         <v>46</v>
       </c>
       <c r="AL24" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AM24" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AN24" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AQ24" s="1" t="s">
         <v>3</v>
@@ -5691,13 +5721,13 @@
     </row>
     <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B25" t="s">
         <v>97</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
@@ -5706,10 +5736,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -5727,7 +5757,7 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
@@ -5738,16 +5768,16 @@
         <v>44</v>
       </c>
       <c r="AE25" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AF25">
         <v>1</v>
       </c>
       <c r="AG25" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AH25" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AJ25">
         <v>7200</v>
@@ -5756,17 +5786,17 @@
         <v>46</v>
       </c>
       <c r="AL25" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AM25" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AN25" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ25" s="1" t="s">
         <v>3</v>
@@ -5774,13 +5804,13 @@
     </row>
     <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B26" t="s">
         <v>97</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D26" t="s">
         <v>27</v>
@@ -5789,10 +5819,10 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -5810,7 +5840,7 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
@@ -5827,10 +5857,10 @@
         <v>1</v>
       </c>
       <c r="AG26" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AH26" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ26">
         <v>5600</v>
@@ -5839,17 +5869,17 @@
         <v>46</v>
       </c>
       <c r="AL26" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AM26" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AN26" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ26" s="1" t="s">
         <v>3</v>
@@ -5857,13 +5887,13 @@
     </row>
     <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D27" t="s">
         <v>27</v>
@@ -5872,10 +5902,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -5893,7 +5923,7 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
@@ -5910,10 +5940,10 @@
         <v>2</v>
       </c>
       <c r="AG27" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AH27" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ27">
         <v>9600</v>
@@ -5922,17 +5952,17 @@
         <v>46</v>
       </c>
       <c r="AL27" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AN27" s="1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ27" s="1" t="s">
         <v>3</v>
@@ -5940,13 +5970,13 @@
     </row>
     <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B28" t="s">
         <v>97</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D28" t="s">
         <v>27</v>
@@ -5955,10 +5985,10 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -5976,7 +6006,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
@@ -5993,10 +6023,10 @@
         <v>2</v>
       </c>
       <c r="AG28" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AH28" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ28">
         <v>4200</v>
@@ -6005,17 +6035,17 @@
         <v>46</v>
       </c>
       <c r="AL28" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN28" s="1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ28" s="1" t="s">
         <v>3</v>
@@ -6023,13 +6053,13 @@
     </row>
     <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B29" t="s">
         <v>97</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D29" t="s">
         <v>27</v>
@@ -6038,10 +6068,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -6059,7 +6089,7 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
@@ -6070,16 +6100,16 @@
         <v>44</v>
       </c>
       <c r="AE29" t="s">
-        <v>45</v>
+        <v>420</v>
       </c>
       <c r="AF29">
         <v>1</v>
       </c>
       <c r="AG29" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AH29" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AJ29">
         <v>5600</v>
@@ -6088,19 +6118,19 @@
         <v>46</v>
       </c>
       <c r="AL29" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AN29" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AO29" s="1" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AP29" s="1" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AQ29" s="1" t="s">
         <v>3</v>
@@ -6108,13 +6138,13 @@
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B30" t="s">
         <v>97</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D30" t="s">
         <v>27</v>
@@ -6123,10 +6153,10 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -6144,7 +6174,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
@@ -6155,37 +6185,37 @@
         <v>44</v>
       </c>
       <c r="AE30" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AF30">
         <v>1</v>
       </c>
       <c r="AG30" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AH30" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AJ30">
         <v>2400</v>
       </c>
       <c r="AK30" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AL30" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AM30" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AN30" s="1" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AO30" s="1" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AP30" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AQ30" s="1" t="s">
         <v>3</v>
@@ -6193,13 +6223,13 @@
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B31" t="s">
         <v>97</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D31" t="s">
         <v>27</v>
@@ -6208,10 +6238,10 @@
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -6229,7 +6259,7 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
@@ -6240,37 +6270,37 @@
         <v>44</v>
       </c>
       <c r="AE31" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AF31">
         <v>1</v>
       </c>
       <c r="AG31" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AH31" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AJ31">
         <v>3800</v>
       </c>
       <c r="AK31" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AL31" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AM31" s="1" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AN31" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AO31" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="AP31" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="AP31" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="AQ31" s="1" t="s">
         <v>3</v>
@@ -6278,13 +6308,13 @@
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B32" t="s">
         <v>97</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
@@ -6293,10 +6323,10 @@
         <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -6314,7 +6344,7 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
@@ -6325,37 +6355,37 @@
         <v>44</v>
       </c>
       <c r="AE32" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AF32">
         <v>1</v>
       </c>
       <c r="AG32" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AH32" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ32">
         <v>3600</v>
       </c>
       <c r="AK32" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL32" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM32" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="AN32" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AO32" s="1" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AP32" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ32" s="1" t="s">
         <v>3</v>
@@ -6363,13 +6393,13 @@
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
@@ -6378,10 +6408,10 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -6399,7 +6429,7 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
@@ -6410,35 +6440,35 @@
         <v>44</v>
       </c>
       <c r="AE33" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AF33">
         <v>1</v>
       </c>
       <c r="AG33" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AH33" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ33">
         <v>2160</v>
       </c>
       <c r="AK33" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL33" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AN33" s="1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ33" s="1" t="s">
         <v>3</v>
@@ -6446,13 +6476,13 @@
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B34" t="s">
         <v>97</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -6461,10 +6491,10 @@
         <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -6482,7 +6512,7 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
@@ -6493,35 +6523,35 @@
         <v>44</v>
       </c>
       <c r="AE34" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AF34">
         <v>1</v>
       </c>
       <c r="AG34" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AH34" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ34">
         <v>2160</v>
       </c>
       <c r="AK34" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL34" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AN34" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="AQ34" s="1" t="s">
         <v>3</v>
@@ -6529,13 +6559,13 @@
     </row>
     <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B35" t="s">
         <v>97</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -6544,10 +6574,10 @@
         <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -6565,7 +6595,7 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
@@ -6576,35 +6606,35 @@
         <v>44</v>
       </c>
       <c r="AE35" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AF35">
         <v>1</v>
       </c>
       <c r="AG35" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AH35" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ35">
         <v>3600</v>
       </c>
       <c r="AK35" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL35" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AN35" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AQ35" s="1" t="s">
         <v>3</v>
@@ -6612,13 +6642,13 @@
     </row>
     <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D36" t="s">
         <v>27</v>
@@ -6627,10 +6657,10 @@
         <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -6648,7 +6678,7 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -6659,35 +6689,35 @@
         <v>44</v>
       </c>
       <c r="AE36" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AF36">
         <v>1</v>
       </c>
       <c r="AG36" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AH36" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ36">
         <v>2160</v>
       </c>
       <c r="AK36" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL36" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM36" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AN36" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ36" s="1" t="s">
         <v>3</v>
@@ -6695,13 +6725,13 @@
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B37" t="s">
         <v>97</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D37" t="s">
         <v>27</v>
@@ -6710,10 +6740,10 @@
         <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -6731,7 +6761,7 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
@@ -6748,10 +6778,10 @@
         <v>1</v>
       </c>
       <c r="AG37" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="AH37" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ37">
         <v>696</v>
@@ -6760,17 +6790,17 @@
         <v>46</v>
       </c>
       <c r="AL37" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM37" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AN37" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ37" s="1" t="s">
         <v>3</v>
@@ -6778,13 +6808,13 @@
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B38" t="s">
         <v>97</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D38" t="s">
         <v>27</v>
@@ -6793,10 +6823,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -6814,7 +6844,7 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
@@ -6831,10 +6861,10 @@
         <v>1</v>
       </c>
       <c r="AG38" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AH38" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ38">
         <v>696</v>
@@ -6843,17 +6873,17 @@
         <v>46</v>
       </c>
       <c r="AL38" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AN38" s="1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AQ38" s="1" t="s">
         <v>3</v>
@@ -6861,13 +6891,13 @@
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B39" t="s">
         <v>97</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D39" t="s">
         <v>27</v>
@@ -6876,10 +6906,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -6897,7 +6927,7 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
@@ -6908,35 +6938,35 @@
         <v>44</v>
       </c>
       <c r="AE39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AF39">
         <v>1</v>
       </c>
       <c r="AG39" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AH39" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AJ39">
         <v>7200</v>
       </c>
       <c r="AK39" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL39" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM39" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AN39" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ39" s="1" t="s">
         <v>3</v>
@@ -6944,13 +6974,13 @@
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D40" t="s">
         <v>27</v>
@@ -6959,10 +6989,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -6980,7 +7010,7 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
@@ -6991,35 +7021,35 @@
         <v>44</v>
       </c>
       <c r="AE40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AF40">
         <v>1</v>
       </c>
       <c r="AG40" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AH40" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AJ40">
         <v>7200</v>
       </c>
       <c r="AK40" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL40" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM40" s="1" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AN40" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ40" s="1" t="s">
         <v>3</v>
@@ -7027,13 +7057,13 @@
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B41" t="s">
         <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D41" t="s">
         <v>27</v>
@@ -7042,10 +7072,10 @@
         <v>28</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -7063,7 +7093,7 @@
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
@@ -7080,29 +7110,29 @@
         <v>2</v>
       </c>
       <c r="AG41" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AH41" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ41">
         <v>7200</v>
       </c>
       <c r="AK41" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL41" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AN41" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ41" s="1" t="s">
         <v>3</v>
@@ -7110,13 +7140,13 @@
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B42" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D42" t="s">
         <v>27</v>
@@ -7125,10 +7155,10 @@
         <v>28</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -7146,7 +7176,7 @@
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
@@ -7163,29 +7193,29 @@
         <v>1.2</v>
       </c>
       <c r="AG42" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AH42" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ42">
         <v>4800</v>
       </c>
       <c r="AK42" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL42" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM42" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="AN42" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AQ42" s="1" t="s">
         <v>3</v>
@@ -7193,13 +7223,13 @@
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B43" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D43" t="s">
         <v>27</v>
@@ -7208,10 +7238,10 @@
         <v>28</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -7229,7 +7259,7 @@
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
@@ -7246,29 +7276,29 @@
         <v>2</v>
       </c>
       <c r="AG43" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AH43" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ43">
         <v>4320</v>
       </c>
       <c r="AK43" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL43" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AM43" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AN43" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AQ43" s="1" t="s">
         <v>3</v>
@@ -7276,13 +7306,13 @@
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B44" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
@@ -7291,10 +7321,10 @@
         <v>28</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -7312,7 +7342,7 @@
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
@@ -7329,10 +7359,10 @@
         <v>1</v>
       </c>
       <c r="AG44" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AH44" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ44">
         <v>696</v>
@@ -7341,17 +7371,17 @@
         <v>46</v>
       </c>
       <c r="AL44" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AN44" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AQ44" s="1" t="s">
         <v>3</v>
@@ -7359,13 +7389,13 @@
     </row>
     <row r="45" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B45" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
@@ -7374,10 +7404,10 @@
         <v>28</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -7388,17 +7418,17 @@
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q45" s="1"/>
       <c r="S45" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="T45" t="s">
         <v>108</v>
@@ -7406,7 +7436,7 @@
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
@@ -7423,41 +7453,41 @@
         <v>2</v>
       </c>
       <c r="AG45" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AH45" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AJ45">
         <v>12800</v>
       </c>
       <c r="AK45" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AL45" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="AN45" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AQ45" s="1"/>
     </row>
     <row r="46" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B46" t="s">
         <v>97</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D46" t="s">
         <v>27</v>
@@ -7466,10 +7496,10 @@
         <v>28</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -7487,7 +7517,7 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
@@ -7498,16 +7528,16 @@
         <v>44</v>
       </c>
       <c r="AE46" t="s">
-        <v>38</v>
+        <v>506</v>
       </c>
       <c r="AF46">
         <v>1</v>
       </c>
       <c r="AG46" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AH46" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AJ46">
         <v>3600</v>
@@ -7516,17 +7546,17 @@
         <v>46</v>
       </c>
       <c r="AL46" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AM46" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AN46" s="1" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="AQ46" s="1" t="s">
         <v>3</v>
@@ -7534,13 +7564,13 @@
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B47" t="s">
         <v>97</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D47" t="s">
         <v>27</v>
@@ -7549,10 +7579,10 @@
         <v>28</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -7567,7 +7597,7 @@
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="S47" s="1" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="T47" t="s">
         <v>108</v>
@@ -7575,7 +7605,7 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -7592,10 +7622,10 @@
         <v>1</v>
       </c>
       <c r="AG47" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="AH47" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="AJ47">
         <v>960</v>
@@ -7604,10 +7634,10 @@
         <v>46</v>
       </c>
       <c r="AM47" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="AN47" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
@@ -7615,13 +7645,13 @@
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B48" t="s">
         <v>97</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D48" t="s">
         <v>27</v>
@@ -7630,10 +7660,10 @@
         <v>28</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -7648,7 +7678,7 @@
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="S48" s="1" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="T48" t="s">
         <v>108</v>
@@ -7656,7 +7686,7 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
@@ -7673,10 +7703,10 @@
         <v>1</v>
       </c>
       <c r="AG48" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="AH48" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="AJ48">
         <v>480</v>
@@ -7685,10 +7715,10 @@
         <v>46</v>
       </c>
       <c r="AM48" s="1" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="AN48" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
@@ -7696,13 +7726,13 @@
     </row>
     <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B49" t="s">
         <v>97</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D49" t="s">
         <v>27</v>
@@ -7711,10 +7741,10 @@
         <v>28</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -7732,7 +7762,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
@@ -7743,16 +7773,16 @@
         <v>69</v>
       </c>
       <c r="AE49" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="AF49">
         <v>9</v>
       </c>
       <c r="AG49" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AH49" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="AI49">
         <v>4</v>
@@ -7764,17 +7794,17 @@
         <v>92</v>
       </c>
       <c r="AL49" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="AN49" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="AQ49" s="1" t="s">
         <v>3</v>
@@ -7782,13 +7812,13 @@
     </row>
     <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B50" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
@@ -7797,10 +7827,10 @@
         <v>28</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -7818,7 +7848,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
@@ -7829,16 +7859,16 @@
         <v>69</v>
       </c>
       <c r="AE50" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="AF50">
         <v>14</v>
       </c>
       <c r="AG50" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AH50" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="AI50">
         <v>8</v>
@@ -7850,17 +7880,17 @@
         <v>92</v>
       </c>
       <c r="AL50" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="AN50" s="1" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="AQ50" s="1" t="s">
         <v>3</v>
@@ -7868,13 +7898,13 @@
     </row>
     <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B51" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
@@ -7883,10 +7913,10 @@
         <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -7904,7 +7934,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -7915,16 +7945,16 @@
         <v>69</v>
       </c>
       <c r="AE51" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="AF51">
         <v>26</v>
       </c>
       <c r="AG51" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AH51" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="AI51">
         <v>16</v>
@@ -7936,17 +7966,17 @@
         <v>92</v>
       </c>
       <c r="AL51" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AM51" s="1" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="AN51" s="1" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="AQ51" s="1" t="s">
         <v>3</v>
@@ -7954,13 +7984,13 @@
     </row>
     <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B52" t="s">
         <v>97</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="D52" t="s">
         <v>27</v>
@@ -7969,10 +7999,10 @@
         <v>28</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -7990,7 +8020,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
       <c r="W52" s="1" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
@@ -8001,32 +8031,32 @@
         <v>44</v>
       </c>
       <c r="AE52" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="AF52">
         <v>2</v>
       </c>
       <c r="AG52" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AH52" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="AK52" t="s">
         <v>92</v>
       </c>
       <c r="AL52" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="AN52" s="1" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AQ52" s="1" t="s">
         <v>3</v>
@@ -8034,13 +8064,13 @@
     </row>
     <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B53" t="s">
         <v>97</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="D53" t="s">
         <v>27</v>
@@ -8049,10 +8079,10 @@
         <v>28</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -8070,7 +8100,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
@@ -8081,32 +8111,32 @@
         <v>44</v>
       </c>
       <c r="AE53" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="AF53">
         <v>2</v>
       </c>
       <c r="AG53" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AH53" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AK53" t="s">
         <v>92</v>
       </c>
       <c r="AL53" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="AM53" s="1" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="AN53" s="1" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="AQ53" s="1" t="s">
         <v>3</v>
@@ -8114,13 +8144,13 @@
     </row>
     <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B54" t="s">
         <v>97</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D54" t="s">
         <v>27</v>
@@ -8129,10 +8159,10 @@
         <v>28</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -8150,7 +8180,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
@@ -8161,32 +8191,32 @@
         <v>44</v>
       </c>
       <c r="AE54" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="AF54">
         <v>1</v>
       </c>
       <c r="AG54" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AH54" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="AK54" t="s">
         <v>92</v>
       </c>
       <c r="AL54" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="AN54" s="1" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AQ54" s="1" t="s">
         <v>3</v>
@@ -8194,13 +8224,13 @@
     </row>
     <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B55" t="s">
         <v>97</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -8209,10 +8239,10 @@
         <v>28</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -8230,7 +8260,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
@@ -8241,32 +8271,32 @@
         <v>44</v>
       </c>
       <c r="AE55" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="AF55">
         <v>1</v>
       </c>
       <c r="AG55" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AH55" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="AK55" t="s">
         <v>92</v>
       </c>
       <c r="AL55" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="AN55" s="1" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AQ55" s="1" t="s">
         <v>3</v>
@@ -8274,13 +8304,13 @@
     </row>
     <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B56" t="s">
         <v>97</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -8289,10 +8319,10 @@
         <v>28</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -8310,7 +8340,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
@@ -8321,32 +8351,32 @@
         <v>44</v>
       </c>
       <c r="AE56" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="AF56">
         <v>1</v>
       </c>
       <c r="AG56" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AH56" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AK56" t="s">
         <v>92</v>
       </c>
       <c r="AL56" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="AN56" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AQ56" s="1" t="s">
         <v>3</v>
@@ -8354,13 +8384,13 @@
     </row>
     <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B57" t="s">
         <v>97</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -8369,10 +8399,10 @@
         <v>28</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -8390,7 +8420,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
@@ -8401,32 +8431,32 @@
         <v>44</v>
       </c>
       <c r="AE57" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="AF57">
         <v>1</v>
       </c>
       <c r="AG57" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AH57" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AK57" t="s">
         <v>92</v>
       </c>
       <c r="AL57" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AM57" s="1" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="AN57" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="AQ57" s="1" t="s">
         <v>3</v>
@@ -8434,13 +8464,13 @@
     </row>
     <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B58" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="D58" t="s">
         <v>27</v>
@@ -8449,10 +8479,10 @@
         <v>28</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -8470,7 +8500,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
@@ -8480,30 +8510,33 @@
       <c r="AD58" t="s">
         <v>44</v>
       </c>
+      <c r="AE58" t="s">
+        <v>581</v>
+      </c>
       <c r="AF58">
         <v>1</v>
       </c>
       <c r="AG58" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="AH58" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="AK58" t="s">
         <v>92</v>
       </c>
       <c r="AL58" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="AM58" s="1" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="AN58" s="1" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="AQ58" s="1" t="s">
         <v>3</v>
@@ -8511,13 +8544,13 @@
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B59" t="s">
         <v>97</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
@@ -8526,10 +8559,10 @@
         <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -8547,7 +8580,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
@@ -8558,16 +8591,16 @@
         <v>44</v>
       </c>
       <c r="AE59" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF59">
         <v>1</v>
       </c>
       <c r="AG59" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AH59" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AJ59">
         <v>12800</v>
@@ -8579,16 +8612,16 @@
         <v>50</v>
       </c>
       <c r="AM59" s="1" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="AN59" s="1" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="AO59" s="1" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="AP59" s="1" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="AQ59" s="1" t="s">
         <v>3</v>
@@ -8596,13 +8629,13 @@
     </row>
     <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B60" t="s">
         <v>97</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -8611,10 +8644,10 @@
         <v>28</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -8632,7 +8665,7 @@
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
@@ -8643,16 +8676,16 @@
         <v>44</v>
       </c>
       <c r="AE60" t="s">
-        <v>45</v>
+        <v>420</v>
       </c>
       <c r="AF60">
         <v>1</v>
       </c>
       <c r="AG60" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AH60" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AJ60">
         <v>12800</v>
@@ -8664,16 +8697,16 @@
         <v>50</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="AN60" s="1" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AO60" s="1" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="AP60" s="1" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="AQ60" s="1" t="s">
         <v>3</v>
@@ -8681,13 +8714,13 @@
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B61" t="s">
         <v>97</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
@@ -8696,10 +8729,10 @@
         <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -8717,7 +8750,7 @@
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
@@ -8728,16 +8761,16 @@
         <v>44</v>
       </c>
       <c r="AE61" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AF61">
         <v>2</v>
       </c>
       <c r="AG61" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AH61" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AJ61">
         <v>51200</v>
@@ -8746,16 +8779,16 @@
         <v>103</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="AN61" s="1" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="AO61" s="1" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="AP61" s="1" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="AQ61" s="1" t="s">
         <v>3</v>
@@ -8814,13 +8847,13 @@
   <sheetData>
     <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -8829,16 +8862,16 @@
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>6</v>
@@ -8850,54 +8883,54 @@
         <v>54</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
@@ -8912,16 +8945,16 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="H2">
         <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -8934,20 +8967,20 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
@@ -8962,16 +8995,16 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="H3">
         <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -8984,20 +9017,20 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
@@ -9012,16 +9045,16 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="H4">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -9034,20 +9067,20 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B5" t="s">
         <v>97</v>
@@ -9062,10 +9095,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -9078,20 +9111,20 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
@@ -9106,10 +9139,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -9122,20 +9155,20 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
@@ -9150,10 +9183,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -9166,20 +9199,20 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B8" t="s">
         <v>97</v>
@@ -9194,10 +9227,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -9210,20 +9243,20 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B9" t="s">
         <v>97</v>
@@ -9238,16 +9271,16 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="H9">
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -9260,20 +9293,20 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B10" t="s">
         <v>97</v>
@@ -9288,16 +9321,16 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="H10">
         <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -9310,20 +9343,20 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B11" t="s">
         <v>97</v>
@@ -9338,53 +9371,53 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="H11">
         <v>36</v>
       </c>
       <c r="I11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K11" t="s">
         <v>54</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="P11" s="1"/>
       <c r="R11" s="1" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B12" t="s">
         <v>97</v>
@@ -9399,55 +9432,55 @@
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="H12">
         <v>32</v>
       </c>
       <c r="I12" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K12" t="s">
         <v>54</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="P12" s="1"/>
       <c r="R12" s="1" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B13" t="s">
         <v>97</v>
@@ -9462,16 +9495,16 @@
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="H13">
         <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -9484,20 +9517,20 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
@@ -9512,16 +9545,16 @@
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="H14">
         <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -9534,20 +9567,20 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
@@ -9562,16 +9595,16 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="H15">
         <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -9584,20 +9617,20 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B16" t="s">
         <v>97</v>
@@ -9612,16 +9645,16 @@
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="H16">
         <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -9634,20 +9667,20 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="B17" t="s">
         <v>97</v>
@@ -9662,16 +9695,16 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="H17">
         <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -9684,20 +9717,20 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B18" t="s">
         <v>97</v>
@@ -9712,16 +9745,16 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="H18">
         <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -9734,20 +9767,20 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B19" t="s">
         <v>97</v>
@@ -9762,16 +9795,16 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="H19">
         <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -9784,20 +9817,20 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="B20" t="s">
         <v>97</v>
@@ -9812,10 +9845,10 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -9828,20 +9861,20 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="B21" t="s">
         <v>97</v>
@@ -9856,10 +9889,10 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -9872,20 +9905,20 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="B22" t="s">
         <v>97</v>
@@ -9900,10 +9933,10 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -9916,20 +9949,20 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
@@ -9944,10 +9977,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -9960,20 +9993,20 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
@@ -9988,10 +10021,10 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -10004,20 +10037,20 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="B25" t="s">
         <v>97</v>
@@ -10032,10 +10065,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -10048,20 +10081,20 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="B26" t="s">
         <v>97</v>
@@ -10076,10 +10109,10 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -10092,20 +10125,20 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
@@ -10120,10 +10153,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -10136,20 +10169,20 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="B28" t="s">
         <v>97</v>
@@ -10164,10 +10197,10 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -10180,20 +10213,20 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B29" t="s">
         <v>97</v>
@@ -10208,10 +10241,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -10224,26 +10257,26 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="B30" t="s">
         <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
         <v>27</v>
@@ -10252,16 +10285,16 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="H30">
         <v>8</v>
       </c>
       <c r="I30" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -10274,26 +10307,26 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B31" t="s">
         <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
         <v>27</v>
@@ -10302,16 +10335,16 @@
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="H31">
         <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -10324,26 +10357,26 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="B32" t="s">
         <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
@@ -10352,16 +10385,16 @@
         <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="H32">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -10374,26 +10407,26 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
@@ -10402,16 +10435,16 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="H33">
         <v>24</v>
       </c>
       <c r="I33" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -10424,26 +10457,26 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="B34" t="s">
         <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -10452,16 +10485,16 @@
         <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="H34">
         <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -10474,26 +10507,26 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="B35" t="s">
         <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -10502,16 +10535,16 @@
         <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="H35">
         <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -10524,26 +10557,26 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D36" t="s">
         <v>27</v>
@@ -10552,16 +10585,16 @@
         <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="H36">
         <v>48</v>
       </c>
       <c r="I36" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -10574,26 +10607,26 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="B37" t="s">
         <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D37" t="s">
         <v>27</v>
@@ -10602,16 +10635,16 @@
         <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="H37">
         <v>48</v>
       </c>
       <c r="I37" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -10624,20 +10657,20 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="B38" t="s">
         <v>97</v>
@@ -10652,10 +10685,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -10668,20 +10701,20 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="B39" t="s">
         <v>97</v>
@@ -10696,10 +10729,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -10712,20 +10745,20 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
@@ -10740,10 +10773,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -10756,15 +10789,15 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -10805,827 +10838,827 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -11651,7 +11684,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -11660,10 +11693,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11671,7 +11704,7 @@
         <v>97</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -11687,7 +11720,7 @@
         <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -11703,7 +11736,7 @@
         <v>97</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -11719,7 +11752,7 @@
         <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
@@ -11735,7 +11768,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -11751,7 +11784,7 @@
         <v>97</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -11767,7 +11800,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
@@ -11783,7 +11816,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -11799,7 +11832,7 @@
         <v>97</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -11815,7 +11848,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -11831,7 +11864,7 @@
         <v>97</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -11847,7 +11880,7 @@
         <v>97</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -11863,7 +11896,7 @@
         <v>97</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
@@ -11879,7 +11912,7 @@
         <v>97</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -11895,7 +11928,7 @@
         <v>97</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
@@ -11911,7 +11944,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -11927,7 +11960,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -11943,7 +11976,7 @@
         <v>97</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
@@ -11959,7 +11992,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
@@ -11975,7 +12008,7 @@
         <v>97</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -11991,7 +12024,7 @@
         <v>97</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>

--- a/data/catalog/datacenter.xlsx
+++ b/data/catalog/datacenter.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="755">
   <si>
     <t>family</t>
   </si>
@@ -1548,9 +1548,6 @@
   </si>
   <si>
     <t>N3K-C3548P-XL</t>
-  </si>
-  <si>
-    <t>https://www.cisco.com/c/en/us/products/collateral/switches/nexus-3000-series-switches/nexus-3524-x-3548-x-eol.html</t>
   </si>
   <si>
     <t>https://www.cisco.com/c/en/us/products/collateral/switches/nexus-3548-switch/data_sheet_c78-707001.html</t>
@@ -7596,16 +7593,14 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-      <c r="S47" s="1" t="s">
-        <v>511</v>
-      </c>
+      <c r="S47" s="1"/>
       <c r="T47" t="s">
         <v>108</v>
       </c>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
@@ -7622,10 +7617,10 @@
         <v>1</v>
       </c>
       <c r="AG47" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AH47" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AJ47">
         <v>960</v>
@@ -7634,10 +7629,10 @@
         <v>46</v>
       </c>
       <c r="AM47" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="AN47" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="AN47" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
@@ -7645,7 +7640,7 @@
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B48" t="s">
         <v>97</v>
@@ -7660,10 +7655,10 @@
         <v>28</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -7677,16 +7672,14 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
-      <c r="S48" s="1" t="s">
-        <v>511</v>
-      </c>
+      <c r="S48" s="1"/>
       <c r="T48" t="s">
         <v>108</v>
       </c>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
@@ -7703,10 +7696,10 @@
         <v>1</v>
       </c>
       <c r="AG48" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AH48" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AJ48">
         <v>480</v>
@@ -7715,10 +7708,10 @@
         <v>46</v>
       </c>
       <c r="AM48" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="AN48" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="AN48" s="1" t="s">
-        <v>518</v>
       </c>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
@@ -7726,13 +7719,13 @@
     </row>
     <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B49" t="s">
         <v>97</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D49" t="s">
         <v>27</v>
@@ -7741,10 +7734,10 @@
         <v>28</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -7762,7 +7755,7 @@
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
@@ -7779,10 +7772,10 @@
         <v>9</v>
       </c>
       <c r="AG49" t="s">
+        <v>522</v>
+      </c>
+      <c r="AH49" t="s">
         <v>523</v>
-      </c>
-      <c r="AH49" t="s">
-        <v>524</v>
       </c>
       <c r="AI49">
         <v>4</v>
@@ -7794,17 +7787,17 @@
         <v>92</v>
       </c>
       <c r="AL49" t="s">
+        <v>524</v>
+      </c>
+      <c r="AM49" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="AM49" s="1" t="s">
+      <c r="AN49" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="AN49" s="1" t="s">
-        <v>527</v>
       </c>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AQ49" s="1" t="s">
         <v>3</v>
@@ -7812,13 +7805,13 @@
     </row>
     <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B50" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
@@ -7827,10 +7820,10 @@
         <v>28</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -7848,7 +7841,7 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
@@ -7865,10 +7858,10 @@
         <v>14</v>
       </c>
       <c r="AG50" t="s">
+        <v>522</v>
+      </c>
+      <c r="AH50" t="s">
         <v>523</v>
-      </c>
-      <c r="AH50" t="s">
-        <v>524</v>
       </c>
       <c r="AI50">
         <v>8</v>
@@ -7880,17 +7873,17 @@
         <v>92</v>
       </c>
       <c r="AL50" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AM50" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="AN50" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="AN50" s="1" t="s">
-        <v>533</v>
       </c>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AQ50" s="1" t="s">
         <v>3</v>
@@ -7898,13 +7891,13 @@
     </row>
     <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B51" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
@@ -7913,10 +7906,10 @@
         <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -7934,7 +7927,7 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -7951,10 +7944,10 @@
         <v>26</v>
       </c>
       <c r="AG51" t="s">
+        <v>522</v>
+      </c>
+      <c r="AH51" t="s">
         <v>523</v>
-      </c>
-      <c r="AH51" t="s">
-        <v>524</v>
       </c>
       <c r="AI51">
         <v>16</v>
@@ -7966,17 +7959,17 @@
         <v>92</v>
       </c>
       <c r="AL51" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AM51" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="AN51" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="AN51" s="1" t="s">
-        <v>538</v>
       </c>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AQ51" s="1" t="s">
         <v>3</v>
@@ -7984,13 +7977,13 @@
     </row>
     <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B52" t="s">
         <v>97</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D52" t="s">
         <v>27</v>
@@ -7999,10 +7992,10 @@
         <v>28</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -8020,7 +8013,7 @@
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
       <c r="W52" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
@@ -8037,26 +8030,26 @@
         <v>2</v>
       </c>
       <c r="AG52" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH52" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AK52" t="s">
         <v>92</v>
       </c>
       <c r="AL52" t="s">
+        <v>543</v>
+      </c>
+      <c r="AM52" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="AM52" s="1" t="s">
+      <c r="AN52" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="AN52" s="1" t="s">
-        <v>546</v>
       </c>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AQ52" s="1" t="s">
         <v>3</v>
@@ -8064,13 +8057,13 @@
     </row>
     <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B53" t="s">
         <v>97</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D53" t="s">
         <v>27</v>
@@ -8079,10 +8072,10 @@
         <v>28</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -8100,7 +8093,7 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
@@ -8117,26 +8110,26 @@
         <v>2</v>
       </c>
       <c r="AG53" t="s">
+        <v>550</v>
+      </c>
+      <c r="AH53" t="s">
         <v>551</v>
-      </c>
-      <c r="AH53" t="s">
-        <v>552</v>
       </c>
       <c r="AK53" t="s">
         <v>92</v>
       </c>
       <c r="AL53" t="s">
+        <v>552</v>
+      </c>
+      <c r="AM53" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="AM53" s="1" t="s">
+      <c r="AN53" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="AN53" s="1" t="s">
-        <v>555</v>
       </c>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AQ53" s="1" t="s">
         <v>3</v>
@@ -8144,13 +8137,13 @@
     </row>
     <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B54" t="s">
         <v>97</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D54" t="s">
         <v>27</v>
@@ -8159,10 +8152,10 @@
         <v>28</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -8180,7 +8173,7 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
@@ -8197,26 +8190,26 @@
         <v>1</v>
       </c>
       <c r="AG54" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH54" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AK54" t="s">
         <v>92</v>
       </c>
       <c r="AL54" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AM54" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="AN54" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="AN54" s="1" t="s">
-        <v>562</v>
       </c>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AQ54" s="1" t="s">
         <v>3</v>
@@ -8224,13 +8217,13 @@
     </row>
     <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B55" t="s">
         <v>97</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -8239,10 +8232,10 @@
         <v>28</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -8260,7 +8253,7 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
@@ -8277,26 +8270,26 @@
         <v>1</v>
       </c>
       <c r="AG55" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH55" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AK55" t="s">
         <v>92</v>
       </c>
       <c r="AL55" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AM55" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="AN55" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="AN55" s="1" t="s">
-        <v>567</v>
       </c>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AQ55" s="1" t="s">
         <v>3</v>
@@ -8304,13 +8297,13 @@
     </row>
     <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B56" t="s">
         <v>97</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -8319,10 +8312,10 @@
         <v>28</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -8340,7 +8333,7 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
@@ -8357,26 +8350,26 @@
         <v>1</v>
       </c>
       <c r="AG56" t="s">
+        <v>550</v>
+      </c>
+      <c r="AH56" t="s">
         <v>551</v>
-      </c>
-      <c r="AH56" t="s">
-        <v>552</v>
       </c>
       <c r="AK56" t="s">
         <v>92</v>
       </c>
       <c r="AL56" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AM56" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="AN56" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="AN56" s="1" t="s">
-        <v>572</v>
       </c>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AQ56" s="1" t="s">
         <v>3</v>
@@ -8384,13 +8377,13 @@
     </row>
     <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B57" t="s">
         <v>97</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -8399,10 +8392,10 @@
         <v>28</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -8420,7 +8413,7 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
@@ -8437,26 +8430,26 @@
         <v>1</v>
       </c>
       <c r="AG57" t="s">
+        <v>550</v>
+      </c>
+      <c r="AH57" t="s">
         <v>551</v>
-      </c>
-      <c r="AH57" t="s">
-        <v>552</v>
       </c>
       <c r="AK57" t="s">
         <v>92</v>
       </c>
       <c r="AL57" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AM57" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="AN57" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="AN57" s="1" t="s">
-        <v>576</v>
       </c>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AQ57" s="1" t="s">
         <v>3</v>
@@ -8464,13 +8457,13 @@
     </row>
     <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B58" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D58" t="s">
         <v>27</v>
@@ -8479,10 +8472,10 @@
         <v>28</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -8500,7 +8493,7 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
@@ -8511,32 +8504,32 @@
         <v>44</v>
       </c>
       <c r="AE58" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AF58">
         <v>1</v>
       </c>
       <c r="AG58" t="s">
+        <v>581</v>
+      </c>
+      <c r="AH58" t="s">
         <v>582</v>
-      </c>
-      <c r="AH58" t="s">
-        <v>583</v>
       </c>
       <c r="AK58" t="s">
         <v>92</v>
       </c>
       <c r="AL58" t="s">
+        <v>583</v>
+      </c>
+      <c r="AM58" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="AM58" s="1" t="s">
+      <c r="AN58" s="1" t="s">
         <v>585</v>
-      </c>
-      <c r="AN58" s="1" t="s">
-        <v>586</v>
       </c>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AQ58" s="1" t="s">
         <v>3</v>
@@ -8544,13 +8537,13 @@
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B59" t="s">
         <v>97</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
@@ -8559,10 +8552,10 @@
         <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -8580,7 +8573,7 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
@@ -8612,16 +8605,16 @@
         <v>50</v>
       </c>
       <c r="AM59" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="AN59" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="AN59" s="1" t="s">
+      <c r="AO59" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="AO59" s="1" t="s">
+      <c r="AP59" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="AP59" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="AQ59" s="1" t="s">
         <v>3</v>
@@ -8629,13 +8622,13 @@
     </row>
     <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B60" t="s">
         <v>97</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -8644,10 +8637,10 @@
         <v>28</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -8665,7 +8658,7 @@
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
@@ -8682,7 +8675,7 @@
         <v>1</v>
       </c>
       <c r="AG60" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AH60" t="s">
         <v>279</v>
@@ -8697,16 +8690,16 @@
         <v>50</v>
       </c>
       <c r="AM60" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="AN60" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="AN60" s="1" t="s">
+      <c r="AO60" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="AO60" s="1" t="s">
+      <c r="AP60" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="AP60" s="1" t="s">
-        <v>600</v>
       </c>
       <c r="AQ60" s="1" t="s">
         <v>3</v>
@@ -8714,13 +8707,13 @@
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B61" t="s">
         <v>97</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
@@ -8729,10 +8722,10 @@
         <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -8750,7 +8743,7 @@
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
@@ -8779,16 +8772,16 @@
         <v>103</v>
       </c>
       <c r="AM61" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="AN61" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="AN61" s="1" t="s">
+      <c r="AO61" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="AO61" s="1" t="s">
+      <c r="AP61" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="AP61" s="1" t="s">
-        <v>605</v>
       </c>
       <c r="AQ61" s="1" t="s">
         <v>3</v>
@@ -8853,7 +8846,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -8868,10 +8861,10 @@
         <v>241</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>608</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>6</v>
@@ -8930,7 +8923,7 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
@@ -8945,10 +8938,10 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H2">
         <v>36</v>
@@ -8967,20 +8960,20 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>611</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
@@ -8995,10 +8988,10 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H3">
         <v>36</v>
@@ -9017,20 +9010,20 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>614</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>615</v>
       </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
@@ -9045,10 +9038,10 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H4">
         <v>14</v>
@@ -9067,20 +9060,20 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>617</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>618</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B5" t="s">
         <v>97</v>
@@ -9095,10 +9088,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -9111,20 +9104,20 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>620</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>621</v>
       </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
@@ -9139,10 +9132,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -9155,20 +9148,20 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="X6" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>624</v>
       </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
@@ -9183,10 +9176,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -9199,20 +9192,20 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="X7" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>627</v>
       </c>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B8" t="s">
         <v>97</v>
@@ -9227,10 +9220,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -9243,20 +9236,20 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="X8" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>630</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B9" t="s">
         <v>97</v>
@@ -9271,10 +9264,10 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H9">
         <v>16</v>
@@ -9293,20 +9286,20 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="X9" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>633</v>
       </c>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B10" t="s">
         <v>97</v>
@@ -9321,10 +9314,10 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H10">
         <v>36</v>
@@ -9343,20 +9336,20 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="X10" s="1" t="s">
         <v>635</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>636</v>
       </c>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B11" t="s">
         <v>97</v>
@@ -9371,10 +9364,10 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H11">
         <v>36</v>
@@ -9387,27 +9380,27 @@
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="O11" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="P11" s="1"/>
       <c r="R11" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
@@ -9417,7 +9410,7 @@
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B12" t="s">
         <v>97</v>
@@ -9432,10 +9425,10 @@
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H12">
         <v>32</v>
@@ -9448,30 +9441,30 @@
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="O12" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="P12" s="1"/>
       <c r="R12" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="X12" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="X12" s="1" t="s">
+      <c r="Y12" s="1" t="s">
         <v>647</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>648</v>
       </c>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1" t="s">
@@ -9480,7 +9473,7 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B13" t="s">
         <v>97</v>
@@ -9495,16 +9488,16 @@
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H13">
         <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -9517,20 +9510,20 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="X13" s="1" t="s">
         <v>651</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>652</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
@@ -9545,16 +9538,16 @@
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H14">
         <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -9567,20 +9560,20 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="X14" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>655</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
@@ -9595,10 +9588,10 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H15">
         <v>24</v>
@@ -9617,20 +9610,20 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="X15" s="1" t="s">
         <v>657</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>658</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B16" t="s">
         <v>97</v>
@@ -9645,10 +9638,10 @@
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H16">
         <v>36</v>
@@ -9667,20 +9660,20 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="X16" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>661</v>
       </c>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B17" t="s">
         <v>97</v>
@@ -9695,10 +9688,10 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H17">
         <v>36</v>
@@ -9717,20 +9710,20 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="X17" s="1" t="s">
         <v>663</v>
-      </c>
-      <c r="X17" s="1" t="s">
-        <v>664</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B18" t="s">
         <v>97</v>
@@ -9745,16 +9738,16 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H18">
         <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -9767,20 +9760,20 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="X18" s="1" t="s">
         <v>667</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>668</v>
       </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B19" t="s">
         <v>97</v>
@@ -9795,10 +9788,10 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H19">
         <v>32</v>
@@ -9817,20 +9810,20 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="X19" s="1" t="s">
         <v>670</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>671</v>
       </c>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B20" t="s">
         <v>97</v>
@@ -9845,10 +9838,10 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -9861,20 +9854,20 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="X20" s="1" t="s">
         <v>673</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>674</v>
       </c>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B21" t="s">
         <v>97</v>
@@ -9889,10 +9882,10 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -9905,20 +9898,20 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="X21" s="1" t="s">
         <v>676</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>677</v>
       </c>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B22" t="s">
         <v>97</v>
@@ -9933,10 +9926,10 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -9949,20 +9942,20 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="X22" s="1" t="s">
         <v>679</v>
-      </c>
-      <c r="X22" s="1" t="s">
-        <v>680</v>
       </c>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
@@ -9977,10 +9970,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -9993,20 +9986,20 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="X23" s="1" t="s">
         <v>682</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>683</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
@@ -10021,10 +10014,10 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -10037,20 +10030,20 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="X24" s="1" t="s">
         <v>685</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>686</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B25" t="s">
         <v>97</v>
@@ -10065,10 +10058,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -10081,20 +10074,20 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="X25" s="1" t="s">
         <v>688</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>689</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B26" t="s">
         <v>97</v>
@@ -10109,10 +10102,10 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -10125,20 +10118,20 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="X26" s="1" t="s">
         <v>691</v>
-      </c>
-      <c r="X26" s="1" t="s">
-        <v>692</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
@@ -10153,10 +10146,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -10169,20 +10162,20 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="X27" s="1" t="s">
         <v>694</v>
-      </c>
-      <c r="X27" s="1" t="s">
-        <v>695</v>
       </c>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B28" t="s">
         <v>97</v>
@@ -10197,10 +10190,10 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -10213,20 +10206,20 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="X28" s="1" t="s">
         <v>697</v>
-      </c>
-      <c r="X28" s="1" t="s">
-        <v>698</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B29" t="s">
         <v>97</v>
@@ -10241,10 +10234,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -10257,20 +10250,20 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="X29" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="X29" s="1" t="s">
-        <v>701</v>
       </c>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B30" t="s">
         <v>97</v>
@@ -10285,10 +10278,10 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H30">
         <v>8</v>
@@ -10307,20 +10300,20 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="X30" s="1" t="s">
         <v>703</v>
-      </c>
-      <c r="X30" s="1" t="s">
-        <v>704</v>
       </c>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B31" t="s">
         <v>97</v>
@@ -10335,16 +10328,16 @@
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H31">
         <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -10357,20 +10350,20 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="X31" s="1" t="s">
         <v>707</v>
-      </c>
-      <c r="X31" s="1" t="s">
-        <v>708</v>
       </c>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B32" t="s">
         <v>97</v>
@@ -10385,16 +10378,16 @@
         <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H32">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -10407,20 +10400,20 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="X32" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="X32" s="1" t="s">
-        <v>712</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
@@ -10435,16 +10428,16 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H33">
         <v>24</v>
       </c>
       <c r="I33" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -10457,20 +10450,20 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="X33" s="1" t="s">
         <v>715</v>
-      </c>
-      <c r="X33" s="1" t="s">
-        <v>716</v>
       </c>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B34" t="s">
         <v>97</v>
@@ -10485,16 +10478,16 @@
         <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H34">
         <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -10507,20 +10500,20 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="X34" s="1" t="s">
         <v>718</v>
-      </c>
-      <c r="X34" s="1" t="s">
-        <v>719</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B35" t="s">
         <v>97</v>
@@ -10535,16 +10528,16 @@
         <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H35">
         <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -10557,20 +10550,20 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="X35" s="1" t="s">
         <v>721</v>
-      </c>
-      <c r="X35" s="1" t="s">
-        <v>722</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
@@ -10585,16 +10578,16 @@
         <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H36">
         <v>48</v>
       </c>
       <c r="I36" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -10607,20 +10600,20 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="X36" s="1" t="s">
         <v>724</v>
-      </c>
-      <c r="X36" s="1" t="s">
-        <v>725</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B37" t="s">
         <v>97</v>
@@ -10635,16 +10628,16 @@
         <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H37">
         <v>48</v>
       </c>
       <c r="I37" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -10657,20 +10650,20 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="X37" s="1" t="s">
         <v>727</v>
-      </c>
-      <c r="X37" s="1" t="s">
-        <v>728</v>
       </c>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B38" t="s">
         <v>97</v>
@@ -10685,10 +10678,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -10701,20 +10694,20 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="X38" s="1" t="s">
         <v>730</v>
-      </c>
-      <c r="X38" s="1" t="s">
-        <v>731</v>
       </c>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B39" t="s">
         <v>97</v>
@@ -10729,10 +10722,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -10745,20 +10738,20 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="X39" s="1" t="s">
         <v>733</v>
-      </c>
-      <c r="X39" s="1" t="s">
-        <v>734</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
@@ -10773,10 +10766,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -10789,15 +10782,15 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="X40" s="1" t="s">
         <v>736</v>
-      </c>
-      <c r="X40" s="1" t="s">
-        <v>737</v>
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -10838,827 +10831,827 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>739</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>274</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>284</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>287</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>296</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>299</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>302</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>302</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>302</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
   </sheetData>
@@ -11693,10 +11686,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>754</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11704,7 +11697,7 @@
         <v>97</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -11720,7 +11713,7 @@
         <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -11736,7 +11729,7 @@
         <v>97</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -11752,7 +11745,7 @@
         <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
@@ -12024,7 +12017,7 @@
         <v>97</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>

--- a/data/catalog/datacenter.xlsx
+++ b/data/catalog/datacenter.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="757">
   <si>
     <t>family</t>
   </si>
@@ -777,6 +777,12 @@
   </si>
   <si>
     <t>licence_note_en</t>
+  </si>
+  <si>
+    <t>variant_note_tr</t>
+  </si>
+  <si>
+    <t>variant_note_en</t>
   </si>
   <si>
     <t>datasheet_url</t>
@@ -3634,7 +3640,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ61"/>
+  <dimension ref="A1:AS61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -3649,21 +3655,21 @@
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="36" style="1" customWidth="1"/>
     <col min="20" max="20" width="22" customWidth="1"/>
-    <col min="21" max="22" width="40" style="1" customWidth="1"/>
-    <col min="23" max="24" width="36" style="1" customWidth="1"/>
-    <col min="25" max="26" width="13" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10" customWidth="1"/>
-    <col min="28" max="29" width="40" style="1" customWidth="1"/>
-    <col min="30" max="30" width="16" customWidth="1"/>
-    <col min="31" max="31" width="22" customWidth="1"/>
-    <col min="32" max="32" width="12" customWidth="1"/>
-    <col min="33" max="34" width="18" customWidth="1"/>
-    <col min="35" max="36" width="12" customWidth="1"/>
-    <col min="37" max="38" width="22" customWidth="1"/>
-    <col min="39" max="43" width="40" style="1" customWidth="1"/>
+    <col min="21" max="24" width="40" style="1" customWidth="1"/>
+    <col min="25" max="26" width="36" style="1" customWidth="1"/>
+    <col min="27" max="28" width="13" style="1" customWidth="1"/>
+    <col min="29" max="29" width="10" customWidth="1"/>
+    <col min="30" max="31" width="40" style="1" customWidth="1"/>
+    <col min="32" max="32" width="16" customWidth="1"/>
+    <col min="33" max="33" width="22" customWidth="1"/>
+    <col min="34" max="34" width="12" customWidth="1"/>
+    <col min="35" max="36" width="18" customWidth="1"/>
+    <col min="37" max="38" width="12" customWidth="1"/>
+    <col min="39" max="40" width="22" customWidth="1"/>
+    <col min="41" max="45" width="40" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>238</v>
       </c>
@@ -3742,19 +3748,19 @@
       <c r="Z1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>258</v>
       </c>
       <c r="AB1" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>262</v>
       </c>
       <c r="AF1" s="2" t="s">
@@ -3773,15 +3779,15 @@
         <v>267</v>
       </c>
       <c r="AK1" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="AM1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AL1" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="AM1" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AN1" s="2" t="s">
         <v>270</v>
       </c>
       <c r="AO1" s="3" t="s">
@@ -3793,16 +3799,22 @@
       <c r="AQ1" s="3" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AR1" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="AS1" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -3811,10 +3823,10 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3831,64 +3843,66 @@
       </c>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
-      <c r="W2" s="1" t="s">
-        <v>276</v>
-      </c>
+      <c r="W2" s="1"/>
       <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
+      <c r="Y2" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" t="s">
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" t="s">
         <v>69</v>
       </c>
-      <c r="AE2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AF2">
+      <c r="AG2" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH2">
         <v>16</v>
       </c>
-      <c r="AG2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AI2">
+      <c r="AI2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>281</v>
+      </c>
+      <c r="AK2">
         <v>8</v>
       </c>
-      <c r="AJ2">
+      <c r="AL2">
         <v>115200</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" t="s">
         <v>46</v>
       </c>
-      <c r="AL2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AN2" t="s">
         <v>282</v>
       </c>
-      <c r="AO2" s="1"/>
+      <c r="AO2" s="1" t="s">
+        <v>283</v>
+      </c>
       <c r="AP2" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="AS2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
@@ -3897,10 +3911,10 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -3917,64 +3931,66 @@
       </c>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
-      <c r="W3" s="1" t="s">
-        <v>276</v>
-      </c>
+      <c r="W3" s="1"/>
       <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
+      <c r="Y3" s="1" t="s">
+        <v>278</v>
+      </c>
       <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" t="s">
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" t="s">
         <v>69</v>
       </c>
-      <c r="AE3" t="s">
-        <v>277</v>
-      </c>
-      <c r="AF3">
+      <c r="AG3" t="s">
+        <v>279</v>
+      </c>
+      <c r="AH3">
         <v>10</v>
       </c>
-      <c r="AG3" t="s">
-        <v>278</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>279</v>
-      </c>
-      <c r="AI3">
+      <c r="AI3" t="s">
+        <v>280</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>281</v>
+      </c>
+      <c r="AK3">
         <v>4</v>
       </c>
-      <c r="AJ3">
+      <c r="AL3">
         <v>57000</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AM3" t="s">
         <v>46</v>
       </c>
-      <c r="AL3" t="s">
-        <v>280</v>
-      </c>
-      <c r="AM3" s="1" t="s">
+      <c r="AN3" t="s">
+        <v>282</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="AN3" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="AO3" s="1"/>
-      <c r="AP3" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="AQ3" s="1" t="s">
+      <c r="AS3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
@@ -3983,10 +3999,10 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -4003,61 +4019,63 @@
       </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
-      <c r="W4" s="1" t="s">
-        <v>289</v>
-      </c>
+      <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
+      <c r="Y4" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" t="s">
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" t="s">
         <v>69</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AG4" t="s">
         <v>70</v>
       </c>
-      <c r="AF4">
+      <c r="AH4">
         <v>7</v>
       </c>
-      <c r="AG4" t="s">
-        <v>290</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>279</v>
-      </c>
-      <c r="AI4">
+      <c r="AI4" t="s">
+        <v>292</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>281</v>
+      </c>
+      <c r="AK4">
         <v>4</v>
       </c>
-      <c r="AK4" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>292</v>
-      </c>
-      <c r="AM4" s="1" t="s">
+      <c r="AM4" t="s">
         <v>293</v>
       </c>
-      <c r="AN4" s="1" t="s">
+      <c r="AN4" t="s">
         <v>294</v>
       </c>
-      <c r="AO4" s="1"/>
+      <c r="AO4" s="1" t="s">
+        <v>295</v>
+      </c>
       <c r="AP4" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="AQ4" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="AQ4" s="1"/>
+      <c r="AR4" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="AS4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B5" t="s">
         <v>97</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D5" t="s">
         <v>27</v>
@@ -4066,10 +4084,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -4086,61 +4104,63 @@
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
-      <c r="W5" s="1" t="s">
-        <v>289</v>
-      </c>
+      <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
+      <c r="Y5" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" t="s">
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" t="s">
         <v>69</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AG5" t="s">
         <v>70</v>
       </c>
-      <c r="AF5">
+      <c r="AH5">
         <v>13</v>
       </c>
-      <c r="AG5" t="s">
-        <v>290</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>279</v>
-      </c>
-      <c r="AI5">
+      <c r="AI5" t="s">
+        <v>292</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>281</v>
+      </c>
+      <c r="AK5">
         <v>8</v>
       </c>
-      <c r="AK5" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>292</v>
-      </c>
-      <c r="AM5" s="1" t="s">
+      <c r="AM5" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>294</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="AQ5" s="1"/>
+      <c r="AR5" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="AN5" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="AO5" s="1"/>
-      <c r="AP5" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="AQ5" s="1" t="s">
+      <c r="AS5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
@@ -4149,10 +4169,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -4169,64 +4189,66 @@
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
-      <c r="W6" s="1" t="s">
-        <v>289</v>
-      </c>
+      <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
+      <c r="Y6" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" t="s">
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" t="s">
         <v>69</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AG6" t="s">
         <v>70</v>
       </c>
-      <c r="AF6">
+      <c r="AH6">
         <v>21</v>
       </c>
-      <c r="AG6" t="s">
-        <v>290</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>279</v>
-      </c>
-      <c r="AI6">
+      <c r="AI6" t="s">
+        <v>292</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>281</v>
+      </c>
+      <c r="AK6">
         <v>16</v>
       </c>
-      <c r="AJ6">
+      <c r="AL6">
         <v>172800</v>
       </c>
-      <c r="AK6" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>292</v>
-      </c>
-      <c r="AM6" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="AN6" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="AO6" s="1"/>
+      <c r="AM6" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>294</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="AP6" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="AQ6" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="AQ6" s="1"/>
+      <c r="AR6" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="AS6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -4235,10 +4257,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -4255,64 +4277,66 @@
       </c>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
-      <c r="W7" s="1" t="s">
-        <v>304</v>
-      </c>
+      <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
+      <c r="Y7" s="1" t="s">
+        <v>306</v>
+      </c>
       <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" t="s">
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" t="s">
         <v>69</v>
       </c>
-      <c r="AE7" t="s">
-        <v>305</v>
-      </c>
-      <c r="AF7">
+      <c r="AG7" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH7">
         <v>4</v>
       </c>
-      <c r="AG7" t="s">
-        <v>306</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>279</v>
-      </c>
-      <c r="AI7">
+      <c r="AI7" t="s">
+        <v>308</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>281</v>
+      </c>
+      <c r="AK7">
         <v>8</v>
       </c>
-      <c r="AJ7">
+      <c r="AL7">
         <v>25600</v>
       </c>
-      <c r="AK7" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>307</v>
-      </c>
-      <c r="AM7" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="AN7" s="1" t="s">
+      <c r="AM7" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN7" t="s">
         <v>309</v>
       </c>
-      <c r="AO7" s="1"/>
+      <c r="AO7" s="1" t="s">
+        <v>310</v>
+      </c>
       <c r="AP7" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="AQ7" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="AQ7" s="1"/>
+      <c r="AR7" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AS7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B8" t="s">
         <v>97</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
@@ -4321,10 +4345,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -4341,61 +4365,63 @@
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
-      <c r="W8" s="1" t="s">
-        <v>313</v>
-      </c>
+      <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
+      <c r="Y8" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" t="s">
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" t="s">
         <v>44</v>
       </c>
-      <c r="AE8" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF8">
+      <c r="AG8" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH8">
         <v>2</v>
       </c>
-      <c r="AG8" t="s">
-        <v>315</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ8">
+      <c r="AI8" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>318</v>
+      </c>
+      <c r="AL8">
         <v>51200</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="AM8" t="s">
         <v>46</v>
       </c>
-      <c r="AL8" t="s">
-        <v>317</v>
-      </c>
-      <c r="AM8" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="AN8" s="1" t="s">
+      <c r="AN8" t="s">
         <v>319</v>
       </c>
-      <c r="AO8" s="1"/>
+      <c r="AO8" s="1" t="s">
+        <v>320</v>
+      </c>
       <c r="AP8" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AQ8" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="AQ8" s="1"/>
+      <c r="AR8" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="AS8" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B9" t="s">
         <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -4404,10 +4430,10 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -4424,61 +4450,63 @@
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
-      <c r="W9" s="1" t="s">
-        <v>313</v>
-      </c>
+      <c r="W9" s="1"/>
       <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
+      <c r="Y9" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" t="s">
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" t="s">
         <v>44</v>
       </c>
-      <c r="AE9" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF9">
+      <c r="AG9" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH9">
         <v>2</v>
       </c>
-      <c r="AG9" t="s">
-        <v>315</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ9">
+      <c r="AI9" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>318</v>
+      </c>
+      <c r="AL9">
         <v>51200</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AM9" t="s">
         <v>46</v>
       </c>
-      <c r="AL9" t="s">
-        <v>317</v>
-      </c>
-      <c r="AM9" s="1" t="s">
+      <c r="AN9" t="s">
+        <v>319</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="AQ9" s="1"/>
+      <c r="AR9" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="AN9" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="AO9" s="1"/>
-      <c r="AP9" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="AQ9" s="1" t="s">
+      <c r="AS9" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B10" t="s">
         <v>97</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
@@ -4487,10 +4515,10 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -4507,42 +4535,38 @@
       </c>
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
-      <c r="W10" s="1" t="s">
-        <v>313</v>
-      </c>
+      <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
+      <c r="Y10" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="Z10" s="1"/>
+      <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" t="s">
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" t="s">
         <v>44</v>
       </c>
-      <c r="AE10" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF10">
+      <c r="AG10" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH10">
         <v>2</v>
       </c>
-      <c r="AG10" t="s">
-        <v>315</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ10">
+      <c r="AI10" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>318</v>
+      </c>
+      <c r="AL10">
         <v>51200</v>
       </c>
-      <c r="AK10" t="s">
+      <c r="AM10" t="s">
         <v>46</v>
       </c>
-      <c r="AL10" t="s">
-        <v>325</v>
-      </c>
-      <c r="AM10" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="AN10" s="1" t="s">
+      <c r="AN10" t="s">
         <v>327</v>
       </c>
       <c r="AO10" s="1" t="s">
@@ -4552,18 +4576,24 @@
         <v>329</v>
       </c>
       <c r="AQ10" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="AR10" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="AS10" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B11" t="s">
         <v>97</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D11" t="s">
         <v>27</v>
@@ -4572,10 +4602,10 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -4592,63 +4622,65 @@
       </c>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
-      <c r="W11" s="1" t="s">
-        <v>313</v>
-      </c>
+      <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
+      <c r="Y11" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" t="s">
+      <c r="AD11" s="1"/>
+      <c r="AE11" s="1"/>
+      <c r="AF11" t="s">
         <v>44</v>
       </c>
-      <c r="AE11" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF11">
+      <c r="AG11" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH11">
         <v>2</v>
       </c>
-      <c r="AG11" t="s">
-        <v>315</v>
-      </c>
-      <c r="AH11" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ11">
+      <c r="AI11" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>318</v>
+      </c>
+      <c r="AL11">
         <v>51200</v>
       </c>
-      <c r="AK11" t="s">
+      <c r="AM11" t="s">
         <v>46</v>
       </c>
-      <c r="AL11" t="s">
-        <v>325</v>
-      </c>
-      <c r="AM11" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="AN11" s="1" t="s">
-        <v>332</v>
+      <c r="AN11" t="s">
+        <v>327</v>
       </c>
       <c r="AO11" s="1" t="s">
         <v>333</v>
       </c>
       <c r="AP11" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AQ11" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="AR11" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="AS11" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B12" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
@@ -4657,10 +4689,10 @@
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -4677,61 +4709,63 @@
       </c>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
-      <c r="W12" s="1" t="s">
-        <v>335</v>
-      </c>
+      <c r="W12" s="1"/>
       <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
+      <c r="Y12" s="1" t="s">
+        <v>337</v>
+      </c>
       <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AD12" t="s">
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" t="s">
         <v>44</v>
       </c>
-      <c r="AE12" t="s">
+      <c r="AG12" t="s">
         <v>70</v>
       </c>
-      <c r="AF12">
+      <c r="AH12">
         <v>3</v>
       </c>
-      <c r="AG12" t="s">
-        <v>315</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ12">
+      <c r="AI12" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>318</v>
+      </c>
+      <c r="AL12">
         <v>102400</v>
       </c>
-      <c r="AK12" t="s">
+      <c r="AM12" t="s">
         <v>46</v>
       </c>
-      <c r="AL12" t="s">
-        <v>336</v>
-      </c>
-      <c r="AM12" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="AN12" s="1" t="s">
+      <c r="AN12" t="s">
         <v>338</v>
       </c>
-      <c r="AO12" s="1"/>
+      <c r="AO12" s="1" t="s">
+        <v>339</v>
+      </c>
       <c r="AP12" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="AQ12" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="AQ12" s="1"/>
+      <c r="AR12" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="AS12" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B13" t="s">
         <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -4740,10 +4774,10 @@
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -4760,61 +4794,63 @@
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
-      <c r="W13" s="1" t="s">
-        <v>335</v>
-      </c>
+      <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
+      <c r="Y13" s="1" t="s">
+        <v>337</v>
+      </c>
       <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
-      <c r="AC13" s="1"/>
-      <c r="AD13" t="s">
+      <c r="AD13" s="1"/>
+      <c r="AE13" s="1"/>
+      <c r="AF13" t="s">
         <v>44</v>
       </c>
-      <c r="AE13" t="s">
+      <c r="AG13" t="s">
         <v>70</v>
       </c>
-      <c r="AF13">
+      <c r="AH13">
         <v>3</v>
       </c>
-      <c r="AG13" t="s">
-        <v>315</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ13">
+      <c r="AI13" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>318</v>
+      </c>
+      <c r="AL13">
         <v>102400</v>
       </c>
-      <c r="AK13" t="s">
+      <c r="AM13" t="s">
         <v>46</v>
       </c>
-      <c r="AL13" t="s">
-        <v>336</v>
-      </c>
-      <c r="AM13" s="1" t="s">
+      <c r="AN13" t="s">
+        <v>338</v>
+      </c>
+      <c r="AO13" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="AP13" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="AQ13" s="1"/>
+      <c r="AR13" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="AN13" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="AO13" s="1"/>
-      <c r="AP13" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="AQ13" s="1" t="s">
+      <c r="AS13" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
@@ -4823,10 +4859,10 @@
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -4843,61 +4879,63 @@
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
-      <c r="W14" s="1" t="s">
-        <v>345</v>
-      </c>
+      <c r="W14" s="1"/>
       <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
+      <c r="Y14" s="1" t="s">
+        <v>347</v>
+      </c>
       <c r="Z14" s="1"/>
+      <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" t="s">
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" t="s">
         <v>44</v>
       </c>
-      <c r="AE14" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF14">
+      <c r="AG14" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH14">
         <v>2</v>
       </c>
-      <c r="AG14" t="s">
-        <v>315</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ14">
+      <c r="AI14" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>318</v>
+      </c>
+      <c r="AL14">
         <v>51200</v>
       </c>
-      <c r="AK14" t="s">
+      <c r="AM14" t="s">
         <v>46</v>
       </c>
-      <c r="AL14" t="s">
-        <v>346</v>
-      </c>
-      <c r="AM14" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="AN14" s="1" t="s">
+      <c r="AN14" t="s">
         <v>348</v>
       </c>
-      <c r="AO14" s="1"/>
+      <c r="AO14" s="1" t="s">
+        <v>349</v>
+      </c>
       <c r="AP14" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="AQ14" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="AQ14" s="1"/>
+      <c r="AR14" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="AS14" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
@@ -4906,10 +4944,10 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -4926,61 +4964,63 @@
       </c>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
-      <c r="W15" s="1" t="s">
-        <v>352</v>
-      </c>
+      <c r="W15" s="1"/>
       <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
+      <c r="Y15" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="Z15" s="1"/>
+      <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
-      <c r="AC15" s="1"/>
-      <c r="AD15" t="s">
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1"/>
+      <c r="AF15" t="s">
         <v>44</v>
       </c>
-      <c r="AE15" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF15">
+      <c r="AG15" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH15">
         <v>1</v>
       </c>
-      <c r="AG15" t="s">
-        <v>353</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ15">
+      <c r="AI15" t="s">
+        <v>355</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>281</v>
+      </c>
+      <c r="AL15">
         <v>25600</v>
       </c>
-      <c r="AK15" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM15" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="AN15" s="1" t="s">
+      <c r="AM15" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN15" t="s">
         <v>356</v>
       </c>
-      <c r="AO15" s="1"/>
+      <c r="AO15" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="AP15" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ15" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="AQ15" s="1"/>
+      <c r="AR15" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS15" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B16" t="s">
         <v>97</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
@@ -4989,10 +5029,10 @@
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -5009,61 +5049,63 @@
       </c>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
-      <c r="W16" s="1" t="s">
-        <v>352</v>
-      </c>
+      <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
+      <c r="Y16" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" t="s">
+      <c r="AD16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AF16" t="s">
         <v>44</v>
       </c>
-      <c r="AE16" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF16">
+      <c r="AG16" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH16">
         <v>1</v>
       </c>
-      <c r="AG16" t="s">
-        <v>353</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ16">
+      <c r="AI16" t="s">
+        <v>355</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>281</v>
+      </c>
+      <c r="AL16">
         <v>25600</v>
       </c>
-      <c r="AK16" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM16" s="1" t="s">
+      <c r="AM16" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO16" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="AP16" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="AQ16" s="1"/>
+      <c r="AR16" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="AN16" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="AO16" s="1"/>
-      <c r="AP16" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ16" s="1" t="s">
+      <c r="AS16" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B17" t="s">
         <v>97</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D17" t="s">
         <v>27</v>
@@ -5072,10 +5114,10 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -5092,61 +5134,63 @@
       </c>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
-      <c r="W17" s="1" t="s">
-        <v>352</v>
-      </c>
+      <c r="W17" s="1"/>
       <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
+      <c r="Y17" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17" t="s">
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" t="s">
         <v>44</v>
       </c>
-      <c r="AE17" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF17">
+      <c r="AG17" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH17">
         <v>2</v>
       </c>
-      <c r="AG17" t="s">
-        <v>353</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ17">
+      <c r="AI17" t="s">
+        <v>355</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>281</v>
+      </c>
+      <c r="AL17">
         <v>38400</v>
       </c>
-      <c r="AK17" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM17" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="AN17" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="AO17" s="1"/>
+      <c r="AM17" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO17" s="1" t="s">
+        <v>364</v>
+      </c>
       <c r="AP17" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ17" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="AQ17" s="1"/>
+      <c r="AR17" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS17" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B18" t="s">
         <v>97</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
@@ -5155,10 +5199,10 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -5175,61 +5219,63 @@
       </c>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
-      <c r="W18" s="1" t="s">
-        <v>352</v>
-      </c>
+      <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
+      <c r="Y18" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" t="s">
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" t="s">
         <v>44</v>
       </c>
-      <c r="AE18" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF18">
+      <c r="AG18" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH18">
         <v>2</v>
       </c>
-      <c r="AG18" t="s">
-        <v>353</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ18">
+      <c r="AI18" t="s">
+        <v>355</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>281</v>
+      </c>
+      <c r="AL18">
         <v>51200</v>
       </c>
-      <c r="AK18" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL18" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM18" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="AN18" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="AO18" s="1"/>
+      <c r="AM18" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO18" s="1" t="s">
+        <v>367</v>
+      </c>
       <c r="AP18" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ18" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="AQ18" s="1"/>
+      <c r="AR18" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS18" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B19" t="s">
         <v>97</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
@@ -5238,10 +5284,10 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -5258,61 +5304,63 @@
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
-      <c r="W19" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
+      <c r="Y19" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" t="s">
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" t="s">
         <v>44</v>
       </c>
-      <c r="AE19" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF19">
+      <c r="AG19" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH19">
         <v>1</v>
       </c>
-      <c r="AG19" t="s">
-        <v>353</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ19">
+      <c r="AI19" t="s">
+        <v>355</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>281</v>
+      </c>
+      <c r="AL19">
         <v>12800</v>
       </c>
-      <c r="AK19" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM19" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="AN19" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="AO19" s="1"/>
+      <c r="AM19" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO19" s="1" t="s">
+        <v>372</v>
+      </c>
       <c r="AP19" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ19" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="AQ19" s="1"/>
+      <c r="AR19" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS19" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B20" t="s">
         <v>97</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
@@ -5321,10 +5369,10 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -5341,61 +5389,63 @@
       </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
-      <c r="W20" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
+      <c r="Y20" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" t="s">
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" t="s">
         <v>44</v>
       </c>
-      <c r="AE20" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF20">
+      <c r="AG20" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH20">
         <v>1</v>
       </c>
-      <c r="AG20" t="s">
-        <v>373</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ20">
+      <c r="AI20" t="s">
+        <v>375</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>281</v>
+      </c>
+      <c r="AL20">
         <v>12000</v>
       </c>
-      <c r="AK20" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM20" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="AN20" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="AO20" s="1"/>
+      <c r="AM20" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO20" s="1" t="s">
+        <v>376</v>
+      </c>
       <c r="AP20" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ20" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="AQ20" s="1"/>
+      <c r="AR20" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS20" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B21" t="s">
         <v>97</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
@@ -5404,10 +5454,10 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -5424,61 +5474,63 @@
       </c>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
-      <c r="W21" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
+      <c r="Y21" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21" t="s">
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" t="s">
         <v>44</v>
       </c>
-      <c r="AE21" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF21">
+      <c r="AG21" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH21">
         <v>2</v>
       </c>
-      <c r="AG21" t="s">
-        <v>377</v>
-      </c>
-      <c r="AH21" t="s">
-        <v>378</v>
-      </c>
-      <c r="AJ21">
+      <c r="AI21" t="s">
+        <v>379</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>380</v>
+      </c>
+      <c r="AL21">
         <v>12800</v>
       </c>
-      <c r="AK21" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL21" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM21" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="AN21" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="AO21" s="1"/>
+      <c r="AM21" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>381</v>
+      </c>
       <c r="AP21" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ21" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="AQ21" s="1"/>
+      <c r="AR21" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS21" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B22" t="s">
         <v>97</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D22" t="s">
         <v>27</v>
@@ -5487,10 +5539,10 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5507,61 +5559,63 @@
       </c>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
-      <c r="W22" s="1" t="s">
-        <v>383</v>
-      </c>
+      <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
+      <c r="Y22" s="1" t="s">
+        <v>385</v>
+      </c>
       <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
-      <c r="AD22" t="s">
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+      <c r="AF22" t="s">
         <v>44</v>
       </c>
-      <c r="AE22" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF22">
+      <c r="AG22" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH22">
         <v>1</v>
       </c>
-      <c r="AG22" t="s">
-        <v>353</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ22">
+      <c r="AI22" t="s">
+        <v>355</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>281</v>
+      </c>
+      <c r="AL22">
         <v>25600</v>
       </c>
-      <c r="AK22" t="s">
+      <c r="AM22" t="s">
         <v>46</v>
       </c>
-      <c r="AL22" t="s">
-        <v>384</v>
-      </c>
-      <c r="AM22" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="AN22" s="1" t="s">
+      <c r="AN22" t="s">
         <v>386</v>
       </c>
-      <c r="AO22" s="1"/>
+      <c r="AO22" s="1" t="s">
+        <v>387</v>
+      </c>
       <c r="AP22" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="AQ22" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="AQ22" s="1"/>
+      <c r="AR22" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="AS22" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
@@ -5570,10 +5624,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -5590,58 +5644,60 @@
       </c>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
-      <c r="W23" s="1" t="s">
-        <v>389</v>
-      </c>
+      <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
+      <c r="Y23" s="1" t="s">
+        <v>391</v>
+      </c>
       <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
-      <c r="AC23" s="1"/>
-      <c r="AD23" t="s">
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1"/>
+      <c r="AF23" t="s">
         <v>44</v>
       </c>
-      <c r="AE23" t="s">
+      <c r="AG23" t="s">
         <v>45</v>
       </c>
-      <c r="AF23">
+      <c r="AH23">
         <v>1</v>
       </c>
-      <c r="AG23" t="s">
-        <v>390</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>279</v>
-      </c>
-      <c r="AK23" t="s">
+      <c r="AI23" t="s">
+        <v>392</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>281</v>
+      </c>
+      <c r="AM23" t="s">
         <v>46</v>
       </c>
-      <c r="AL23" t="s">
-        <v>317</v>
-      </c>
-      <c r="AM23" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="AN23" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="AO23" s="1"/>
+      <c r="AN23" t="s">
+        <v>319</v>
+      </c>
+      <c r="AO23" s="1" t="s">
+        <v>393</v>
+      </c>
       <c r="AP23" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="AQ23" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="AQ23" s="1"/>
+      <c r="AR23" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="AS23" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
@@ -5650,10 +5706,10 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -5670,61 +5726,63 @@
       </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
-      <c r="W24" s="1" t="s">
-        <v>396</v>
-      </c>
+      <c r="W24" s="1"/>
       <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
+      <c r="Y24" s="1" t="s">
+        <v>398</v>
+      </c>
       <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
-      <c r="AD24" t="s">
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" t="s">
         <v>44</v>
       </c>
-      <c r="AE24" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF24">
+      <c r="AG24" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH24">
         <v>2</v>
       </c>
-      <c r="AG24" t="s">
-        <v>377</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>378</v>
-      </c>
-      <c r="AJ24">
+      <c r="AI24" t="s">
+        <v>379</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>380</v>
+      </c>
+      <c r="AL24">
         <v>12800</v>
       </c>
-      <c r="AK24" t="s">
+      <c r="AM24" t="s">
         <v>46</v>
       </c>
-      <c r="AL24" t="s">
-        <v>317</v>
-      </c>
-      <c r="AM24" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="AN24" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="AO24" s="1"/>
+      <c r="AN24" t="s">
+        <v>319</v>
+      </c>
+      <c r="AO24" s="1" t="s">
+        <v>399</v>
+      </c>
       <c r="AP24" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="AQ24" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="AQ24" s="1"/>
+      <c r="AR24" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="AS24" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B25" t="s">
         <v>97</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
@@ -5733,10 +5791,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -5753,61 +5811,63 @@
       </c>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
-      <c r="W25" s="1" t="s">
-        <v>402</v>
-      </c>
+      <c r="W25" s="1"/>
       <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
+      <c r="Y25" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
-      <c r="AC25" s="1"/>
-      <c r="AD25" t="s">
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+      <c r="AF25" t="s">
         <v>44</v>
       </c>
-      <c r="AE25" t="s">
-        <v>305</v>
-      </c>
-      <c r="AF25">
+      <c r="AG25" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH25">
         <v>1</v>
       </c>
-      <c r="AG25" t="s">
-        <v>377</v>
-      </c>
-      <c r="AH25" t="s">
-        <v>378</v>
-      </c>
-      <c r="AJ25">
+      <c r="AI25" t="s">
+        <v>379</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>380</v>
+      </c>
+      <c r="AL25">
         <v>7200</v>
       </c>
-      <c r="AK25" t="s">
+      <c r="AM25" t="s">
         <v>46</v>
       </c>
-      <c r="AL25" t="s">
-        <v>403</v>
-      </c>
-      <c r="AM25" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="AN25" s="1" t="s">
+      <c r="AN25" t="s">
         <v>405</v>
       </c>
-      <c r="AO25" s="1"/>
+      <c r="AO25" s="1" t="s">
+        <v>406</v>
+      </c>
       <c r="AP25" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="AQ25" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="AQ25" s="1"/>
+      <c r="AR25" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="AS25" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B26" t="s">
         <v>97</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D26" t="s">
         <v>27</v>
@@ -5816,10 +5876,10 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -5836,61 +5896,63 @@
       </c>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
-      <c r="W26" s="1" t="s">
-        <v>402</v>
-      </c>
+      <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
+      <c r="Y26" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
-      <c r="AD26" t="s">
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" t="s">
         <v>44</v>
       </c>
-      <c r="AE26" t="s">
+      <c r="AG26" t="s">
         <v>45</v>
       </c>
-      <c r="AF26">
+      <c r="AH26">
         <v>1</v>
       </c>
-      <c r="AG26" t="s">
+      <c r="AI26" t="s">
+        <v>410</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL26">
+        <v>5600</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>46</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>405</v>
+      </c>
+      <c r="AO26" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="AP26" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="AQ26" s="1"/>
+      <c r="AR26" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="AH26" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ26">
-        <v>5600</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>46</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>403</v>
-      </c>
-      <c r="AM26" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="AN26" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="AO26" s="1"/>
-      <c r="AP26" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="AQ26" s="1" t="s">
+      <c r="AS26" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D27" t="s">
         <v>27</v>
@@ -5899,10 +5961,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -5919,61 +5981,63 @@
       </c>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
-      <c r="W27" s="1" t="s">
-        <v>402</v>
-      </c>
+      <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
+      <c r="Y27" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
-      <c r="AD27" t="s">
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" t="s">
         <v>44</v>
       </c>
-      <c r="AE27" t="s">
+      <c r="AG27" t="s">
         <v>45</v>
       </c>
-      <c r="AF27">
+      <c r="AH27">
         <v>2</v>
       </c>
-      <c r="AG27" t="s">
-        <v>412</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ27">
+      <c r="AI27" t="s">
+        <v>414</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL27">
         <v>9600</v>
       </c>
-      <c r="AK27" t="s">
+      <c r="AM27" t="s">
         <v>46</v>
       </c>
-      <c r="AL27" t="s">
-        <v>403</v>
-      </c>
-      <c r="AM27" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="AN27" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="AO27" s="1"/>
+      <c r="AN27" t="s">
+        <v>405</v>
+      </c>
+      <c r="AO27" s="1" t="s">
+        <v>415</v>
+      </c>
       <c r="AP27" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="AQ27" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="AQ27" s="1"/>
+      <c r="AR27" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="AS27" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B28" t="s">
         <v>97</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D28" t="s">
         <v>27</v>
@@ -5982,10 +6046,10 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -6002,61 +6066,63 @@
       </c>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
-      <c r="W28" s="1" t="s">
-        <v>402</v>
-      </c>
+      <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
+      <c r="Y28" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" t="s">
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" t="s">
         <v>44</v>
       </c>
-      <c r="AE28" t="s">
+      <c r="AG28" t="s">
         <v>45</v>
       </c>
-      <c r="AF28">
+      <c r="AH28">
         <v>2</v>
       </c>
-      <c r="AG28" t="s">
-        <v>416</v>
-      </c>
-      <c r="AH28" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ28">
+      <c r="AI28" t="s">
+        <v>418</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL28">
         <v>4200</v>
       </c>
-      <c r="AK28" t="s">
+      <c r="AM28" t="s">
         <v>46</v>
       </c>
-      <c r="AL28" t="s">
-        <v>403</v>
-      </c>
-      <c r="AM28" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="AN28" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="AO28" s="1"/>
+      <c r="AN28" t="s">
+        <v>405</v>
+      </c>
+      <c r="AO28" s="1" t="s">
+        <v>419</v>
+      </c>
       <c r="AP28" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="AQ28" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="AQ28" s="1"/>
+      <c r="AR28" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="AS28" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B29" t="s">
         <v>97</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D29" t="s">
         <v>27</v>
@@ -6065,10 +6131,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -6085,43 +6151,39 @@
       </c>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
-      <c r="W29" s="1" t="s">
-        <v>402</v>
-      </c>
+      <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
+      <c r="Y29" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
-      <c r="AD29" t="s">
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" t="s">
         <v>44</v>
       </c>
-      <c r="AE29" t="s">
-        <v>420</v>
-      </c>
-      <c r="AF29">
+      <c r="AG29" t="s">
+        <v>422</v>
+      </c>
+      <c r="AH29">
         <v>1</v>
       </c>
-      <c r="AG29" t="s">
-        <v>412</v>
-      </c>
-      <c r="AH29" t="s">
-        <v>378</v>
-      </c>
-      <c r="AJ29">
+      <c r="AI29" t="s">
+        <v>414</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>380</v>
+      </c>
+      <c r="AL29">
         <v>5600</v>
       </c>
-      <c r="AK29" t="s">
+      <c r="AM29" t="s">
         <v>46</v>
       </c>
-      <c r="AL29" t="s">
+      <c r="AN29" t="s">
         <v>177</v>
-      </c>
-      <c r="AM29" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="AN29" s="1" t="s">
-        <v>422</v>
       </c>
       <c r="AO29" s="1" t="s">
         <v>423</v>
@@ -6130,18 +6192,24 @@
         <v>424</v>
       </c>
       <c r="AQ29" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="AR29" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="AS29" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B30" t="s">
         <v>97</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D30" t="s">
         <v>27</v>
@@ -6150,10 +6218,10 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -6170,42 +6238,38 @@
       </c>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
-      <c r="W30" s="1" t="s">
-        <v>427</v>
-      </c>
+      <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
+      <c r="Y30" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
-      <c r="AD30" t="s">
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AF30" t="s">
         <v>44</v>
       </c>
-      <c r="AE30" t="s">
-        <v>428</v>
-      </c>
-      <c r="AF30">
+      <c r="AG30" t="s">
+        <v>430</v>
+      </c>
+      <c r="AH30">
         <v>1</v>
       </c>
-      <c r="AG30" t="s">
-        <v>429</v>
-      </c>
-      <c r="AH30" t="s">
-        <v>378</v>
-      </c>
-      <c r="AJ30">
+      <c r="AI30" t="s">
+        <v>431</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>380</v>
+      </c>
+      <c r="AL30">
         <v>2400</v>
       </c>
-      <c r="AK30" t="s">
-        <v>430</v>
-      </c>
-      <c r="AL30" t="s">
-        <v>431</v>
-      </c>
-      <c r="AM30" s="1" t="s">
+      <c r="AM30" t="s">
         <v>432</v>
       </c>
-      <c r="AN30" s="1" t="s">
+      <c r="AN30" t="s">
         <v>433</v>
       </c>
       <c r="AO30" s="1" t="s">
@@ -6215,18 +6279,24 @@
         <v>435</v>
       </c>
       <c r="AQ30" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="AR30" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="AS30" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B31" t="s">
         <v>97</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D31" t="s">
         <v>27</v>
@@ -6235,10 +6305,10 @@
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -6255,63 +6325,65 @@
       </c>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
-      <c r="W31" s="1" t="s">
-        <v>427</v>
-      </c>
+      <c r="W31" s="1"/>
       <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
+      <c r="Y31" s="1" t="s">
+        <v>429</v>
+      </c>
       <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
-      <c r="AC31" s="1"/>
-      <c r="AD31" t="s">
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" t="s">
         <v>44</v>
       </c>
-      <c r="AE31" t="s">
-        <v>428</v>
-      </c>
-      <c r="AF31">
+      <c r="AG31" t="s">
+        <v>430</v>
+      </c>
+      <c r="AH31">
         <v>1</v>
       </c>
-      <c r="AG31" t="s">
-        <v>408</v>
-      </c>
-      <c r="AH31" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ31">
+      <c r="AI31" t="s">
+        <v>410</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>281</v>
+      </c>
+      <c r="AL31">
         <v>3800</v>
       </c>
-      <c r="AK31" t="s">
-        <v>430</v>
-      </c>
-      <c r="AL31" t="s">
-        <v>431</v>
-      </c>
-      <c r="AM31" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="AN31" s="1" t="s">
-        <v>438</v>
+      <c r="AM31" t="s">
+        <v>432</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>433</v>
       </c>
       <c r="AO31" s="1" t="s">
         <v>439</v>
       </c>
       <c r="AP31" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AQ31" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="AR31" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="AS31" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B32" t="s">
         <v>97</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
@@ -6320,10 +6392,10 @@
         <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -6340,63 +6412,65 @@
       </c>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
-      <c r="W32" s="1" t="s">
-        <v>442</v>
-      </c>
+      <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
+      <c r="Y32" s="1" t="s">
+        <v>444</v>
+      </c>
       <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
-      <c r="AD32" t="s">
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" t="s">
         <v>44</v>
       </c>
-      <c r="AE32" t="s">
-        <v>443</v>
-      </c>
-      <c r="AF32">
+      <c r="AG32" t="s">
+        <v>445</v>
+      </c>
+      <c r="AH32">
         <v>1</v>
       </c>
-      <c r="AG32" t="s">
-        <v>408</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ32">
+      <c r="AI32" t="s">
+        <v>410</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL32">
         <v>3600</v>
       </c>
-      <c r="AK32" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM32" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="AN32" s="1" t="s">
-        <v>445</v>
+      <c r="AM32" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>356</v>
       </c>
       <c r="AO32" s="1" t="s">
         <v>446</v>
       </c>
       <c r="AP32" s="1" t="s">
-        <v>357</v>
+        <v>447</v>
       </c>
       <c r="AQ32" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="AR32" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS32" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
@@ -6405,10 +6479,10 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -6425,61 +6499,63 @@
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
-      <c r="W33" s="1" t="s">
-        <v>442</v>
-      </c>
+      <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
+      <c r="Y33" s="1" t="s">
+        <v>444</v>
+      </c>
       <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
-      <c r="AC33" s="1"/>
-      <c r="AD33" t="s">
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" t="s">
         <v>44</v>
       </c>
-      <c r="AE33" t="s">
-        <v>443</v>
-      </c>
-      <c r="AF33">
+      <c r="AG33" t="s">
+        <v>445</v>
+      </c>
+      <c r="AH33">
         <v>1</v>
       </c>
-      <c r="AG33" t="s">
-        <v>448</v>
-      </c>
-      <c r="AH33" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ33">
+      <c r="AI33" t="s">
+        <v>450</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL33">
         <v>2160</v>
       </c>
-      <c r="AK33" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL33" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM33" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="AN33" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="AO33" s="1"/>
+      <c r="AM33" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO33" s="1" t="s">
+        <v>451</v>
+      </c>
       <c r="AP33" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ33" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="AQ33" s="1"/>
+      <c r="AR33" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS33" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B34" t="s">
         <v>97</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -6488,10 +6564,10 @@
         <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -6508,61 +6584,63 @@
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
-      <c r="W34" s="1" t="s">
-        <v>442</v>
-      </c>
+      <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
+      <c r="Y34" s="1" t="s">
+        <v>444</v>
+      </c>
       <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
-      <c r="AC34" s="1"/>
-      <c r="AD34" t="s">
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" t="s">
         <v>44</v>
       </c>
-      <c r="AE34" t="s">
-        <v>443</v>
-      </c>
-      <c r="AF34">
+      <c r="AG34" t="s">
+        <v>445</v>
+      </c>
+      <c r="AH34">
         <v>1</v>
       </c>
-      <c r="AG34" t="s">
-        <v>448</v>
-      </c>
-      <c r="AH34" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ34">
+      <c r="AI34" t="s">
+        <v>450</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL34">
         <v>2160</v>
       </c>
-      <c r="AK34" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL34" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM34" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="AN34" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="AO34" s="1"/>
+      <c r="AM34" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO34" s="1" t="s">
+        <v>454</v>
+      </c>
       <c r="AP34" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="AQ34" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="AQ34" s="1"/>
+      <c r="AR34" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="AS34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B35" t="s">
         <v>97</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -6571,10 +6649,10 @@
         <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -6591,61 +6669,63 @@
       </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
-      <c r="W35" s="1" t="s">
-        <v>442</v>
-      </c>
+      <c r="W35" s="1"/>
       <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
+      <c r="Y35" s="1" t="s">
+        <v>444</v>
+      </c>
       <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
-      <c r="AD35" t="s">
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" t="s">
         <v>44</v>
       </c>
-      <c r="AE35" t="s">
-        <v>443</v>
-      </c>
-      <c r="AF35">
+      <c r="AG35" t="s">
+        <v>445</v>
+      </c>
+      <c r="AH35">
         <v>1</v>
       </c>
-      <c r="AG35" t="s">
-        <v>408</v>
-      </c>
-      <c r="AH35" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ35">
+      <c r="AI35" t="s">
+        <v>410</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL35">
         <v>3600</v>
       </c>
-      <c r="AK35" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL35" t="s">
-        <v>307</v>
-      </c>
-      <c r="AM35" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="AN35" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="AO35" s="1"/>
+      <c r="AM35" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>309</v>
+      </c>
+      <c r="AO35" s="1" t="s">
+        <v>458</v>
+      </c>
       <c r="AP35" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="AQ35" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="AQ35" s="1"/>
+      <c r="AR35" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AS35" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D36" t="s">
         <v>27</v>
@@ -6654,10 +6734,10 @@
         <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -6674,61 +6754,63 @@
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
-      <c r="W36" s="1" t="s">
-        <v>442</v>
-      </c>
+      <c r="W36" s="1"/>
       <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
+      <c r="Y36" s="1" t="s">
+        <v>444</v>
+      </c>
       <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
-      <c r="AD36" t="s">
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" t="s">
         <v>44</v>
       </c>
-      <c r="AE36" t="s">
-        <v>443</v>
-      </c>
-      <c r="AF36">
+      <c r="AG36" t="s">
+        <v>445</v>
+      </c>
+      <c r="AH36">
         <v>1</v>
       </c>
-      <c r="AG36" t="s">
-        <v>448</v>
-      </c>
-      <c r="AH36" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ36">
+      <c r="AI36" t="s">
+        <v>450</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL36">
         <v>2160</v>
       </c>
-      <c r="AK36" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL36" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM36" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="AN36" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="AO36" s="1"/>
+      <c r="AM36" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO36" s="1" t="s">
+        <v>461</v>
+      </c>
       <c r="AP36" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ36" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="AQ36" s="1"/>
+      <c r="AR36" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS36" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B37" t="s">
         <v>97</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D37" t="s">
         <v>27</v>
@@ -6737,10 +6819,10 @@
         <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -6757,61 +6839,63 @@
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
-      <c r="W37" s="1" t="s">
-        <v>442</v>
-      </c>
+      <c r="W37" s="1"/>
       <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
+      <c r="Y37" s="1" t="s">
+        <v>444</v>
+      </c>
       <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
-      <c r="AD37" t="s">
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AF37" t="s">
         <v>44</v>
       </c>
-      <c r="AE37" t="s">
+      <c r="AG37" t="s">
         <v>38</v>
       </c>
-      <c r="AF37">
+      <c r="AH37">
         <v>1</v>
       </c>
-      <c r="AG37" t="s">
-        <v>462</v>
-      </c>
-      <c r="AH37" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ37">
+      <c r="AI37" t="s">
+        <v>464</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL37">
         <v>696</v>
       </c>
-      <c r="AK37" t="s">
+      <c r="AM37" t="s">
         <v>46</v>
       </c>
-      <c r="AL37" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM37" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="AN37" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="AO37" s="1"/>
+      <c r="AN37" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO37" s="1" t="s">
+        <v>465</v>
+      </c>
       <c r="AP37" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ37" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="AQ37" s="1"/>
+      <c r="AR37" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS37" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B38" t="s">
         <v>97</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D38" t="s">
         <v>27</v>
@@ -6820,10 +6904,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -6840,61 +6924,63 @@
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
-      <c r="W38" s="1" t="s">
-        <v>442</v>
-      </c>
+      <c r="W38" s="1"/>
       <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
+      <c r="Y38" s="1" t="s">
+        <v>444</v>
+      </c>
       <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
-      <c r="AD38" t="s">
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1"/>
+      <c r="AF38" t="s">
         <v>44</v>
       </c>
-      <c r="AE38" t="s">
+      <c r="AG38" t="s">
         <v>38</v>
       </c>
-      <c r="AF38">
+      <c r="AH38">
         <v>1</v>
       </c>
-      <c r="AG38" t="s">
-        <v>466</v>
-      </c>
-      <c r="AH38" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ38">
+      <c r="AI38" t="s">
+        <v>468</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL38">
         <v>696</v>
       </c>
-      <c r="AK38" t="s">
+      <c r="AM38" t="s">
         <v>46</v>
       </c>
-      <c r="AL38" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM38" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="AN38" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="AO38" s="1"/>
+      <c r="AN38" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO38" s="1" t="s">
+        <v>469</v>
+      </c>
       <c r="AP38" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="AQ38" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="AQ38" s="1"/>
+      <c r="AR38" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="AS38" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B39" t="s">
         <v>97</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D39" t="s">
         <v>27</v>
@@ -6903,10 +6989,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -6923,61 +7009,63 @@
       </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
-      <c r="W39" s="1" t="s">
-        <v>472</v>
-      </c>
+      <c r="W39" s="1"/>
       <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
+      <c r="Y39" s="1" t="s">
+        <v>474</v>
+      </c>
       <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
-      <c r="AC39" s="1"/>
-      <c r="AD39" t="s">
+      <c r="AD39" s="1"/>
+      <c r="AE39" s="1"/>
+      <c r="AF39" t="s">
         <v>44</v>
       </c>
-      <c r="AE39" t="s">
-        <v>305</v>
-      </c>
-      <c r="AF39">
+      <c r="AG39" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH39">
         <v>1</v>
       </c>
-      <c r="AG39" t="s">
-        <v>377</v>
-      </c>
-      <c r="AH39" t="s">
-        <v>378</v>
-      </c>
-      <c r="AJ39">
+      <c r="AI39" t="s">
+        <v>379</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>380</v>
+      </c>
+      <c r="AL39">
         <v>7200</v>
       </c>
-      <c r="AK39" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL39" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM39" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="AN39" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="AO39" s="1"/>
+      <c r="AM39" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO39" s="1" t="s">
+        <v>475</v>
+      </c>
       <c r="AP39" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ39" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="AQ39" s="1"/>
+      <c r="AR39" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS39" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D40" t="s">
         <v>27</v>
@@ -6986,10 +7074,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -7006,61 +7094,63 @@
       </c>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
-      <c r="W40" s="1" t="s">
-        <v>472</v>
-      </c>
+      <c r="W40" s="1"/>
       <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
+      <c r="Y40" s="1" t="s">
+        <v>474</v>
+      </c>
       <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
-      <c r="AC40" s="1"/>
-      <c r="AD40" t="s">
+      <c r="AD40" s="1"/>
+      <c r="AE40" s="1"/>
+      <c r="AF40" t="s">
         <v>44</v>
       </c>
-      <c r="AE40" t="s">
-        <v>305</v>
-      </c>
-      <c r="AF40">
+      <c r="AG40" t="s">
+        <v>307</v>
+      </c>
+      <c r="AH40">
         <v>1</v>
       </c>
-      <c r="AG40" t="s">
-        <v>377</v>
-      </c>
-      <c r="AH40" t="s">
-        <v>378</v>
-      </c>
-      <c r="AJ40">
+      <c r="AI40" t="s">
+        <v>379</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>380</v>
+      </c>
+      <c r="AL40">
         <v>7200</v>
       </c>
-      <c r="AK40" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL40" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM40" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="AN40" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="AO40" s="1"/>
+      <c r="AM40" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO40" s="1" t="s">
+        <v>478</v>
+      </c>
       <c r="AP40" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ40" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="AQ40" s="1"/>
+      <c r="AR40" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS40" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B41" t="s">
         <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D41" t="s">
         <v>27</v>
@@ -7069,10 +7159,10 @@
         <v>28</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -7089,61 +7179,63 @@
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
-      <c r="W41" s="1" t="s">
-        <v>472</v>
-      </c>
+      <c r="W41" s="1"/>
       <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
+      <c r="Y41" s="1" t="s">
+        <v>474</v>
+      </c>
       <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
-      <c r="AC41" s="1"/>
-      <c r="AD41" t="s">
+      <c r="AD41" s="1"/>
+      <c r="AE41" s="1"/>
+      <c r="AF41" t="s">
         <v>44</v>
       </c>
-      <c r="AE41" t="s">
+      <c r="AG41" t="s">
         <v>45</v>
       </c>
-      <c r="AF41">
+      <c r="AH41">
         <v>2</v>
       </c>
-      <c r="AG41" t="s">
-        <v>479</v>
-      </c>
-      <c r="AH41" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ41">
+      <c r="AI41" t="s">
+        <v>481</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL41">
         <v>7200</v>
       </c>
-      <c r="AK41" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL41" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM41" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="AN41" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="AO41" s="1"/>
+      <c r="AM41" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO41" s="1" t="s">
+        <v>482</v>
+      </c>
       <c r="AP41" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ41" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="AQ41" s="1"/>
+      <c r="AR41" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS41" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B42" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D42" t="s">
         <v>27</v>
@@ -7152,10 +7244,10 @@
         <v>28</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -7172,61 +7264,63 @@
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
-      <c r="W42" s="1" t="s">
-        <v>472</v>
-      </c>
+      <c r="W42" s="1"/>
       <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
+      <c r="Y42" s="1" t="s">
+        <v>474</v>
+      </c>
       <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
-      <c r="AD42" t="s">
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" t="s">
         <v>44</v>
       </c>
-      <c r="AE42" t="s">
+      <c r="AG42" t="s">
         <v>45</v>
       </c>
-      <c r="AF42">
+      <c r="AH42">
         <v>1.2</v>
       </c>
-      <c r="AG42" t="s">
-        <v>479</v>
-      </c>
-      <c r="AH42" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ42">
+      <c r="AI42" t="s">
+        <v>481</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL42">
         <v>4800</v>
       </c>
-      <c r="AK42" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL42" t="s">
-        <v>354</v>
-      </c>
-      <c r="AM42" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="AN42" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="AO42" s="1"/>
+      <c r="AM42" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>356</v>
+      </c>
+      <c r="AO42" s="1" t="s">
+        <v>485</v>
+      </c>
       <c r="AP42" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ42" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="AQ42" s="1"/>
+      <c r="AR42" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS42" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B43" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D43" t="s">
         <v>27</v>
@@ -7235,10 +7329,10 @@
         <v>28</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -7255,61 +7349,63 @@
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
-      <c r="W43" s="1" t="s">
-        <v>472</v>
-      </c>
+      <c r="W43" s="1"/>
       <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
+      <c r="Y43" s="1" t="s">
+        <v>474</v>
+      </c>
       <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
-      <c r="AC43" s="1"/>
-      <c r="AD43" t="s">
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AF43" t="s">
         <v>44</v>
       </c>
-      <c r="AE43" t="s">
+      <c r="AG43" t="s">
         <v>45</v>
       </c>
-      <c r="AF43">
+      <c r="AH43">
         <v>2</v>
       </c>
-      <c r="AG43" t="s">
-        <v>416</v>
-      </c>
-      <c r="AH43" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ43">
+      <c r="AI43" t="s">
+        <v>418</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL43">
         <v>4320</v>
       </c>
-      <c r="AK43" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL43" t="s">
-        <v>292</v>
-      </c>
-      <c r="AM43" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="AN43" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="AO43" s="1"/>
+      <c r="AM43" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>294</v>
+      </c>
+      <c r="AO43" s="1" t="s">
+        <v>488</v>
+      </c>
       <c r="AP43" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="AQ43" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="AQ43" s="1"/>
+      <c r="AR43" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="AS43" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B44" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
@@ -7318,10 +7414,10 @@
         <v>28</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -7338,61 +7434,63 @@
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
-      <c r="W44" s="1" t="s">
-        <v>490</v>
-      </c>
+      <c r="W44" s="1"/>
       <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
+      <c r="Y44" s="1" t="s">
+        <v>492</v>
+      </c>
       <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
-      <c r="AC44" s="1"/>
-      <c r="AD44" t="s">
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" t="s">
         <v>44</v>
       </c>
-      <c r="AE44" t="s">
+      <c r="AG44" t="s">
         <v>38</v>
       </c>
-      <c r="AF44">
+      <c r="AH44">
         <v>1</v>
       </c>
-      <c r="AG44" t="s">
-        <v>466</v>
-      </c>
-      <c r="AH44" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ44">
+      <c r="AI44" t="s">
+        <v>468</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL44">
         <v>696</v>
       </c>
-      <c r="AK44" t="s">
+      <c r="AM44" t="s">
         <v>46</v>
       </c>
-      <c r="AL44" t="s">
-        <v>491</v>
-      </c>
-      <c r="AM44" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="AN44" s="1" t="s">
+      <c r="AN44" t="s">
         <v>493</v>
       </c>
-      <c r="AO44" s="1"/>
+      <c r="AO44" s="1" t="s">
+        <v>494</v>
+      </c>
       <c r="AP44" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="AQ44" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="AQ44" s="1"/>
+      <c r="AR44" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="AS44" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B45" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
@@ -7401,10 +7499,10 @@
         <v>28</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -7415,76 +7513,78 @@
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q45" s="1"/>
       <c r="S45" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="T45" t="s">
         <v>108</v>
       </c>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
-      <c r="W45" s="1" t="s">
-        <v>500</v>
-      </c>
+      <c r="W45" s="1"/>
       <c r="X45" s="1"/>
-      <c r="Y45" s="1"/>
+      <c r="Y45" s="1" t="s">
+        <v>502</v>
+      </c>
       <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
-      <c r="AC45" s="1"/>
-      <c r="AD45" t="s">
+      <c r="AD45" s="1"/>
+      <c r="AE45" s="1"/>
+      <c r="AF45" t="s">
         <v>44</v>
       </c>
-      <c r="AE45" t="s">
+      <c r="AG45" t="s">
         <v>70</v>
       </c>
-      <c r="AF45">
+      <c r="AH45">
         <v>2</v>
       </c>
-      <c r="AG45" t="s">
-        <v>377</v>
-      </c>
-      <c r="AH45" t="s">
-        <v>378</v>
-      </c>
-      <c r="AJ45">
+      <c r="AI45" t="s">
+        <v>379</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>380</v>
+      </c>
+      <c r="AL45">
         <v>12800</v>
       </c>
-      <c r="AK45" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL45" t="s">
-        <v>317</v>
-      </c>
-      <c r="AM45" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="AN45" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="AO45" s="1"/>
+      <c r="AM45" t="s">
+        <v>293</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>319</v>
+      </c>
+      <c r="AO45" s="1" t="s">
+        <v>503</v>
+      </c>
       <c r="AP45" s="1" t="s">
-        <v>399</v>
+        <v>504</v>
       </c>
       <c r="AQ45" s="1"/>
-    </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AR45" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="AS45" s="1"/>
+    </row>
+    <row r="46" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B46" t="s">
         <v>97</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D46" t="s">
         <v>27</v>
@@ -7493,10 +7593,10 @@
         <v>28</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -7513,61 +7613,63 @@
       </c>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
-      <c r="W46" s="1" t="s">
-        <v>505</v>
-      </c>
+      <c r="W46" s="1"/>
       <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
+      <c r="Y46" s="1" t="s">
+        <v>507</v>
+      </c>
       <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
-      <c r="AC46" s="1"/>
-      <c r="AD46" t="s">
+      <c r="AD46" s="1"/>
+      <c r="AE46" s="1"/>
+      <c r="AF46" t="s">
         <v>44</v>
       </c>
-      <c r="AE46" t="s">
-        <v>506</v>
-      </c>
-      <c r="AF46">
+      <c r="AG46" t="s">
+        <v>508</v>
+      </c>
+      <c r="AH46">
         <v>1</v>
       </c>
-      <c r="AG46" t="s">
-        <v>408</v>
-      </c>
-      <c r="AH46" t="s">
-        <v>377</v>
-      </c>
-      <c r="AJ46">
+      <c r="AI46" t="s">
+        <v>410</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL46">
         <v>3600</v>
       </c>
-      <c r="AK46" t="s">
+      <c r="AM46" t="s">
         <v>46</v>
       </c>
-      <c r="AL46" t="s">
+      <c r="AN46" t="s">
         <v>152</v>
       </c>
-      <c r="AM46" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="AN46" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="AO46" s="1"/>
+      <c r="AO46" s="1" t="s">
+        <v>509</v>
+      </c>
       <c r="AP46" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="AQ46" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="AQ46" s="1"/>
+      <c r="AR46" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="AS46" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B47" t="s">
         <v>97</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D47" t="s">
         <v>27</v>
@@ -7576,10 +7678,10 @@
         <v>28</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -7599,54 +7701,56 @@
       </c>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
-      <c r="W47" s="1" t="s">
-        <v>511</v>
-      </c>
+      <c r="W47" s="1"/>
       <c r="X47" s="1"/>
-      <c r="Y47" s="1"/>
+      <c r="Y47" s="1" t="s">
+        <v>513</v>
+      </c>
       <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
-      <c r="AC47" s="1"/>
-      <c r="AD47" t="s">
+      <c r="AD47" s="1"/>
+      <c r="AE47" s="1"/>
+      <c r="AF47" t="s">
         <v>44</v>
       </c>
-      <c r="AE47" t="s">
+      <c r="AG47" t="s">
         <v>38</v>
       </c>
-      <c r="AF47">
+      <c r="AH47">
         <v>1</v>
       </c>
-      <c r="AG47" t="s">
-        <v>512</v>
-      </c>
-      <c r="AH47" t="s">
-        <v>512</v>
-      </c>
-      <c r="AJ47">
+      <c r="AI47" t="s">
+        <v>514</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>514</v>
+      </c>
+      <c r="AL47">
         <v>960</v>
       </c>
-      <c r="AK47" t="s">
+      <c r="AM47" t="s">
         <v>46</v>
       </c>
-      <c r="AM47" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="AN47" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="AO47" s="1"/>
-      <c r="AP47" s="1"/>
+      <c r="AO47" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="AP47" s="1" t="s">
+        <v>516</v>
+      </c>
       <c r="AQ47" s="1"/>
-    </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AR47" s="1"/>
+      <c r="AS47" s="1"/>
+    </row>
+    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B48" t="s">
         <v>97</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D48" t="s">
         <v>27</v>
@@ -7655,10 +7759,10 @@
         <v>28</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -7678,54 +7782,56 @@
       </c>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
-      <c r="W48" s="1" t="s">
-        <v>511</v>
-      </c>
+      <c r="W48" s="1"/>
       <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
+      <c r="Y48" s="1" t="s">
+        <v>513</v>
+      </c>
       <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
-      <c r="AC48" s="1"/>
-      <c r="AD48" t="s">
+      <c r="AD48" s="1"/>
+      <c r="AE48" s="1"/>
+      <c r="AF48" t="s">
         <v>44</v>
       </c>
-      <c r="AE48" t="s">
+      <c r="AG48" t="s">
         <v>38</v>
       </c>
-      <c r="AF48">
+      <c r="AH48">
         <v>1</v>
       </c>
-      <c r="AG48" t="s">
-        <v>512</v>
-      </c>
-      <c r="AH48" t="s">
-        <v>512</v>
-      </c>
-      <c r="AJ48">
+      <c r="AI48" t="s">
+        <v>514</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>514</v>
+      </c>
+      <c r="AL48">
         <v>480</v>
       </c>
-      <c r="AK48" t="s">
+      <c r="AM48" t="s">
         <v>46</v>
       </c>
-      <c r="AM48" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="AN48" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="AO48" s="1"/>
-      <c r="AP48" s="1"/>
+      <c r="AO48" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="AP48" s="1" t="s">
+        <v>519</v>
+      </c>
       <c r="AQ48" s="1"/>
-    </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="AR48" s="1"/>
+      <c r="AS48" s="1"/>
+    </row>
+    <row r="49" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B49" t="s">
         <v>97</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D49" t="s">
         <v>27</v>
@@ -7734,10 +7840,10 @@
         <v>28</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -7754,64 +7860,66 @@
       </c>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
-      <c r="W49" s="1" t="s">
-        <v>521</v>
-      </c>
+      <c r="W49" s="1"/>
       <c r="X49" s="1"/>
-      <c r="Y49" s="1"/>
+      <c r="Y49" s="1" t="s">
+        <v>523</v>
+      </c>
       <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
-      <c r="AC49" s="1"/>
-      <c r="AD49" t="s">
+      <c r="AD49" s="1"/>
+      <c r="AE49" s="1"/>
+      <c r="AF49" t="s">
         <v>69</v>
       </c>
-      <c r="AE49" t="s">
+      <c r="AG49" t="s">
         <v>143</v>
       </c>
-      <c r="AF49">
+      <c r="AH49">
         <v>9</v>
       </c>
-      <c r="AG49" t="s">
-        <v>522</v>
-      </c>
-      <c r="AH49" t="s">
-        <v>523</v>
-      </c>
-      <c r="AI49">
+      <c r="AI49" t="s">
+        <v>524</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>525</v>
+      </c>
+      <c r="AK49">
         <v>4</v>
       </c>
-      <c r="AJ49">
+      <c r="AL49">
         <v>12000</v>
       </c>
-      <c r="AK49" t="s">
+      <c r="AM49" t="s">
         <v>92</v>
       </c>
-      <c r="AL49" t="s">
-        <v>524</v>
-      </c>
-      <c r="AM49" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="AN49" s="1" t="s">
+      <c r="AN49" t="s">
         <v>526</v>
       </c>
-      <c r="AO49" s="1"/>
+      <c r="AO49" s="1" t="s">
+        <v>527</v>
+      </c>
       <c r="AP49" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="AQ49" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="AQ49" s="1"/>
+      <c r="AR49" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="AS49" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B50" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
@@ -7820,10 +7928,10 @@
         <v>28</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -7840,64 +7948,66 @@
       </c>
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
-      <c r="W50" s="1" t="s">
-        <v>530</v>
-      </c>
+      <c r="W50" s="1"/>
       <c r="X50" s="1"/>
-      <c r="Y50" s="1"/>
+      <c r="Y50" s="1" t="s">
+        <v>532</v>
+      </c>
       <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
-      <c r="AC50" s="1"/>
-      <c r="AD50" t="s">
+      <c r="AD50" s="1"/>
+      <c r="AE50" s="1"/>
+      <c r="AF50" t="s">
         <v>69</v>
       </c>
-      <c r="AE50" t="s">
+      <c r="AG50" t="s">
         <v>143</v>
       </c>
-      <c r="AF50">
+      <c r="AH50">
         <v>14</v>
       </c>
-      <c r="AG50" t="s">
-        <v>522</v>
-      </c>
-      <c r="AH50" t="s">
-        <v>523</v>
-      </c>
-      <c r="AI50">
+      <c r="AI50" t="s">
+        <v>524</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>525</v>
+      </c>
+      <c r="AK50">
         <v>8</v>
       </c>
-      <c r="AJ50">
+      <c r="AL50">
         <v>24000</v>
       </c>
-      <c r="AK50" t="s">
+      <c r="AM50" t="s">
         <v>92</v>
       </c>
-      <c r="AL50" t="s">
-        <v>524</v>
-      </c>
-      <c r="AM50" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="AN50" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="AO50" s="1"/>
+      <c r="AN50" t="s">
+        <v>526</v>
+      </c>
+      <c r="AO50" s="1" t="s">
+        <v>533</v>
+      </c>
       <c r="AP50" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="AQ50" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="AQ50" s="1"/>
+      <c r="AR50" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="AS50" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B51" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
@@ -7906,10 +8016,10 @@
         <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -7926,64 +8036,66 @@
       </c>
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
-      <c r="W51" s="1" t="s">
-        <v>535</v>
-      </c>
+      <c r="W51" s="1"/>
       <c r="X51" s="1"/>
-      <c r="Y51" s="1"/>
+      <c r="Y51" s="1" t="s">
+        <v>537</v>
+      </c>
       <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
-      <c r="AC51" s="1"/>
-      <c r="AD51" t="s">
+      <c r="AD51" s="1"/>
+      <c r="AE51" s="1"/>
+      <c r="AF51" t="s">
         <v>69</v>
       </c>
-      <c r="AE51" t="s">
+      <c r="AG51" t="s">
         <v>143</v>
       </c>
-      <c r="AF51">
+      <c r="AH51">
         <v>26</v>
       </c>
-      <c r="AG51" t="s">
-        <v>522</v>
-      </c>
-      <c r="AH51" t="s">
-        <v>523</v>
-      </c>
-      <c r="AI51">
+      <c r="AI51" t="s">
+        <v>524</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>525</v>
+      </c>
+      <c r="AK51">
         <v>16</v>
       </c>
-      <c r="AJ51">
+      <c r="AL51">
         <v>48000</v>
       </c>
-      <c r="AK51" t="s">
+      <c r="AM51" t="s">
         <v>92</v>
       </c>
-      <c r="AL51" t="s">
-        <v>524</v>
-      </c>
-      <c r="AM51" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="AN51" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="AO51" s="1"/>
+      <c r="AN51" t="s">
+        <v>526</v>
+      </c>
+      <c r="AO51" s="1" t="s">
+        <v>538</v>
+      </c>
       <c r="AP51" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="AQ51" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="AQ51" s="1"/>
+      <c r="AR51" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="AS51" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B52" t="s">
         <v>97</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D52" t="s">
         <v>27</v>
@@ -7992,10 +8104,10 @@
         <v>28</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -8012,58 +8124,60 @@
       </c>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
-      <c r="W52" s="1" t="s">
-        <v>541</v>
-      </c>
+      <c r="W52" s="1"/>
       <c r="X52" s="1"/>
-      <c r="Y52" s="1"/>
+      <c r="Y52" s="1" t="s">
+        <v>543</v>
+      </c>
       <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
-      <c r="AC52" s="1"/>
-      <c r="AD52" t="s">
+      <c r="AD52" s="1"/>
+      <c r="AE52" s="1"/>
+      <c r="AF52" t="s">
         <v>44</v>
       </c>
-      <c r="AE52" t="s">
+      <c r="AG52" t="s">
         <v>137</v>
       </c>
-      <c r="AF52">
+      <c r="AH52">
         <v>2</v>
       </c>
-      <c r="AG52" t="s">
-        <v>542</v>
-      </c>
-      <c r="AH52" t="s">
-        <v>523</v>
-      </c>
-      <c r="AK52" t="s">
+      <c r="AI52" t="s">
+        <v>544</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>525</v>
+      </c>
+      <c r="AM52" t="s">
         <v>92</v>
       </c>
-      <c r="AL52" t="s">
-        <v>543</v>
-      </c>
-      <c r="AM52" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="AN52" s="1" t="s">
+      <c r="AN52" t="s">
         <v>545</v>
       </c>
-      <c r="AO52" s="1"/>
+      <c r="AO52" s="1" t="s">
+        <v>546</v>
+      </c>
       <c r="AP52" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="AQ52" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="AQ52" s="1"/>
+      <c r="AR52" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="AS52" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B53" t="s">
         <v>97</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D53" t="s">
         <v>27</v>
@@ -8072,10 +8186,10 @@
         <v>28</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -8092,58 +8206,60 @@
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
-      <c r="W53" s="1" t="s">
-        <v>549</v>
-      </c>
+      <c r="W53" s="1"/>
       <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
+      <c r="Y53" s="1" t="s">
+        <v>551</v>
+      </c>
       <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
-      <c r="AC53" s="1"/>
-      <c r="AD53" t="s">
+      <c r="AD53" s="1"/>
+      <c r="AE53" s="1"/>
+      <c r="AF53" t="s">
         <v>44</v>
       </c>
-      <c r="AE53" t="s">
+      <c r="AG53" t="s">
         <v>137</v>
       </c>
-      <c r="AF53">
+      <c r="AH53">
         <v>2</v>
       </c>
-      <c r="AG53" t="s">
-        <v>550</v>
-      </c>
-      <c r="AH53" t="s">
-        <v>551</v>
-      </c>
-      <c r="AK53" t="s">
+      <c r="AI53" t="s">
+        <v>552</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>553</v>
+      </c>
+      <c r="AM53" t="s">
         <v>92</v>
       </c>
-      <c r="AL53" t="s">
-        <v>552</v>
-      </c>
-      <c r="AM53" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="AN53" s="1" t="s">
+      <c r="AN53" t="s">
         <v>554</v>
       </c>
-      <c r="AO53" s="1"/>
+      <c r="AO53" s="1" t="s">
+        <v>555</v>
+      </c>
       <c r="AP53" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="AQ53" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="AQ53" s="1"/>
+      <c r="AR53" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="AS53" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B54" t="s">
         <v>97</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D54" t="s">
         <v>27</v>
@@ -8152,10 +8268,10 @@
         <v>28</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -8172,58 +8288,60 @@
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
-      <c r="W54" s="1" t="s">
-        <v>559</v>
-      </c>
+      <c r="W54" s="1"/>
       <c r="X54" s="1"/>
-      <c r="Y54" s="1"/>
+      <c r="Y54" s="1" t="s">
+        <v>561</v>
+      </c>
       <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
-      <c r="AC54" s="1"/>
-      <c r="AD54" t="s">
+      <c r="AD54" s="1"/>
+      <c r="AE54" s="1"/>
+      <c r="AF54" t="s">
         <v>44</v>
       </c>
-      <c r="AE54" t="s">
+      <c r="AG54" t="s">
         <v>137</v>
       </c>
-      <c r="AF54">
+      <c r="AH54">
         <v>1</v>
       </c>
-      <c r="AG54" t="s">
-        <v>542</v>
-      </c>
-      <c r="AH54" t="s">
-        <v>523</v>
-      </c>
-      <c r="AK54" t="s">
+      <c r="AI54" t="s">
+        <v>544</v>
+      </c>
+      <c r="AJ54" t="s">
+        <v>525</v>
+      </c>
+      <c r="AM54" t="s">
         <v>92</v>
       </c>
-      <c r="AL54" t="s">
-        <v>543</v>
-      </c>
-      <c r="AM54" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="AN54" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="AO54" s="1"/>
+      <c r="AN54" t="s">
+        <v>545</v>
+      </c>
+      <c r="AO54" s="1" t="s">
+        <v>562</v>
+      </c>
       <c r="AP54" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="AQ54" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="AQ54" s="1"/>
+      <c r="AR54" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="AS54" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B55" t="s">
         <v>97</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -8232,10 +8350,10 @@
         <v>28</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -8252,58 +8370,60 @@
       </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
-      <c r="W55" s="1" t="s">
-        <v>564</v>
-      </c>
+      <c r="W55" s="1"/>
       <c r="X55" s="1"/>
-      <c r="Y55" s="1"/>
+      <c r="Y55" s="1" t="s">
+        <v>566</v>
+      </c>
       <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
-      <c r="AC55" s="1"/>
-      <c r="AD55" t="s">
+      <c r="AD55" s="1"/>
+      <c r="AE55" s="1"/>
+      <c r="AF55" t="s">
         <v>44</v>
       </c>
-      <c r="AE55" t="s">
+      <c r="AG55" t="s">
         <v>137</v>
       </c>
-      <c r="AF55">
+      <c r="AH55">
         <v>1</v>
       </c>
-      <c r="AG55" t="s">
-        <v>542</v>
-      </c>
-      <c r="AH55" t="s">
-        <v>523</v>
-      </c>
-      <c r="AK55" t="s">
+      <c r="AI55" t="s">
+        <v>544</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>525</v>
+      </c>
+      <c r="AM55" t="s">
         <v>92</v>
       </c>
-      <c r="AL55" t="s">
-        <v>543</v>
-      </c>
-      <c r="AM55" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="AN55" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="AO55" s="1"/>
+      <c r="AN55" t="s">
+        <v>545</v>
+      </c>
+      <c r="AO55" s="1" t="s">
+        <v>567</v>
+      </c>
       <c r="AP55" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="AQ55" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="AQ55" s="1"/>
+      <c r="AR55" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="AS55" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B56" t="s">
         <v>97</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -8312,10 +8432,10 @@
         <v>28</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -8332,58 +8452,60 @@
       </c>
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
-      <c r="W56" s="1" t="s">
-        <v>569</v>
-      </c>
+      <c r="W56" s="1"/>
       <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
+      <c r="Y56" s="1" t="s">
+        <v>571</v>
+      </c>
       <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
-      <c r="AC56" s="1"/>
-      <c r="AD56" t="s">
+      <c r="AD56" s="1"/>
+      <c r="AE56" s="1"/>
+      <c r="AF56" t="s">
         <v>44</v>
       </c>
-      <c r="AE56" t="s">
+      <c r="AG56" t="s">
         <v>137</v>
       </c>
-      <c r="AF56">
+      <c r="AH56">
         <v>1</v>
       </c>
-      <c r="AG56" t="s">
-        <v>550</v>
-      </c>
-      <c r="AH56" t="s">
-        <v>551</v>
-      </c>
-      <c r="AK56" t="s">
+      <c r="AI56" t="s">
+        <v>552</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>553</v>
+      </c>
+      <c r="AM56" t="s">
         <v>92</v>
       </c>
-      <c r="AL56" t="s">
-        <v>543</v>
-      </c>
-      <c r="AM56" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="AN56" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="AO56" s="1"/>
+      <c r="AN56" t="s">
+        <v>545</v>
+      </c>
+      <c r="AO56" s="1" t="s">
+        <v>572</v>
+      </c>
       <c r="AP56" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="AQ56" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="AQ56" s="1"/>
+      <c r="AR56" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="AS56" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B57" t="s">
         <v>97</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -8392,10 +8514,10 @@
         <v>28</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -8412,58 +8534,60 @@
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
-      <c r="W57" s="1" t="s">
-        <v>569</v>
-      </c>
+      <c r="W57" s="1"/>
       <c r="X57" s="1"/>
-      <c r="Y57" s="1"/>
+      <c r="Y57" s="1" t="s">
+        <v>571</v>
+      </c>
       <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
-      <c r="AC57" s="1"/>
-      <c r="AD57" t="s">
+      <c r="AD57" s="1"/>
+      <c r="AE57" s="1"/>
+      <c r="AF57" t="s">
         <v>44</v>
       </c>
-      <c r="AE57" t="s">
+      <c r="AG57" t="s">
         <v>137</v>
       </c>
-      <c r="AF57">
+      <c r="AH57">
         <v>1</v>
       </c>
-      <c r="AG57" t="s">
-        <v>550</v>
-      </c>
-      <c r="AH57" t="s">
-        <v>551</v>
-      </c>
-      <c r="AK57" t="s">
+      <c r="AI57" t="s">
+        <v>552</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>553</v>
+      </c>
+      <c r="AM57" t="s">
         <v>92</v>
       </c>
-      <c r="AL57" t="s">
-        <v>543</v>
-      </c>
-      <c r="AM57" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="AN57" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="AO57" s="1"/>
+      <c r="AN57" t="s">
+        <v>545</v>
+      </c>
+      <c r="AO57" s="1" t="s">
+        <v>576</v>
+      </c>
       <c r="AP57" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="AQ57" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="AQ57" s="1"/>
+      <c r="AR57" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="AS57" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B58" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D58" t="s">
         <v>27</v>
@@ -8472,10 +8596,10 @@
         <v>28</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -8492,58 +8616,60 @@
       </c>
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
-      <c r="W58" s="1" t="s">
-        <v>579</v>
-      </c>
+      <c r="W58" s="1"/>
       <c r="X58" s="1"/>
-      <c r="Y58" s="1"/>
+      <c r="Y58" s="1" t="s">
+        <v>581</v>
+      </c>
       <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
-      <c r="AC58" s="1"/>
-      <c r="AD58" t="s">
+      <c r="AD58" s="1"/>
+      <c r="AE58" s="1"/>
+      <c r="AF58" t="s">
         <v>44</v>
       </c>
-      <c r="AE58" t="s">
-        <v>580</v>
-      </c>
-      <c r="AF58">
+      <c r="AG58" t="s">
+        <v>582</v>
+      </c>
+      <c r="AH58">
         <v>1</v>
       </c>
-      <c r="AG58" t="s">
-        <v>581</v>
-      </c>
-      <c r="AH58" t="s">
-        <v>582</v>
-      </c>
-      <c r="AK58" t="s">
+      <c r="AI58" t="s">
+        <v>583</v>
+      </c>
+      <c r="AJ58" t="s">
+        <v>584</v>
+      </c>
+      <c r="AM58" t="s">
         <v>92</v>
       </c>
-      <c r="AL58" t="s">
-        <v>583</v>
-      </c>
-      <c r="AM58" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="AN58" s="1" t="s">
+      <c r="AN58" t="s">
         <v>585</v>
       </c>
-      <c r="AO58" s="1"/>
+      <c r="AO58" s="1" t="s">
+        <v>586</v>
+      </c>
       <c r="AP58" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="AQ58" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="AQ58" s="1"/>
+      <c r="AR58" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="AS58" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B59" t="s">
         <v>97</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
@@ -8552,10 +8678,10 @@
         <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -8572,43 +8698,39 @@
       </c>
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
-      <c r="W59" s="1" t="s">
-        <v>589</v>
-      </c>
+      <c r="W59" s="1"/>
       <c r="X59" s="1"/>
-      <c r="Y59" s="1"/>
+      <c r="Y59" s="1" t="s">
+        <v>591</v>
+      </c>
       <c r="Z59" s="1"/>
+      <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
-      <c r="AC59" s="1"/>
-      <c r="AD59" t="s">
+      <c r="AD59" s="1"/>
+      <c r="AE59" s="1"/>
+      <c r="AF59" t="s">
         <v>44</v>
       </c>
-      <c r="AE59" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF59">
+      <c r="AG59" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH59">
         <v>1</v>
       </c>
-      <c r="AG59" t="s">
-        <v>278</v>
-      </c>
-      <c r="AH59" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ59">
+      <c r="AI59" t="s">
+        <v>280</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>281</v>
+      </c>
+      <c r="AL59">
         <v>12800</v>
       </c>
-      <c r="AK59" t="s">
+      <c r="AM59" t="s">
         <v>103</v>
       </c>
-      <c r="AL59" t="s">
+      <c r="AN59" t="s">
         <v>50</v>
-      </c>
-      <c r="AM59" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="AN59" s="1" t="s">
-        <v>591</v>
       </c>
       <c r="AO59" s="1" t="s">
         <v>592</v>
@@ -8617,18 +8739,24 @@
         <v>593</v>
       </c>
       <c r="AQ59" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="AR59" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="AS59" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B60" t="s">
         <v>97</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -8637,10 +8765,10 @@
         <v>28</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -8657,43 +8785,39 @@
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
-      <c r="W60" s="1" t="s">
-        <v>589</v>
-      </c>
+      <c r="W60" s="1"/>
       <c r="X60" s="1"/>
-      <c r="Y60" s="1"/>
+      <c r="Y60" s="1" t="s">
+        <v>591</v>
+      </c>
       <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
-      <c r="AC60" s="1"/>
-      <c r="AD60" t="s">
+      <c r="AD60" s="1"/>
+      <c r="AE60" s="1"/>
+      <c r="AF60" t="s">
         <v>44</v>
       </c>
-      <c r="AE60" t="s">
-        <v>420</v>
-      </c>
-      <c r="AF60">
+      <c r="AG60" t="s">
+        <v>422</v>
+      </c>
+      <c r="AH60">
         <v>1</v>
       </c>
-      <c r="AG60" t="s">
-        <v>595</v>
-      </c>
-      <c r="AH60" t="s">
-        <v>279</v>
-      </c>
-      <c r="AJ60">
+      <c r="AI60" t="s">
+        <v>597</v>
+      </c>
+      <c r="AJ60" t="s">
+        <v>281</v>
+      </c>
+      <c r="AL60">
         <v>12800</v>
       </c>
-      <c r="AK60" t="s">
+      <c r="AM60" t="s">
         <v>103</v>
       </c>
-      <c r="AL60" t="s">
+      <c r="AN60" t="s">
         <v>50</v>
-      </c>
-      <c r="AM60" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="AN60" s="1" t="s">
-        <v>597</v>
       </c>
       <c r="AO60" s="1" t="s">
         <v>598</v>
@@ -8702,18 +8826,24 @@
         <v>599</v>
       </c>
       <c r="AQ60" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="AR60" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="AS60" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B61" t="s">
         <v>97</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
@@ -8722,10 +8852,10 @@
         <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -8742,40 +8872,36 @@
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
-      <c r="W61" s="1" t="s">
-        <v>589</v>
-      </c>
+      <c r="W61" s="1"/>
       <c r="X61" s="1"/>
-      <c r="Y61" s="1"/>
+      <c r="Y61" s="1" t="s">
+        <v>591</v>
+      </c>
       <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
-      <c r="AC61" s="1"/>
-      <c r="AD61" t="s">
+      <c r="AD61" s="1"/>
+      <c r="AE61" s="1"/>
+      <c r="AF61" t="s">
         <v>44</v>
       </c>
-      <c r="AE61" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF61">
+      <c r="AG61" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH61">
         <v>2</v>
       </c>
-      <c r="AG61" t="s">
-        <v>315</v>
-      </c>
-      <c r="AH61" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ61">
+      <c r="AI61" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>318</v>
+      </c>
+      <c r="AL61">
         <v>51200</v>
       </c>
-      <c r="AK61" t="s">
+      <c r="AM61" t="s">
         <v>103</v>
-      </c>
-      <c r="AM61" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="AN61" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="AO61" s="1" t="s">
         <v>603</v>
@@ -8784,16 +8910,22 @@
         <v>604</v>
       </c>
       <c r="AQ61" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="AR61" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="AS61" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ1"/>
+  <autoFilter ref="A1:AS1"/>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Use yes or no." sqref="AA2:AA2000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Use yes or no." sqref="AC2:AC2000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Pick a value from the dc_device_type list." sqref="AD2:AD2000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Pick a value from the dc_device_type list." sqref="AF2:AF2000">
       <formula1>_vocab!$T$2:$T$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Pick a value from the family list." sqref="B2:B2000">
@@ -8846,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -8861,10 +8993,10 @@
         <v>241</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>6</v>
@@ -8894,36 +9026,36 @@
         <v>251</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
@@ -8938,16 +9070,16 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H2">
         <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -8960,20 +9092,20 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
@@ -8988,16 +9120,16 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H3">
         <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -9010,20 +9142,20 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
@@ -9038,16 +9170,16 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H4">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -9060,20 +9192,20 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B5" t="s">
         <v>97</v>
@@ -9088,10 +9220,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -9104,20 +9236,20 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
@@ -9132,10 +9264,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -9148,20 +9280,20 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
@@ -9176,10 +9308,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -9192,20 +9324,20 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B8" t="s">
         <v>97</v>
@@ -9220,10 +9352,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -9236,20 +9368,20 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B9" t="s">
         <v>97</v>
@@ -9264,16 +9396,16 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H9">
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -9286,20 +9418,20 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B10" t="s">
         <v>97</v>
@@ -9314,16 +9446,16 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H10">
         <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -9336,20 +9468,20 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B11" t="s">
         <v>97</v>
@@ -9364,53 +9496,53 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H11">
         <v>36</v>
       </c>
       <c r="I11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K11" t="s">
         <v>54</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="P11" s="1"/>
       <c r="R11" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B12" t="s">
         <v>97</v>
@@ -9425,55 +9557,55 @@
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H12">
         <v>32</v>
       </c>
       <c r="I12" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K12" t="s">
         <v>54</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="P12" s="1"/>
       <c r="R12" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B13" t="s">
         <v>97</v>
@@ -9488,16 +9620,16 @@
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H13">
         <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -9510,20 +9642,20 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
@@ -9538,16 +9670,16 @@
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H14">
         <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -9560,20 +9692,20 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
@@ -9588,16 +9720,16 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H15">
         <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -9610,20 +9742,20 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B16" t="s">
         <v>97</v>
@@ -9638,16 +9770,16 @@
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="H16">
         <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -9660,20 +9792,20 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B17" t="s">
         <v>97</v>
@@ -9688,16 +9820,16 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H17">
         <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -9710,20 +9842,20 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B18" t="s">
         <v>97</v>
@@ -9738,16 +9870,16 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H18">
         <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -9760,20 +9892,20 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B19" t="s">
         <v>97</v>
@@ -9788,16 +9920,16 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="H19">
         <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -9810,20 +9942,20 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B20" t="s">
         <v>97</v>
@@ -9838,10 +9970,10 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -9854,20 +9986,20 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B21" t="s">
         <v>97</v>
@@ -9882,10 +10014,10 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -9898,20 +10030,20 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B22" t="s">
         <v>97</v>
@@ -9926,10 +10058,10 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -9942,20 +10074,20 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
@@ -9970,10 +10102,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -9986,20 +10118,20 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
@@ -10014,10 +10146,10 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -10030,20 +10162,20 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B25" t="s">
         <v>97</v>
@@ -10058,10 +10190,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -10074,20 +10206,20 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B26" t="s">
         <v>97</v>
@@ -10102,10 +10234,10 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -10118,20 +10250,20 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
@@ -10146,10 +10278,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -10162,20 +10294,20 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B28" t="s">
         <v>97</v>
@@ -10190,10 +10322,10 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -10206,20 +10338,20 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B29" t="s">
         <v>97</v>
@@ -10234,10 +10366,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -10250,20 +10382,20 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B30" t="s">
         <v>97</v>
@@ -10278,16 +10410,16 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H30">
         <v>8</v>
       </c>
       <c r="I30" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -10300,20 +10432,20 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B31" t="s">
         <v>97</v>
@@ -10328,16 +10460,16 @@
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H31">
         <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -10350,20 +10482,20 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B32" t="s">
         <v>97</v>
@@ -10378,16 +10510,16 @@
         <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H32">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -10400,20 +10532,20 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
@@ -10428,16 +10560,16 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="H33">
         <v>24</v>
       </c>
       <c r="I33" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -10450,20 +10582,20 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B34" t="s">
         <v>97</v>
@@ -10478,16 +10610,16 @@
         <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="H34">
         <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -10500,20 +10632,20 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B35" t="s">
         <v>97</v>
@@ -10528,16 +10660,16 @@
         <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="H35">
         <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -10550,20 +10682,20 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
@@ -10578,16 +10710,16 @@
         <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H36">
         <v>48</v>
       </c>
       <c r="I36" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -10600,20 +10732,20 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B37" t="s">
         <v>97</v>
@@ -10628,16 +10760,16 @@
         <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="H37">
         <v>48</v>
       </c>
       <c r="I37" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -10650,20 +10782,20 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B38" t="s">
         <v>97</v>
@@ -10678,10 +10810,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -10694,20 +10826,20 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B39" t="s">
         <v>97</v>
@@ -10722,10 +10854,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -10738,20 +10870,20 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
@@ -10766,10 +10898,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -10782,15 +10914,15 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -10831,827 +10963,827 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -11686,10 +11818,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11697,7 +11829,7 @@
         <v>97</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -11713,7 +11845,7 @@
         <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -11729,7 +11861,7 @@
         <v>97</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -11745,7 +11877,7 @@
         <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
@@ -11761,7 +11893,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -11777,7 +11909,7 @@
         <v>97</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -11793,7 +11925,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
@@ -11809,7 +11941,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -11825,7 +11957,7 @@
         <v>97</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -11841,7 +11973,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -11857,7 +11989,7 @@
         <v>97</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -11873,7 +12005,7 @@
         <v>97</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -11889,7 +12021,7 @@
         <v>97</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
@@ -11905,7 +12037,7 @@
         <v>97</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -11921,7 +12053,7 @@
         <v>97</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
@@ -11937,7 +12069,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -11953,7 +12085,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -11969,7 +12101,7 @@
         <v>97</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
@@ -11985,7 +12117,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
@@ -12001,7 +12133,7 @@
         <v>97</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -12017,7 +12149,7 @@
         <v>97</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>

--- a/data/catalog/datacenter.xlsx
+++ b/data/catalog/datacenter.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="758">
   <si>
     <t>family</t>
   </si>
@@ -771,6 +771,9 @@
   </si>
   <si>
     <t>eol_bulletin_url</t>
+  </si>
+  <si>
+    <t>licence_required</t>
   </si>
   <si>
     <t>licence_note_tr</t>
@@ -3640,7 +3643,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AS61"/>
+  <dimension ref="A1:AT61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -3655,21 +3658,22 @@
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="36" style="1" customWidth="1"/>
     <col min="20" max="20" width="22" customWidth="1"/>
-    <col min="21" max="24" width="40" style="1" customWidth="1"/>
-    <col min="25" max="26" width="36" style="1" customWidth="1"/>
-    <col min="27" max="28" width="13" style="1" customWidth="1"/>
-    <col min="29" max="29" width="10" customWidth="1"/>
-    <col min="30" max="31" width="40" style="1" customWidth="1"/>
-    <col min="32" max="32" width="16" customWidth="1"/>
-    <col min="33" max="33" width="22" customWidth="1"/>
-    <col min="34" max="34" width="12" customWidth="1"/>
-    <col min="35" max="36" width="18" customWidth="1"/>
-    <col min="37" max="38" width="12" customWidth="1"/>
-    <col min="39" max="40" width="22" customWidth="1"/>
-    <col min="41" max="45" width="40" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10" customWidth="1"/>
+    <col min="22" max="25" width="40" style="1" customWidth="1"/>
+    <col min="26" max="27" width="36" style="1" customWidth="1"/>
+    <col min="28" max="29" width="13" style="1" customWidth="1"/>
+    <col min="30" max="30" width="10" customWidth="1"/>
+    <col min="31" max="32" width="40" style="1" customWidth="1"/>
+    <col min="33" max="33" width="16" customWidth="1"/>
+    <col min="34" max="34" width="22" customWidth="1"/>
+    <col min="35" max="35" width="12" customWidth="1"/>
+    <col min="36" max="37" width="18" customWidth="1"/>
+    <col min="38" max="39" width="12" customWidth="1"/>
+    <col min="40" max="41" width="22" customWidth="1"/>
+    <col min="42" max="46" width="40" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>238</v>
       </c>
@@ -3730,7 +3734,7 @@
       <c r="T1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>252</v>
       </c>
       <c r="V1" s="3" t="s">
@@ -3754,16 +3758,16 @@
       <c r="AB1" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="2" t="s">
         <v>261</v>
       </c>
       <c r="AE1" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>263</v>
       </c>
       <c r="AG1" s="2" t="s">
@@ -3785,12 +3789,12 @@
         <v>269</v>
       </c>
       <c r="AM1" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="AN1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AO1" s="2" t="s">
         <v>271</v>
       </c>
       <c r="AP1" s="3" t="s">
@@ -3805,16 +3809,19 @@
       <c r="AS1" s="3" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT1" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -3823,10 +3830,10 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3841,68 +3848,68 @@
       <c r="T2" t="s">
         <v>108</v>
       </c>
-      <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
-      <c r="Y2" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
-      <c r="AD2" s="1"/>
+      <c r="AC2" s="1"/>
       <c r="AE2" s="1"/>
-      <c r="AF2" t="s">
+      <c r="AF2" s="1"/>
+      <c r="AG2" t="s">
         <v>69</v>
       </c>
-      <c r="AG2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AH2">
+      <c r="AH2" t="s">
+        <v>280</v>
+      </c>
+      <c r="AI2">
         <v>16</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>280</v>
       </c>
       <c r="AJ2" t="s">
         <v>281</v>
       </c>
-      <c r="AK2">
+      <c r="AK2" t="s">
+        <v>282</v>
+      </c>
+      <c r="AL2">
         <v>8</v>
       </c>
-      <c r="AL2">
+      <c r="AM2">
         <v>115200</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>46</v>
       </c>
-      <c r="AN2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AO2" t="s">
         <v>283</v>
       </c>
       <c r="AP2" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="AQ2" s="1"/>
-      <c r="AR2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>285</v>
       </c>
+      <c r="AR2" s="1"/>
       <c r="AS2" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="AT2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
@@ -3911,10 +3918,10 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -3929,68 +3936,68 @@
       <c r="T3" t="s">
         <v>108</v>
       </c>
-      <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
-      <c r="Y3" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1" t="s">
+        <v>279</v>
+      </c>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
-      <c r="AD3" s="1"/>
+      <c r="AC3" s="1"/>
       <c r="AE3" s="1"/>
-      <c r="AF3" t="s">
+      <c r="AF3" s="1"/>
+      <c r="AG3" t="s">
         <v>69</v>
       </c>
-      <c r="AG3" t="s">
-        <v>279</v>
-      </c>
-      <c r="AH3">
+      <c r="AH3" t="s">
+        <v>280</v>
+      </c>
+      <c r="AI3">
         <v>10</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>280</v>
       </c>
       <c r="AJ3" t="s">
         <v>281</v>
       </c>
-      <c r="AK3">
+      <c r="AK3" t="s">
+        <v>282</v>
+      </c>
+      <c r="AL3">
         <v>4</v>
       </c>
-      <c r="AL3">
+      <c r="AM3">
         <v>57000</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AN3" t="s">
         <v>46</v>
       </c>
-      <c r="AN3" t="s">
-        <v>282</v>
-      </c>
-      <c r="AO3" s="1" t="s">
-        <v>287</v>
+      <c r="AO3" t="s">
+        <v>283</v>
       </c>
       <c r="AP3" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="AQ3" s="1"/>
-      <c r="AR3" s="1" t="s">
-        <v>285</v>
-      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="AR3" s="1"/>
       <c r="AS3" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="AT3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
@@ -3999,10 +4006,10 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -4017,65 +4024,65 @@
       <c r="T4" t="s">
         <v>108</v>
       </c>
-      <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="Z4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
-      <c r="AD4" s="1"/>
+      <c r="AC4" s="1"/>
       <c r="AE4" s="1"/>
-      <c r="AF4" t="s">
+      <c r="AF4" s="1"/>
+      <c r="AG4" t="s">
         <v>69</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AH4" t="s">
         <v>70</v>
       </c>
-      <c r="AH4">
+      <c r="AI4">
         <v>7</v>
       </c>
-      <c r="AI4" t="s">
-        <v>292</v>
-      </c>
       <c r="AJ4" t="s">
-        <v>281</v>
-      </c>
-      <c r="AK4">
+        <v>293</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>282</v>
+      </c>
+      <c r="AL4">
         <v>4</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>293</v>
       </c>
       <c r="AN4" t="s">
         <v>294</v>
       </c>
-      <c r="AO4" s="1" t="s">
+      <c r="AO4" t="s">
         <v>295</v>
       </c>
       <c r="AP4" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="AQ4" s="1"/>
-      <c r="AR4" s="1" t="s">
+      <c r="AQ4" s="1" t="s">
         <v>297</v>
       </c>
+      <c r="AR4" s="1"/>
       <c r="AS4" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="AT4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B5" t="s">
         <v>97</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D5" t="s">
         <v>27</v>
@@ -4084,10 +4091,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -4102,65 +4109,65 @@
       <c r="T5" t="s">
         <v>108</v>
       </c>
-      <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-      <c r="Y5" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="Z5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
-      <c r="AD5" s="1"/>
+      <c r="AC5" s="1"/>
       <c r="AE5" s="1"/>
-      <c r="AF5" t="s">
+      <c r="AF5" s="1"/>
+      <c r="AG5" t="s">
         <v>69</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AH5" t="s">
         <v>70</v>
       </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>13</v>
       </c>
-      <c r="AI5" t="s">
-        <v>292</v>
-      </c>
       <c r="AJ5" t="s">
-        <v>281</v>
-      </c>
-      <c r="AK5">
+        <v>293</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>282</v>
+      </c>
+      <c r="AL5">
         <v>8</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>293</v>
       </c>
       <c r="AN5" t="s">
         <v>294</v>
       </c>
-      <c r="AO5" s="1" t="s">
-        <v>299</v>
+      <c r="AO5" t="s">
+        <v>295</v>
       </c>
       <c r="AP5" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="AQ5" s="1"/>
-      <c r="AR5" s="1" t="s">
-        <v>297</v>
-      </c>
+      <c r="AQ5" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="AR5" s="1"/>
       <c r="AS5" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="AT5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
@@ -4169,10 +4176,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -4187,68 +4194,68 @@
       <c r="T6" t="s">
         <v>108</v>
       </c>
-      <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="Z6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
-      <c r="AD6" s="1"/>
+      <c r="AC6" s="1"/>
       <c r="AE6" s="1"/>
-      <c r="AF6" t="s">
+      <c r="AF6" s="1"/>
+      <c r="AG6" t="s">
         <v>69</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AH6" t="s">
         <v>70</v>
       </c>
-      <c r="AH6">
+      <c r="AI6">
         <v>21</v>
       </c>
-      <c r="AI6" t="s">
-        <v>292</v>
-      </c>
       <c r="AJ6" t="s">
-        <v>281</v>
-      </c>
-      <c r="AK6">
+        <v>293</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>282</v>
+      </c>
+      <c r="AL6">
         <v>16</v>
       </c>
-      <c r="AL6">
+      <c r="AM6">
         <v>172800</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>293</v>
       </c>
       <c r="AN6" t="s">
         <v>294</v>
       </c>
-      <c r="AO6" s="1" t="s">
-        <v>302</v>
+      <c r="AO6" t="s">
+        <v>295</v>
       </c>
       <c r="AP6" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="AQ6" s="1"/>
-      <c r="AR6" s="1" t="s">
-        <v>297</v>
-      </c>
+      <c r="AQ6" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="AR6" s="1"/>
       <c r="AS6" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="AT6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -4257,10 +4264,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -4275,68 +4282,68 @@
       <c r="T7" t="s">
         <v>108</v>
       </c>
-      <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
-      <c r="Y7" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="Z7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1" t="s">
+        <v>307</v>
+      </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
-      <c r="AD7" s="1"/>
+      <c r="AC7" s="1"/>
       <c r="AE7" s="1"/>
-      <c r="AF7" t="s">
+      <c r="AF7" s="1"/>
+      <c r="AG7" t="s">
         <v>69</v>
       </c>
-      <c r="AG7" t="s">
-        <v>307</v>
-      </c>
-      <c r="AH7">
+      <c r="AH7" t="s">
+        <v>308</v>
+      </c>
+      <c r="AI7">
         <v>4</v>
       </c>
-      <c r="AI7" t="s">
-        <v>308</v>
-      </c>
       <c r="AJ7" t="s">
-        <v>281</v>
-      </c>
-      <c r="AK7">
+        <v>309</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>282</v>
+      </c>
+      <c r="AL7">
         <v>8</v>
       </c>
-      <c r="AL7">
+      <c r="AM7">
         <v>25600</v>
       </c>
-      <c r="AM7" t="s">
-        <v>293</v>
-      </c>
       <c r="AN7" t="s">
-        <v>309</v>
-      </c>
-      <c r="AO7" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="AO7" t="s">
         <v>310</v>
       </c>
       <c r="AP7" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="AQ7" s="1"/>
-      <c r="AR7" s="1" t="s">
+      <c r="AQ7" s="1" t="s">
         <v>312</v>
       </c>
+      <c r="AR7" s="1"/>
       <c r="AS7" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AT7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B8" t="s">
         <v>97</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
@@ -4345,10 +4352,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -4363,65 +4370,65 @@
       <c r="T8" t="s">
         <v>108</v>
       </c>
-      <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
-      <c r="Y8" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="Z8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1" t="s">
+        <v>316</v>
+      </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
-      <c r="AD8" s="1"/>
+      <c r="AC8" s="1"/>
       <c r="AE8" s="1"/>
-      <c r="AF8" t="s">
+      <c r="AF8" s="1"/>
+      <c r="AG8" t="s">
         <v>44</v>
       </c>
-      <c r="AG8" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH8">
+      <c r="AH8" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI8">
         <v>2</v>
-      </c>
-      <c r="AI8" t="s">
-        <v>317</v>
       </c>
       <c r="AJ8" t="s">
         <v>318</v>
       </c>
-      <c r="AL8">
+      <c r="AK8" t="s">
+        <v>319</v>
+      </c>
+      <c r="AM8">
         <v>51200</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AN8" t="s">
         <v>46</v>
       </c>
-      <c r="AN8" t="s">
-        <v>319</v>
-      </c>
-      <c r="AO8" s="1" t="s">
+      <c r="AO8" t="s">
         <v>320</v>
       </c>
       <c r="AP8" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="AQ8" s="1"/>
-      <c r="AR8" s="1" t="s">
+      <c r="AQ8" s="1" t="s">
         <v>322</v>
       </c>
+      <c r="AR8" s="1"/>
       <c r="AS8" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AT8" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B9" t="s">
         <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -4430,10 +4437,10 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -4448,65 +4455,65 @@
       <c r="T9" t="s">
         <v>108</v>
       </c>
-      <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
-      <c r="Y9" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="Z9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1" t="s">
+        <v>316</v>
+      </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
-      <c r="AD9" s="1"/>
+      <c r="AC9" s="1"/>
       <c r="AE9" s="1"/>
-      <c r="AF9" t="s">
+      <c r="AF9" s="1"/>
+      <c r="AG9" t="s">
         <v>44</v>
       </c>
-      <c r="AG9" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH9">
+      <c r="AH9" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI9">
         <v>2</v>
-      </c>
-      <c r="AI9" t="s">
-        <v>317</v>
       </c>
       <c r="AJ9" t="s">
         <v>318</v>
       </c>
-      <c r="AL9">
+      <c r="AK9" t="s">
+        <v>319</v>
+      </c>
+      <c r="AM9">
         <v>51200</v>
       </c>
-      <c r="AM9" t="s">
+      <c r="AN9" t="s">
         <v>46</v>
       </c>
-      <c r="AN9" t="s">
-        <v>319</v>
-      </c>
-      <c r="AO9" s="1" t="s">
-        <v>324</v>
+      <c r="AO9" t="s">
+        <v>320</v>
       </c>
       <c r="AP9" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="AQ9" s="1"/>
-      <c r="AR9" s="1" t="s">
-        <v>322</v>
-      </c>
+      <c r="AQ9" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="AR9" s="1"/>
       <c r="AS9" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AT9" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B10" t="s">
         <v>97</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
@@ -4515,10 +4522,10 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -4533,43 +4540,40 @@
       <c r="T10" t="s">
         <v>108</v>
       </c>
-      <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
-      <c r="Y10" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="Z10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1" t="s">
+        <v>316</v>
+      </c>
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
-      <c r="AD10" s="1"/>
+      <c r="AC10" s="1"/>
       <c r="AE10" s="1"/>
-      <c r="AF10" t="s">
+      <c r="AF10" s="1"/>
+      <c r="AG10" t="s">
         <v>44</v>
       </c>
-      <c r="AG10" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH10">
+      <c r="AH10" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI10">
         <v>2</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>317</v>
       </c>
       <c r="AJ10" t="s">
         <v>318</v>
       </c>
-      <c r="AL10">
+      <c r="AK10" t="s">
+        <v>319</v>
+      </c>
+      <c r="AM10">
         <v>51200</v>
       </c>
-      <c r="AM10" t="s">
+      <c r="AN10" t="s">
         <v>46</v>
       </c>
-      <c r="AN10" t="s">
-        <v>327</v>
-      </c>
-      <c r="AO10" s="1" t="s">
+      <c r="AO10" t="s">
         <v>328</v>
       </c>
       <c r="AP10" s="1" t="s">
@@ -4582,18 +4586,21 @@
         <v>331</v>
       </c>
       <c r="AS10" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="AT10" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B11" t="s">
         <v>97</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D11" t="s">
         <v>27</v>
@@ -4602,10 +4609,10 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -4620,44 +4627,41 @@
       <c r="T11" t="s">
         <v>108</v>
       </c>
-      <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
-      <c r="Y11" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="Z11" s="1"/>
+      <c r="Y11" s="1"/>
+      <c r="Z11" s="1" t="s">
+        <v>316</v>
+      </c>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
-      <c r="AD11" s="1"/>
+      <c r="AC11" s="1"/>
       <c r="AE11" s="1"/>
-      <c r="AF11" t="s">
+      <c r="AF11" s="1"/>
+      <c r="AG11" t="s">
         <v>44</v>
       </c>
-      <c r="AG11" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH11">
+      <c r="AH11" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI11">
         <v>2</v>
-      </c>
-      <c r="AI11" t="s">
-        <v>317</v>
       </c>
       <c r="AJ11" t="s">
         <v>318</v>
       </c>
-      <c r="AL11">
+      <c r="AK11" t="s">
+        <v>319</v>
+      </c>
+      <c r="AM11">
         <v>51200</v>
       </c>
-      <c r="AM11" t="s">
+      <c r="AN11" t="s">
         <v>46</v>
       </c>
-      <c r="AN11" t="s">
-        <v>327</v>
-      </c>
-      <c r="AO11" s="1" t="s">
-        <v>333</v>
+      <c r="AO11" t="s">
+        <v>328</v>
       </c>
       <c r="AP11" s="1" t="s">
         <v>334</v>
@@ -4666,21 +4670,24 @@
         <v>335</v>
       </c>
       <c r="AR11" s="1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AS11" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="AT11" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B12" t="s">
         <v>97</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
@@ -4689,10 +4696,10 @@
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -4707,65 +4714,65 @@
       <c r="T12" t="s">
         <v>108</v>
       </c>
-      <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
-      <c r="Y12" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
-      <c r="AD12" s="1"/>
+      <c r="AC12" s="1"/>
       <c r="AE12" s="1"/>
-      <c r="AF12" t="s">
+      <c r="AF12" s="1"/>
+      <c r="AG12" t="s">
         <v>44</v>
       </c>
-      <c r="AG12" t="s">
+      <c r="AH12" t="s">
         <v>70</v>
       </c>
-      <c r="AH12">
+      <c r="AI12">
         <v>3</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>317</v>
       </c>
       <c r="AJ12" t="s">
         <v>318</v>
       </c>
-      <c r="AL12">
+      <c r="AK12" t="s">
+        <v>319</v>
+      </c>
+      <c r="AM12">
         <v>102400</v>
       </c>
-      <c r="AM12" t="s">
+      <c r="AN12" t="s">
         <v>46</v>
       </c>
-      <c r="AN12" t="s">
-        <v>338</v>
-      </c>
-      <c r="AO12" s="1" t="s">
+      <c r="AO12" t="s">
         <v>339</v>
       </c>
       <c r="AP12" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="AQ12" s="1"/>
-      <c r="AR12" s="1" t="s">
+      <c r="AQ12" s="1" t="s">
         <v>341</v>
       </c>
+      <c r="AR12" s="1"/>
       <c r="AS12" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="AT12" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B13" t="s">
         <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -4774,10 +4781,10 @@
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -4792,65 +4799,65 @@
       <c r="T13" t="s">
         <v>108</v>
       </c>
-      <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
-      <c r="Y13" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="Z13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1" t="s">
+        <v>338</v>
+      </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
-      <c r="AD13" s="1"/>
+      <c r="AC13" s="1"/>
       <c r="AE13" s="1"/>
-      <c r="AF13" t="s">
+      <c r="AF13" s="1"/>
+      <c r="AG13" t="s">
         <v>44</v>
       </c>
-      <c r="AG13" t="s">
+      <c r="AH13" t="s">
         <v>70</v>
       </c>
-      <c r="AH13">
+      <c r="AI13">
         <v>3</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>317</v>
       </c>
       <c r="AJ13" t="s">
         <v>318</v>
       </c>
-      <c r="AL13">
+      <c r="AK13" t="s">
+        <v>319</v>
+      </c>
+      <c r="AM13">
         <v>102400</v>
       </c>
-      <c r="AM13" t="s">
+      <c r="AN13" t="s">
         <v>46</v>
       </c>
-      <c r="AN13" t="s">
-        <v>338</v>
-      </c>
-      <c r="AO13" s="1" t="s">
-        <v>343</v>
+      <c r="AO13" t="s">
+        <v>339</v>
       </c>
       <c r="AP13" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="AQ13" s="1"/>
-      <c r="AR13" s="1" t="s">
-        <v>341</v>
-      </c>
+      <c r="AQ13" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="AR13" s="1"/>
       <c r="AS13" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="AT13" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
@@ -4859,10 +4866,10 @@
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -4877,65 +4884,65 @@
       <c r="T14" t="s">
         <v>108</v>
       </c>
-      <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
-      <c r="Y14" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="Z14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1" t="s">
+        <v>348</v>
+      </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
-      <c r="AD14" s="1"/>
+      <c r="AC14" s="1"/>
       <c r="AE14" s="1"/>
-      <c r="AF14" t="s">
+      <c r="AF14" s="1"/>
+      <c r="AG14" t="s">
         <v>44</v>
       </c>
-      <c r="AG14" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH14">
+      <c r="AH14" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI14">
         <v>2</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>317</v>
       </c>
       <c r="AJ14" t="s">
         <v>318</v>
       </c>
-      <c r="AL14">
+      <c r="AK14" t="s">
+        <v>319</v>
+      </c>
+      <c r="AM14">
         <v>51200</v>
       </c>
-      <c r="AM14" t="s">
+      <c r="AN14" t="s">
         <v>46</v>
       </c>
-      <c r="AN14" t="s">
-        <v>348</v>
-      </c>
-      <c r="AO14" s="1" t="s">
+      <c r="AO14" t="s">
         <v>349</v>
       </c>
       <c r="AP14" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="AQ14" s="1"/>
-      <c r="AR14" s="1" t="s">
+      <c r="AQ14" s="1" t="s">
         <v>351</v>
       </c>
+      <c r="AR14" s="1"/>
       <c r="AS14" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="AT14" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
@@ -4944,10 +4951,10 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -4962,65 +4969,65 @@
       <c r="T15" t="s">
         <v>108</v>
       </c>
-      <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
-      <c r="Y15" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="Z15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
-      <c r="AD15" s="1"/>
+      <c r="AC15" s="1"/>
       <c r="AE15" s="1"/>
-      <c r="AF15" t="s">
+      <c r="AF15" s="1"/>
+      <c r="AG15" t="s">
         <v>44</v>
       </c>
-      <c r="AG15" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH15">
+      <c r="AH15" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI15">
         <v>1</v>
       </c>
-      <c r="AI15" t="s">
-        <v>355</v>
-      </c>
       <c r="AJ15" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL15">
+        <v>356</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM15">
         <v>25600</v>
       </c>
-      <c r="AM15" t="s">
-        <v>293</v>
-      </c>
       <c r="AN15" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO15" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="AO15" t="s">
         <v>357</v>
       </c>
       <c r="AP15" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="AQ15" s="1"/>
-      <c r="AR15" s="1" t="s">
+      <c r="AQ15" s="1" t="s">
         <v>359</v>
       </c>
+      <c r="AR15" s="1"/>
       <c r="AS15" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT15" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B16" t="s">
         <v>97</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
@@ -5029,10 +5036,10 @@
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -5047,65 +5054,65 @@
       <c r="T16" t="s">
         <v>108</v>
       </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
-      <c r="Y16" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="Z16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
-      <c r="AD16" s="1"/>
+      <c r="AC16" s="1"/>
       <c r="AE16" s="1"/>
-      <c r="AF16" t="s">
+      <c r="AF16" s="1"/>
+      <c r="AG16" t="s">
         <v>44</v>
       </c>
-      <c r="AG16" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH16">
+      <c r="AH16" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI16">
         <v>1</v>
       </c>
-      <c r="AI16" t="s">
-        <v>355</v>
-      </c>
       <c r="AJ16" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL16">
+        <v>356</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM16">
         <v>25600</v>
       </c>
-      <c r="AM16" t="s">
-        <v>293</v>
-      </c>
       <c r="AN16" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO16" s="1" t="s">
-        <v>361</v>
+        <v>294</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>357</v>
       </c>
       <c r="AP16" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="AQ16" s="1"/>
-      <c r="AR16" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ16" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="AR16" s="1"/>
       <c r="AS16" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT16" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B17" t="s">
         <v>97</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D17" t="s">
         <v>27</v>
@@ -5114,10 +5121,10 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -5132,65 +5139,65 @@
       <c r="T17" t="s">
         <v>108</v>
       </c>
-      <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
-      <c r="Y17" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="Z17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
-      <c r="AD17" s="1"/>
+      <c r="AC17" s="1"/>
       <c r="AE17" s="1"/>
-      <c r="AF17" t="s">
+      <c r="AF17" s="1"/>
+      <c r="AG17" t="s">
         <v>44</v>
       </c>
-      <c r="AG17" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH17">
+      <c r="AH17" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI17">
         <v>2</v>
       </c>
-      <c r="AI17" t="s">
-        <v>355</v>
-      </c>
       <c r="AJ17" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL17">
+        <v>356</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM17">
         <v>38400</v>
       </c>
-      <c r="AM17" t="s">
-        <v>293</v>
-      </c>
       <c r="AN17" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO17" s="1" t="s">
-        <v>364</v>
+        <v>294</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>357</v>
       </c>
       <c r="AP17" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="AQ17" s="1"/>
-      <c r="AR17" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ17" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="AR17" s="1"/>
       <c r="AS17" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT17" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B18" t="s">
         <v>97</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
@@ -5199,10 +5206,10 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -5217,65 +5224,65 @@
       <c r="T18" t="s">
         <v>108</v>
       </c>
-      <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
-      <c r="Y18" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="Z18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
-      <c r="AD18" s="1"/>
+      <c r="AC18" s="1"/>
       <c r="AE18" s="1"/>
-      <c r="AF18" t="s">
+      <c r="AF18" s="1"/>
+      <c r="AG18" t="s">
         <v>44</v>
       </c>
-      <c r="AG18" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH18">
+      <c r="AH18" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI18">
         <v>2</v>
       </c>
-      <c r="AI18" t="s">
-        <v>355</v>
-      </c>
       <c r="AJ18" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL18">
+        <v>356</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM18">
         <v>51200</v>
       </c>
-      <c r="AM18" t="s">
-        <v>293</v>
-      </c>
       <c r="AN18" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO18" s="1" t="s">
-        <v>367</v>
+        <v>294</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>357</v>
       </c>
       <c r="AP18" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="AQ18" s="1"/>
-      <c r="AR18" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ18" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="AR18" s="1"/>
       <c r="AS18" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT18" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B19" t="s">
         <v>97</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
@@ -5284,10 +5291,10 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -5302,65 +5309,65 @@
       <c r="T19" t="s">
         <v>108</v>
       </c>
-      <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
-      <c r="Y19" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1" t="s">
+        <v>372</v>
+      </c>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
-      <c r="AD19" s="1"/>
+      <c r="AC19" s="1"/>
       <c r="AE19" s="1"/>
-      <c r="AF19" t="s">
+      <c r="AF19" s="1"/>
+      <c r="AG19" t="s">
         <v>44</v>
       </c>
-      <c r="AG19" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH19">
+      <c r="AH19" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI19">
         <v>1</v>
       </c>
-      <c r="AI19" t="s">
-        <v>355</v>
-      </c>
       <c r="AJ19" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL19">
+        <v>356</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM19">
         <v>12800</v>
       </c>
-      <c r="AM19" t="s">
-        <v>293</v>
-      </c>
       <c r="AN19" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO19" s="1" t="s">
-        <v>372</v>
+        <v>294</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>357</v>
       </c>
       <c r="AP19" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="AQ19" s="1"/>
-      <c r="AR19" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ19" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="AR19" s="1"/>
       <c r="AS19" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT19" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B20" t="s">
         <v>97</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
@@ -5369,10 +5376,10 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -5387,65 +5394,65 @@
       <c r="T20" t="s">
         <v>108</v>
       </c>
-      <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
-      <c r="Y20" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1" t="s">
+        <v>372</v>
+      </c>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
-      <c r="AD20" s="1"/>
+      <c r="AC20" s="1"/>
       <c r="AE20" s="1"/>
-      <c r="AF20" t="s">
+      <c r="AF20" s="1"/>
+      <c r="AG20" t="s">
         <v>44</v>
       </c>
-      <c r="AG20" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH20">
+      <c r="AH20" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI20">
         <v>1</v>
       </c>
-      <c r="AI20" t="s">
-        <v>375</v>
-      </c>
       <c r="AJ20" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL20">
+        <v>376</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM20">
         <v>12000</v>
       </c>
-      <c r="AM20" t="s">
-        <v>293</v>
-      </c>
       <c r="AN20" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO20" s="1" t="s">
-        <v>376</v>
+        <v>294</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>357</v>
       </c>
       <c r="AP20" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="AQ20" s="1"/>
-      <c r="AR20" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ20" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="AR20" s="1"/>
       <c r="AS20" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT20" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B21" t="s">
         <v>97</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
@@ -5454,10 +5461,10 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -5472,65 +5479,65 @@
       <c r="T21" t="s">
         <v>108</v>
       </c>
-      <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
-      <c r="Y21" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="Z21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1" t="s">
+        <v>372</v>
+      </c>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
-      <c r="AD21" s="1"/>
+      <c r="AC21" s="1"/>
       <c r="AE21" s="1"/>
-      <c r="AF21" t="s">
+      <c r="AF21" s="1"/>
+      <c r="AG21" t="s">
         <v>44</v>
       </c>
-      <c r="AG21" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH21">
+      <c r="AH21" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI21">
         <v>2</v>
-      </c>
-      <c r="AI21" t="s">
-        <v>379</v>
       </c>
       <c r="AJ21" t="s">
         <v>380</v>
       </c>
-      <c r="AL21">
+      <c r="AK21" t="s">
+        <v>381</v>
+      </c>
+      <c r="AM21">
         <v>12800</v>
       </c>
-      <c r="AM21" t="s">
-        <v>293</v>
-      </c>
       <c r="AN21" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO21" s="1" t="s">
-        <v>381</v>
+        <v>294</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>357</v>
       </c>
       <c r="AP21" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="AQ21" s="1"/>
-      <c r="AR21" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ21" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="AR21" s="1"/>
       <c r="AS21" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT21" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B22" t="s">
         <v>97</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D22" t="s">
         <v>27</v>
@@ -5539,10 +5546,10 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5557,65 +5564,65 @@
       <c r="T22" t="s">
         <v>108</v>
       </c>
-      <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
-      <c r="Y22" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="Z22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1" t="s">
+        <v>386</v>
+      </c>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
-      <c r="AD22" s="1"/>
+      <c r="AC22" s="1"/>
       <c r="AE22" s="1"/>
-      <c r="AF22" t="s">
+      <c r="AF22" s="1"/>
+      <c r="AG22" t="s">
         <v>44</v>
       </c>
-      <c r="AG22" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH22">
+      <c r="AH22" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI22">
         <v>1</v>
       </c>
-      <c r="AI22" t="s">
-        <v>355</v>
-      </c>
       <c r="AJ22" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL22">
+        <v>356</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM22">
         <v>25600</v>
       </c>
-      <c r="AM22" t="s">
+      <c r="AN22" t="s">
         <v>46</v>
       </c>
-      <c r="AN22" t="s">
-        <v>386</v>
-      </c>
-      <c r="AO22" s="1" t="s">
+      <c r="AO22" t="s">
         <v>387</v>
       </c>
       <c r="AP22" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="AQ22" s="1"/>
-      <c r="AR22" s="1" t="s">
+      <c r="AQ22" s="1" t="s">
         <v>389</v>
       </c>
+      <c r="AR22" s="1"/>
       <c r="AS22" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="AT22" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
@@ -5624,10 +5631,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -5642,62 +5649,62 @@
       <c r="T23" t="s">
         <v>108</v>
       </c>
-      <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
-      <c r="Y23" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="Z23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1" t="s">
+        <v>392</v>
+      </c>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
-      <c r="AD23" s="1"/>
+      <c r="AC23" s="1"/>
       <c r="AE23" s="1"/>
-      <c r="AF23" t="s">
+      <c r="AF23" s="1"/>
+      <c r="AG23" t="s">
         <v>44</v>
       </c>
-      <c r="AG23" t="s">
+      <c r="AH23" t="s">
         <v>45</v>
       </c>
-      <c r="AH23">
+      <c r="AI23">
         <v>1</v>
       </c>
-      <c r="AI23" t="s">
-        <v>392</v>
-      </c>
       <c r="AJ23" t="s">
-        <v>281</v>
-      </c>
-      <c r="AM23" t="s">
+        <v>393</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>282</v>
+      </c>
+      <c r="AN23" t="s">
         <v>46</v>
       </c>
-      <c r="AN23" t="s">
-        <v>319</v>
-      </c>
-      <c r="AO23" s="1" t="s">
-        <v>393</v>
+      <c r="AO23" t="s">
+        <v>320</v>
       </c>
       <c r="AP23" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="AQ23" s="1"/>
-      <c r="AR23" s="1" t="s">
+      <c r="AQ23" s="1" t="s">
         <v>395</v>
       </c>
+      <c r="AR23" s="1"/>
       <c r="AS23" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="AT23" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
@@ -5706,10 +5713,10 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -5724,65 +5731,65 @@
       <c r="T24" t="s">
         <v>108</v>
       </c>
-      <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
-      <c r="Y24" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="Z24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1" t="s">
+        <v>399</v>
+      </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
-      <c r="AD24" s="1"/>
+      <c r="AC24" s="1"/>
       <c r="AE24" s="1"/>
-      <c r="AF24" t="s">
+      <c r="AF24" s="1"/>
+      <c r="AG24" t="s">
         <v>44</v>
       </c>
-      <c r="AG24" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH24">
+      <c r="AH24" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI24">
         <v>2</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>379</v>
       </c>
       <c r="AJ24" t="s">
         <v>380</v>
       </c>
-      <c r="AL24">
+      <c r="AK24" t="s">
+        <v>381</v>
+      </c>
+      <c r="AM24">
         <v>12800</v>
       </c>
-      <c r="AM24" t="s">
+      <c r="AN24" t="s">
         <v>46</v>
       </c>
-      <c r="AN24" t="s">
-        <v>319</v>
-      </c>
-      <c r="AO24" s="1" t="s">
-        <v>399</v>
+      <c r="AO24" t="s">
+        <v>320</v>
       </c>
       <c r="AP24" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="AQ24" s="1"/>
-      <c r="AR24" s="1" t="s">
+      <c r="AQ24" s="1" t="s">
         <v>401</v>
       </c>
+      <c r="AR24" s="1"/>
       <c r="AS24" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="AT24" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B25" t="s">
         <v>97</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
@@ -5791,10 +5798,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -5809,65 +5816,65 @@
       <c r="T25" t="s">
         <v>108</v>
       </c>
-      <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
-      <c r="Y25" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
-      <c r="AD25" s="1"/>
+      <c r="AC25" s="1"/>
       <c r="AE25" s="1"/>
-      <c r="AF25" t="s">
+      <c r="AF25" s="1"/>
+      <c r="AG25" t="s">
         <v>44</v>
       </c>
-      <c r="AG25" t="s">
-        <v>307</v>
-      </c>
-      <c r="AH25">
+      <c r="AH25" t="s">
+        <v>308</v>
+      </c>
+      <c r="AI25">
         <v>1</v>
-      </c>
-      <c r="AI25" t="s">
-        <v>379</v>
       </c>
       <c r="AJ25" t="s">
         <v>380</v>
       </c>
-      <c r="AL25">
+      <c r="AK25" t="s">
+        <v>381</v>
+      </c>
+      <c r="AM25">
         <v>7200</v>
       </c>
-      <c r="AM25" t="s">
+      <c r="AN25" t="s">
         <v>46</v>
       </c>
-      <c r="AN25" t="s">
-        <v>405</v>
-      </c>
-      <c r="AO25" s="1" t="s">
+      <c r="AO25" t="s">
         <v>406</v>
       </c>
       <c r="AP25" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="AQ25" s="1"/>
-      <c r="AR25" s="1" t="s">
+      <c r="AQ25" s="1" t="s">
         <v>408</v>
       </c>
+      <c r="AR25" s="1"/>
       <c r="AS25" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="AT25" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B26" t="s">
         <v>97</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D26" t="s">
         <v>27</v>
@@ -5876,10 +5883,10 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -5894,65 +5901,65 @@
       <c r="T26" t="s">
         <v>108</v>
       </c>
-      <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
-      <c r="Y26" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
-      <c r="AD26" s="1"/>
+      <c r="AC26" s="1"/>
       <c r="AE26" s="1"/>
-      <c r="AF26" t="s">
+      <c r="AF26" s="1"/>
+      <c r="AG26" t="s">
         <v>44</v>
       </c>
-      <c r="AG26" t="s">
+      <c r="AH26" t="s">
         <v>45</v>
       </c>
-      <c r="AH26">
+      <c r="AI26">
         <v>1</v>
       </c>
-      <c r="AI26" t="s">
-        <v>410</v>
-      </c>
       <c r="AJ26" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL26">
+        <v>411</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM26">
         <v>5600</v>
       </c>
-      <c r="AM26" t="s">
+      <c r="AN26" t="s">
         <v>46</v>
       </c>
-      <c r="AN26" t="s">
-        <v>405</v>
-      </c>
-      <c r="AO26" s="1" t="s">
-        <v>411</v>
+      <c r="AO26" t="s">
+        <v>406</v>
       </c>
       <c r="AP26" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="AQ26" s="1"/>
-      <c r="AR26" s="1" t="s">
-        <v>408</v>
-      </c>
+      <c r="AQ26" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="AR26" s="1"/>
       <c r="AS26" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="AT26" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D27" t="s">
         <v>27</v>
@@ -5961,10 +5968,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -5979,65 +5986,65 @@
       <c r="T27" t="s">
         <v>108</v>
       </c>
-      <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
-      <c r="Y27" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
-      <c r="AD27" s="1"/>
+      <c r="AC27" s="1"/>
       <c r="AE27" s="1"/>
-      <c r="AF27" t="s">
+      <c r="AF27" s="1"/>
+      <c r="AG27" t="s">
         <v>44</v>
       </c>
-      <c r="AG27" t="s">
+      <c r="AH27" t="s">
         <v>45</v>
       </c>
-      <c r="AH27">
+      <c r="AI27">
         <v>2</v>
       </c>
-      <c r="AI27" t="s">
-        <v>414</v>
-      </c>
       <c r="AJ27" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL27">
+        <v>415</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM27">
         <v>9600</v>
       </c>
-      <c r="AM27" t="s">
+      <c r="AN27" t="s">
         <v>46</v>
       </c>
-      <c r="AN27" t="s">
-        <v>405</v>
-      </c>
-      <c r="AO27" s="1" t="s">
-        <v>415</v>
+      <c r="AO27" t="s">
+        <v>406</v>
       </c>
       <c r="AP27" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="AQ27" s="1"/>
-      <c r="AR27" s="1" t="s">
-        <v>408</v>
-      </c>
+      <c r="AQ27" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="AR27" s="1"/>
       <c r="AS27" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="AT27" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B28" t="s">
         <v>97</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D28" t="s">
         <v>27</v>
@@ -6046,10 +6053,10 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -6064,65 +6071,65 @@
       <c r="T28" t="s">
         <v>108</v>
       </c>
-      <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
-      <c r="Y28" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
-      <c r="AD28" s="1"/>
+      <c r="AC28" s="1"/>
       <c r="AE28" s="1"/>
-      <c r="AF28" t="s">
+      <c r="AF28" s="1"/>
+      <c r="AG28" t="s">
         <v>44</v>
       </c>
-      <c r="AG28" t="s">
+      <c r="AH28" t="s">
         <v>45</v>
       </c>
-      <c r="AH28">
+      <c r="AI28">
         <v>2</v>
       </c>
-      <c r="AI28" t="s">
-        <v>418</v>
-      </c>
       <c r="AJ28" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL28">
+        <v>419</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM28">
         <v>4200</v>
       </c>
-      <c r="AM28" t="s">
+      <c r="AN28" t="s">
         <v>46</v>
       </c>
-      <c r="AN28" t="s">
-        <v>405</v>
-      </c>
-      <c r="AO28" s="1" t="s">
-        <v>419</v>
+      <c r="AO28" t="s">
+        <v>406</v>
       </c>
       <c r="AP28" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="AQ28" s="1"/>
-      <c r="AR28" s="1" t="s">
-        <v>408</v>
-      </c>
+      <c r="AQ28" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="AR28" s="1"/>
       <c r="AS28" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="AT28" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B29" t="s">
         <v>97</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D29" t="s">
         <v>27</v>
@@ -6131,10 +6138,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -6149,44 +6156,41 @@
       <c r="T29" t="s">
         <v>108</v>
       </c>
-      <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
-      <c r="Y29" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1" t="s">
+        <v>405</v>
+      </c>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
-      <c r="AD29" s="1"/>
+      <c r="AC29" s="1"/>
       <c r="AE29" s="1"/>
-      <c r="AF29" t="s">
+      <c r="AF29" s="1"/>
+      <c r="AG29" t="s">
         <v>44</v>
       </c>
-      <c r="AG29" t="s">
-        <v>422</v>
-      </c>
-      <c r="AH29">
+      <c r="AH29" t="s">
+        <v>423</v>
+      </c>
+      <c r="AI29">
         <v>1</v>
       </c>
-      <c r="AI29" t="s">
-        <v>414</v>
-      </c>
       <c r="AJ29" t="s">
-        <v>380</v>
-      </c>
-      <c r="AL29">
+        <v>415</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>381</v>
+      </c>
+      <c r="AM29">
         <v>5600</v>
       </c>
-      <c r="AM29" t="s">
+      <c r="AN29" t="s">
         <v>46</v>
       </c>
-      <c r="AN29" t="s">
+      <c r="AO29" t="s">
         <v>177</v>
-      </c>
-      <c r="AO29" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="AP29" s="1" t="s">
         <v>424</v>
@@ -6198,18 +6202,21 @@
         <v>426</v>
       </c>
       <c r="AS29" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="AT29" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B30" t="s">
         <v>97</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D30" t="s">
         <v>27</v>
@@ -6218,10 +6225,10 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -6236,43 +6243,40 @@
       <c r="T30" t="s">
         <v>108</v>
       </c>
-      <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
-      <c r="Y30" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="Z30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1" t="s">
+        <v>430</v>
+      </c>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
-      <c r="AD30" s="1"/>
+      <c r="AC30" s="1"/>
       <c r="AE30" s="1"/>
-      <c r="AF30" t="s">
+      <c r="AF30" s="1"/>
+      <c r="AG30" t="s">
         <v>44</v>
       </c>
-      <c r="AG30" t="s">
-        <v>430</v>
-      </c>
-      <c r="AH30">
+      <c r="AH30" t="s">
+        <v>431</v>
+      </c>
+      <c r="AI30">
         <v>1</v>
       </c>
-      <c r="AI30" t="s">
-        <v>431</v>
-      </c>
       <c r="AJ30" t="s">
-        <v>380</v>
-      </c>
-      <c r="AL30">
+        <v>432</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>381</v>
+      </c>
+      <c r="AM30">
         <v>2400</v>
-      </c>
-      <c r="AM30" t="s">
-        <v>432</v>
       </c>
       <c r="AN30" t="s">
         <v>433</v>
       </c>
-      <c r="AO30" s="1" t="s">
+      <c r="AO30" t="s">
         <v>434</v>
       </c>
       <c r="AP30" s="1" t="s">
@@ -6285,18 +6289,21 @@
         <v>437</v>
       </c>
       <c r="AS30" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="AT30" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B31" t="s">
         <v>97</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D31" t="s">
         <v>27</v>
@@ -6305,10 +6312,10 @@
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -6323,44 +6330,41 @@
       <c r="T31" t="s">
         <v>108</v>
       </c>
-      <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
-      <c r="Y31" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="Z31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1" t="s">
+        <v>430</v>
+      </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
-      <c r="AD31" s="1"/>
+      <c r="AC31" s="1"/>
       <c r="AE31" s="1"/>
-      <c r="AF31" t="s">
+      <c r="AF31" s="1"/>
+      <c r="AG31" t="s">
         <v>44</v>
       </c>
-      <c r="AG31" t="s">
-        <v>430</v>
-      </c>
-      <c r="AH31">
+      <c r="AH31" t="s">
+        <v>431</v>
+      </c>
+      <c r="AI31">
         <v>1</v>
       </c>
-      <c r="AI31" t="s">
-        <v>410</v>
-      </c>
       <c r="AJ31" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL31">
+        <v>411</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM31">
         <v>3800</v>
-      </c>
-      <c r="AM31" t="s">
-        <v>432</v>
       </c>
       <c r="AN31" t="s">
         <v>433</v>
       </c>
-      <c r="AO31" s="1" t="s">
-        <v>439</v>
+      <c r="AO31" t="s">
+        <v>434</v>
       </c>
       <c r="AP31" s="1" t="s">
         <v>440</v>
@@ -6369,21 +6373,24 @@
         <v>441</v>
       </c>
       <c r="AR31" s="1" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AS31" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="AT31" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B32" t="s">
         <v>97</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
@@ -6392,10 +6399,10 @@
         <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -6410,44 +6417,41 @@
       <c r="T32" t="s">
         <v>108</v>
       </c>
-      <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
-      <c r="Y32" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1" t="s">
+        <v>445</v>
+      </c>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
-      <c r="AD32" s="1"/>
+      <c r="AC32" s="1"/>
       <c r="AE32" s="1"/>
-      <c r="AF32" t="s">
+      <c r="AF32" s="1"/>
+      <c r="AG32" t="s">
         <v>44</v>
       </c>
-      <c r="AG32" t="s">
-        <v>445</v>
-      </c>
-      <c r="AH32">
+      <c r="AH32" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI32">
         <v>1</v>
       </c>
-      <c r="AI32" t="s">
-        <v>410</v>
-      </c>
       <c r="AJ32" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL32">
+        <v>411</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM32">
         <v>3600</v>
       </c>
-      <c r="AM32" t="s">
-        <v>293</v>
-      </c>
       <c r="AN32" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO32" s="1" t="s">
-        <v>446</v>
+        <v>294</v>
+      </c>
+      <c r="AO32" t="s">
+        <v>357</v>
       </c>
       <c r="AP32" s="1" t="s">
         <v>447</v>
@@ -6456,21 +6460,24 @@
         <v>448</v>
       </c>
       <c r="AR32" s="1" t="s">
-        <v>359</v>
+        <v>449</v>
       </c>
       <c r="AS32" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT32" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
@@ -6479,10 +6486,10 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -6497,65 +6504,65 @@
       <c r="T33" t="s">
         <v>108</v>
       </c>
-      <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
-      <c r="Y33" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1" t="s">
+        <v>445</v>
+      </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
-      <c r="AD33" s="1"/>
+      <c r="AC33" s="1"/>
       <c r="AE33" s="1"/>
-      <c r="AF33" t="s">
+      <c r="AF33" s="1"/>
+      <c r="AG33" t="s">
         <v>44</v>
       </c>
-      <c r="AG33" t="s">
-        <v>445</v>
-      </c>
-      <c r="AH33">
+      <c r="AH33" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI33">
         <v>1</v>
       </c>
-      <c r="AI33" t="s">
-        <v>450</v>
-      </c>
       <c r="AJ33" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL33">
+        <v>451</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM33">
         <v>2160</v>
       </c>
-      <c r="AM33" t="s">
-        <v>293</v>
-      </c>
       <c r="AN33" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO33" s="1" t="s">
-        <v>451</v>
+        <v>294</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>357</v>
       </c>
       <c r="AP33" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="AQ33" s="1"/>
-      <c r="AR33" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ33" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="AR33" s="1"/>
       <c r="AS33" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT33" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B34" t="s">
         <v>97</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -6564,10 +6571,10 @@
         <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -6582,65 +6589,65 @@
       <c r="T34" t="s">
         <v>108</v>
       </c>
-      <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
-      <c r="Y34" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1" t="s">
+        <v>445</v>
+      </c>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
-      <c r="AD34" s="1"/>
+      <c r="AC34" s="1"/>
       <c r="AE34" s="1"/>
-      <c r="AF34" t="s">
+      <c r="AF34" s="1"/>
+      <c r="AG34" t="s">
         <v>44</v>
       </c>
-      <c r="AG34" t="s">
-        <v>445</v>
-      </c>
-      <c r="AH34">
+      <c r="AH34" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI34">
         <v>1</v>
       </c>
-      <c r="AI34" t="s">
-        <v>450</v>
-      </c>
       <c r="AJ34" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL34">
+        <v>451</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM34">
         <v>2160</v>
       </c>
-      <c r="AM34" t="s">
-        <v>293</v>
-      </c>
       <c r="AN34" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO34" s="1" t="s">
-        <v>454</v>
+        <v>294</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>357</v>
       </c>
       <c r="AP34" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="AQ34" s="1"/>
-      <c r="AR34" s="1" t="s">
+      <c r="AQ34" s="1" t="s">
         <v>456</v>
       </c>
+      <c r="AR34" s="1"/>
       <c r="AS34" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="AT34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B35" t="s">
         <v>97</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -6649,10 +6656,10 @@
         <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -6667,65 +6674,65 @@
       <c r="T35" t="s">
         <v>108</v>
       </c>
-      <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
-      <c r="Y35" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1" t="s">
+        <v>445</v>
+      </c>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
-      <c r="AD35" s="1"/>
+      <c r="AC35" s="1"/>
       <c r="AE35" s="1"/>
-      <c r="AF35" t="s">
+      <c r="AF35" s="1"/>
+      <c r="AG35" t="s">
         <v>44</v>
       </c>
-      <c r="AG35" t="s">
-        <v>445</v>
-      </c>
-      <c r="AH35">
+      <c r="AH35" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI35">
         <v>1</v>
       </c>
-      <c r="AI35" t="s">
-        <v>410</v>
-      </c>
       <c r="AJ35" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL35">
+        <v>411</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM35">
         <v>3600</v>
       </c>
-      <c r="AM35" t="s">
-        <v>293</v>
-      </c>
       <c r="AN35" t="s">
-        <v>309</v>
-      </c>
-      <c r="AO35" s="1" t="s">
-        <v>458</v>
+        <v>294</v>
+      </c>
+      <c r="AO35" t="s">
+        <v>310</v>
       </c>
       <c r="AP35" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="AQ35" s="1"/>
-      <c r="AR35" s="1" t="s">
-        <v>312</v>
-      </c>
+      <c r="AQ35" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="AR35" s="1"/>
       <c r="AS35" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AT35" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D36" t="s">
         <v>27</v>
@@ -6734,10 +6741,10 @@
         <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -6752,65 +6759,65 @@
       <c r="T36" t="s">
         <v>108</v>
       </c>
-      <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
-      <c r="Y36" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1" t="s">
+        <v>445</v>
+      </c>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
-      <c r="AD36" s="1"/>
+      <c r="AC36" s="1"/>
       <c r="AE36" s="1"/>
-      <c r="AF36" t="s">
+      <c r="AF36" s="1"/>
+      <c r="AG36" t="s">
         <v>44</v>
       </c>
-      <c r="AG36" t="s">
-        <v>445</v>
-      </c>
-      <c r="AH36">
+      <c r="AH36" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI36">
         <v>1</v>
       </c>
-      <c r="AI36" t="s">
-        <v>450</v>
-      </c>
       <c r="AJ36" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL36">
+        <v>451</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM36">
         <v>2160</v>
       </c>
-      <c r="AM36" t="s">
-        <v>293</v>
-      </c>
       <c r="AN36" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO36" s="1" t="s">
-        <v>461</v>
+        <v>294</v>
+      </c>
+      <c r="AO36" t="s">
+        <v>357</v>
       </c>
       <c r="AP36" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="AQ36" s="1"/>
-      <c r="AR36" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ36" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="AR36" s="1"/>
       <c r="AS36" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT36" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B37" t="s">
         <v>97</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D37" t="s">
         <v>27</v>
@@ -6819,10 +6826,10 @@
         <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -6837,65 +6844,65 @@
       <c r="T37" t="s">
         <v>108</v>
       </c>
-      <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
-      <c r="Y37" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1" t="s">
+        <v>445</v>
+      </c>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
-      <c r="AD37" s="1"/>
+      <c r="AC37" s="1"/>
       <c r="AE37" s="1"/>
-      <c r="AF37" t="s">
+      <c r="AF37" s="1"/>
+      <c r="AG37" t="s">
         <v>44</v>
       </c>
-      <c r="AG37" t="s">
+      <c r="AH37" t="s">
         <v>38</v>
       </c>
-      <c r="AH37">
+      <c r="AI37">
         <v>1</v>
       </c>
-      <c r="AI37" t="s">
-        <v>464</v>
-      </c>
       <c r="AJ37" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL37">
+        <v>465</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM37">
         <v>696</v>
       </c>
-      <c r="AM37" t="s">
+      <c r="AN37" t="s">
         <v>46</v>
       </c>
-      <c r="AN37" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO37" s="1" t="s">
-        <v>465</v>
+      <c r="AO37" t="s">
+        <v>357</v>
       </c>
       <c r="AP37" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="AQ37" s="1"/>
-      <c r="AR37" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ37" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="AR37" s="1"/>
       <c r="AS37" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT37" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B38" t="s">
         <v>97</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D38" t="s">
         <v>27</v>
@@ -6904,10 +6911,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -6922,65 +6929,65 @@
       <c r="T38" t="s">
         <v>108</v>
       </c>
-      <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
-      <c r="Y38" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="Z38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1" t="s">
+        <v>445</v>
+      </c>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
-      <c r="AD38" s="1"/>
+      <c r="AC38" s="1"/>
       <c r="AE38" s="1"/>
-      <c r="AF38" t="s">
+      <c r="AF38" s="1"/>
+      <c r="AG38" t="s">
         <v>44</v>
       </c>
-      <c r="AG38" t="s">
+      <c r="AH38" t="s">
         <v>38</v>
       </c>
-      <c r="AH38">
+      <c r="AI38">
         <v>1</v>
       </c>
-      <c r="AI38" t="s">
-        <v>468</v>
-      </c>
       <c r="AJ38" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL38">
+        <v>469</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM38">
         <v>696</v>
       </c>
-      <c r="AM38" t="s">
+      <c r="AN38" t="s">
         <v>46</v>
       </c>
-      <c r="AN38" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO38" s="1" t="s">
-        <v>469</v>
+      <c r="AO38" t="s">
+        <v>357</v>
       </c>
       <c r="AP38" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="AQ38" s="1"/>
-      <c r="AR38" s="1" t="s">
+      <c r="AQ38" s="1" t="s">
         <v>471</v>
       </c>
+      <c r="AR38" s="1"/>
       <c r="AS38" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="AT38" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B39" t="s">
         <v>97</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D39" t="s">
         <v>27</v>
@@ -6989,10 +6996,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -7007,65 +7014,65 @@
       <c r="T39" t="s">
         <v>108</v>
       </c>
-      <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
-      <c r="Y39" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="Z39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1" t="s">
+        <v>475</v>
+      </c>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
-      <c r="AD39" s="1"/>
+      <c r="AC39" s="1"/>
       <c r="AE39" s="1"/>
-      <c r="AF39" t="s">
+      <c r="AF39" s="1"/>
+      <c r="AG39" t="s">
         <v>44</v>
       </c>
-      <c r="AG39" t="s">
-        <v>307</v>
-      </c>
-      <c r="AH39">
+      <c r="AH39" t="s">
+        <v>308</v>
+      </c>
+      <c r="AI39">
         <v>1</v>
-      </c>
-      <c r="AI39" t="s">
-        <v>379</v>
       </c>
       <c r="AJ39" t="s">
         <v>380</v>
       </c>
-      <c r="AL39">
+      <c r="AK39" t="s">
+        <v>381</v>
+      </c>
+      <c r="AM39">
         <v>7200</v>
       </c>
-      <c r="AM39" t="s">
-        <v>293</v>
-      </c>
       <c r="AN39" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO39" s="1" t="s">
-        <v>475</v>
+        <v>294</v>
+      </c>
+      <c r="AO39" t="s">
+        <v>357</v>
       </c>
       <c r="AP39" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="AQ39" s="1"/>
-      <c r="AR39" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ39" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="AR39" s="1"/>
       <c r="AS39" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT39" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D40" t="s">
         <v>27</v>
@@ -7074,10 +7081,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -7092,65 +7099,65 @@
       <c r="T40" t="s">
         <v>108</v>
       </c>
-      <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
-      <c r="Y40" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="Z40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1" t="s">
+        <v>475</v>
+      </c>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
-      <c r="AD40" s="1"/>
+      <c r="AC40" s="1"/>
       <c r="AE40" s="1"/>
-      <c r="AF40" t="s">
+      <c r="AF40" s="1"/>
+      <c r="AG40" t="s">
         <v>44</v>
       </c>
-      <c r="AG40" t="s">
-        <v>307</v>
-      </c>
-      <c r="AH40">
+      <c r="AH40" t="s">
+        <v>308</v>
+      </c>
+      <c r="AI40">
         <v>1</v>
-      </c>
-      <c r="AI40" t="s">
-        <v>379</v>
       </c>
       <c r="AJ40" t="s">
         <v>380</v>
       </c>
-      <c r="AL40">
+      <c r="AK40" t="s">
+        <v>381</v>
+      </c>
+      <c r="AM40">
         <v>7200</v>
       </c>
-      <c r="AM40" t="s">
-        <v>293</v>
-      </c>
       <c r="AN40" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO40" s="1" t="s">
-        <v>478</v>
+        <v>294</v>
+      </c>
+      <c r="AO40" t="s">
+        <v>357</v>
       </c>
       <c r="AP40" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="AQ40" s="1"/>
-      <c r="AR40" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ40" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="AR40" s="1"/>
       <c r="AS40" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT40" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B41" t="s">
         <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D41" t="s">
         <v>27</v>
@@ -7159,10 +7166,10 @@
         <v>28</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -7177,65 +7184,65 @@
       <c r="T41" t="s">
         <v>108</v>
       </c>
-      <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
-      <c r="Y41" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="Z41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1" t="s">
+        <v>475</v>
+      </c>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
-      <c r="AD41" s="1"/>
+      <c r="AC41" s="1"/>
       <c r="AE41" s="1"/>
-      <c r="AF41" t="s">
+      <c r="AF41" s="1"/>
+      <c r="AG41" t="s">
         <v>44</v>
       </c>
-      <c r="AG41" t="s">
+      <c r="AH41" t="s">
         <v>45</v>
       </c>
-      <c r="AH41">
+      <c r="AI41">
         <v>2</v>
       </c>
-      <c r="AI41" t="s">
-        <v>481</v>
-      </c>
       <c r="AJ41" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL41">
+        <v>482</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM41">
         <v>7200</v>
       </c>
-      <c r="AM41" t="s">
-        <v>293</v>
-      </c>
       <c r="AN41" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO41" s="1" t="s">
-        <v>482</v>
+        <v>294</v>
+      </c>
+      <c r="AO41" t="s">
+        <v>357</v>
       </c>
       <c r="AP41" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="AQ41" s="1"/>
-      <c r="AR41" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ41" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="AR41" s="1"/>
       <c r="AS41" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT41" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B42" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D42" t="s">
         <v>27</v>
@@ -7244,10 +7251,10 @@
         <v>28</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -7262,65 +7269,65 @@
       <c r="T42" t="s">
         <v>108</v>
       </c>
-      <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
-      <c r="Y42" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="Z42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1" t="s">
+        <v>475</v>
+      </c>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
-      <c r="AD42" s="1"/>
+      <c r="AC42" s="1"/>
       <c r="AE42" s="1"/>
-      <c r="AF42" t="s">
+      <c r="AF42" s="1"/>
+      <c r="AG42" t="s">
         <v>44</v>
       </c>
-      <c r="AG42" t="s">
+      <c r="AH42" t="s">
         <v>45</v>
       </c>
-      <c r="AH42">
+      <c r="AI42">
         <v>1.2</v>
       </c>
-      <c r="AI42" t="s">
-        <v>481</v>
-      </c>
       <c r="AJ42" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL42">
+        <v>482</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM42">
         <v>4800</v>
       </c>
-      <c r="AM42" t="s">
-        <v>293</v>
-      </c>
       <c r="AN42" t="s">
-        <v>356</v>
-      </c>
-      <c r="AO42" s="1" t="s">
-        <v>485</v>
+        <v>294</v>
+      </c>
+      <c r="AO42" t="s">
+        <v>357</v>
       </c>
       <c r="AP42" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="AQ42" s="1"/>
-      <c r="AR42" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="AQ42" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="AR42" s="1"/>
       <c r="AS42" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AT42" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B43" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D43" t="s">
         <v>27</v>
@@ -7329,10 +7336,10 @@
         <v>28</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -7347,65 +7354,65 @@
       <c r="T43" t="s">
         <v>108</v>
       </c>
-      <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
-      <c r="Y43" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="Z43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1" t="s">
+        <v>475</v>
+      </c>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
-      <c r="AD43" s="1"/>
+      <c r="AC43" s="1"/>
       <c r="AE43" s="1"/>
-      <c r="AF43" t="s">
+      <c r="AF43" s="1"/>
+      <c r="AG43" t="s">
         <v>44</v>
       </c>
-      <c r="AG43" t="s">
+      <c r="AH43" t="s">
         <v>45</v>
       </c>
-      <c r="AH43">
+      <c r="AI43">
         <v>2</v>
       </c>
-      <c r="AI43" t="s">
-        <v>418</v>
-      </c>
       <c r="AJ43" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL43">
+        <v>419</v>
+      </c>
+      <c r="AK43" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM43">
         <v>4320</v>
-      </c>
-      <c r="AM43" t="s">
-        <v>293</v>
       </c>
       <c r="AN43" t="s">
         <v>294</v>
       </c>
-      <c r="AO43" s="1" t="s">
-        <v>488</v>
+      <c r="AO43" t="s">
+        <v>295</v>
       </c>
       <c r="AP43" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="AQ43" s="1"/>
-      <c r="AR43" s="1" t="s">
-        <v>297</v>
-      </c>
+      <c r="AQ43" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="AR43" s="1"/>
       <c r="AS43" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="AT43" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B44" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
@@ -7414,10 +7421,10 @@
         <v>28</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -7432,65 +7439,65 @@
       <c r="T44" t="s">
         <v>108</v>
       </c>
-      <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
-      <c r="Y44" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="Z44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1" t="s">
+        <v>493</v>
+      </c>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
-      <c r="AD44" s="1"/>
+      <c r="AC44" s="1"/>
       <c r="AE44" s="1"/>
-      <c r="AF44" t="s">
+      <c r="AF44" s="1"/>
+      <c r="AG44" t="s">
         <v>44</v>
       </c>
-      <c r="AG44" t="s">
+      <c r="AH44" t="s">
         <v>38</v>
       </c>
-      <c r="AH44">
+      <c r="AI44">
         <v>1</v>
       </c>
-      <c r="AI44" t="s">
-        <v>468</v>
-      </c>
       <c r="AJ44" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL44">
+        <v>469</v>
+      </c>
+      <c r="AK44" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM44">
         <v>696</v>
       </c>
-      <c r="AM44" t="s">
+      <c r="AN44" t="s">
         <v>46</v>
       </c>
-      <c r="AN44" t="s">
-        <v>493</v>
-      </c>
-      <c r="AO44" s="1" t="s">
+      <c r="AO44" t="s">
         <v>494</v>
       </c>
       <c r="AP44" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="AQ44" s="1"/>
-      <c r="AR44" s="1" t="s">
+      <c r="AQ44" s="1" t="s">
         <v>496</v>
       </c>
+      <c r="AR44" s="1"/>
       <c r="AS44" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="AT44" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B45" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
@@ -7499,10 +7506,10 @@
         <v>28</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -7513,78 +7520,78 @@
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q45" s="1"/>
       <c r="S45" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="T45" t="s">
         <v>108</v>
       </c>
-      <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
-      <c r="Y45" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="Z45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1" t="s">
+        <v>503</v>
+      </c>
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
-      <c r="AD45" s="1"/>
+      <c r="AC45" s="1"/>
       <c r="AE45" s="1"/>
-      <c r="AF45" t="s">
+      <c r="AF45" s="1"/>
+      <c r="AG45" t="s">
         <v>44</v>
       </c>
-      <c r="AG45" t="s">
+      <c r="AH45" t="s">
         <v>70</v>
       </c>
-      <c r="AH45">
+      <c r="AI45">
         <v>2</v>
-      </c>
-      <c r="AI45" t="s">
-        <v>379</v>
       </c>
       <c r="AJ45" t="s">
         <v>380</v>
       </c>
-      <c r="AL45">
+      <c r="AK45" t="s">
+        <v>381</v>
+      </c>
+      <c r="AM45">
         <v>12800</v>
       </c>
-      <c r="AM45" t="s">
-        <v>293</v>
-      </c>
       <c r="AN45" t="s">
-        <v>319</v>
-      </c>
-      <c r="AO45" s="1" t="s">
-        <v>503</v>
+        <v>294</v>
+      </c>
+      <c r="AO45" t="s">
+        <v>320</v>
       </c>
       <c r="AP45" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="AQ45" s="1"/>
-      <c r="AR45" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="AS45" s="1"/>
-    </row>
-    <row r="46" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AQ45" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="AR45" s="1"/>
+      <c r="AS45" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="AT45" s="1"/>
+    </row>
+    <row r="46" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B46" t="s">
         <v>97</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D46" t="s">
         <v>27</v>
@@ -7593,10 +7600,10 @@
         <v>28</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -7611,65 +7618,65 @@
       <c r="T46" t="s">
         <v>108</v>
       </c>
-      <c r="U46" s="1"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
-      <c r="Y46" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="Z46" s="1"/>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1" t="s">
+        <v>508</v>
+      </c>
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
-      <c r="AD46" s="1"/>
+      <c r="AC46" s="1"/>
       <c r="AE46" s="1"/>
-      <c r="AF46" t="s">
+      <c r="AF46" s="1"/>
+      <c r="AG46" t="s">
         <v>44</v>
       </c>
-      <c r="AG46" t="s">
-        <v>508</v>
-      </c>
-      <c r="AH46">
+      <c r="AH46" t="s">
+        <v>509</v>
+      </c>
+      <c r="AI46">
         <v>1</v>
       </c>
-      <c r="AI46" t="s">
-        <v>410</v>
-      </c>
       <c r="AJ46" t="s">
-        <v>379</v>
-      </c>
-      <c r="AL46">
+        <v>411</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>380</v>
+      </c>
+      <c r="AM46">
         <v>3600</v>
       </c>
-      <c r="AM46" t="s">
+      <c r="AN46" t="s">
         <v>46</v>
       </c>
-      <c r="AN46" t="s">
+      <c r="AO46" t="s">
         <v>152</v>
-      </c>
-      <c r="AO46" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="AP46" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="AQ46" s="1"/>
-      <c r="AR46" s="1" t="s">
+      <c r="AQ46" s="1" t="s">
         <v>511</v>
       </c>
+      <c r="AR46" s="1"/>
       <c r="AS46" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT46" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B47" t="s">
         <v>97</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D47" t="s">
         <v>27</v>
@@ -7678,10 +7685,10 @@
         <v>28</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -7699,58 +7706,58 @@
       <c r="T47" t="s">
         <v>108</v>
       </c>
-      <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
-      <c r="Y47" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="Z47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1" t="s">
+        <v>514</v>
+      </c>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
-      <c r="AD47" s="1"/>
+      <c r="AC47" s="1"/>
       <c r="AE47" s="1"/>
-      <c r="AF47" t="s">
+      <c r="AF47" s="1"/>
+      <c r="AG47" t="s">
         <v>44</v>
       </c>
-      <c r="AG47" t="s">
+      <c r="AH47" t="s">
         <v>38</v>
       </c>
-      <c r="AH47">
+      <c r="AI47">
         <v>1</v>
       </c>
-      <c r="AI47" t="s">
-        <v>514</v>
-      </c>
       <c r="AJ47" t="s">
-        <v>514</v>
-      </c>
-      <c r="AL47">
+        <v>515</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>515</v>
+      </c>
+      <c r="AM47">
         <v>960</v>
       </c>
-      <c r="AM47" t="s">
+      <c r="AN47" t="s">
         <v>46</v>
-      </c>
-      <c r="AO47" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="AP47" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="AQ47" s="1"/>
+      <c r="AQ47" s="1" t="s">
+        <v>517</v>
+      </c>
       <c r="AR47" s="1"/>
       <c r="AS47" s="1"/>
-    </row>
-    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT47" s="1"/>
+    </row>
+    <row r="48" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B48" t="s">
         <v>97</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D48" t="s">
         <v>27</v>
@@ -7759,10 +7766,10 @@
         <v>28</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -7780,58 +7787,58 @@
       <c r="T48" t="s">
         <v>108</v>
       </c>
-      <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
-      <c r="Y48" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="Z48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1" t="s">
+        <v>514</v>
+      </c>
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
-      <c r="AD48" s="1"/>
+      <c r="AC48" s="1"/>
       <c r="AE48" s="1"/>
-      <c r="AF48" t="s">
+      <c r="AF48" s="1"/>
+      <c r="AG48" t="s">
         <v>44</v>
       </c>
-      <c r="AG48" t="s">
+      <c r="AH48" t="s">
         <v>38</v>
       </c>
-      <c r="AH48">
+      <c r="AI48">
         <v>1</v>
       </c>
-      <c r="AI48" t="s">
-        <v>514</v>
-      </c>
       <c r="AJ48" t="s">
-        <v>514</v>
-      </c>
-      <c r="AL48">
+        <v>515</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>515</v>
+      </c>
+      <c r="AM48">
         <v>480</v>
       </c>
-      <c r="AM48" t="s">
+      <c r="AN48" t="s">
         <v>46</v>
-      </c>
-      <c r="AO48" s="1" t="s">
-        <v>518</v>
       </c>
       <c r="AP48" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="AQ48" s="1"/>
+      <c r="AQ48" s="1" t="s">
+        <v>520</v>
+      </c>
       <c r="AR48" s="1"/>
       <c r="AS48" s="1"/>
-    </row>
-    <row r="49" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT48" s="1"/>
+    </row>
+    <row r="49" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B49" t="s">
         <v>97</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D49" t="s">
         <v>27</v>
@@ -7840,10 +7847,10 @@
         <v>28</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -7858,68 +7865,68 @@
       <c r="T49" t="s">
         <v>118</v>
       </c>
-      <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
       <c r="X49" s="1"/>
-      <c r="Y49" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="Z49" s="1"/>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1" t="s">
+        <v>524</v>
+      </c>
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
-      <c r="AD49" s="1"/>
+      <c r="AC49" s="1"/>
       <c r="AE49" s="1"/>
-      <c r="AF49" t="s">
+      <c r="AF49" s="1"/>
+      <c r="AG49" t="s">
         <v>69</v>
       </c>
-      <c r="AG49" t="s">
+      <c r="AH49" t="s">
         <v>143</v>
       </c>
-      <c r="AH49">
+      <c r="AI49">
         <v>9</v>
-      </c>
-      <c r="AI49" t="s">
-        <v>524</v>
       </c>
       <c r="AJ49" t="s">
         <v>525</v>
       </c>
-      <c r="AK49">
+      <c r="AK49" t="s">
+        <v>526</v>
+      </c>
+      <c r="AL49">
         <v>4</v>
       </c>
-      <c r="AL49">
+      <c r="AM49">
         <v>12000</v>
       </c>
-      <c r="AM49" t="s">
+      <c r="AN49" t="s">
         <v>92</v>
       </c>
-      <c r="AN49" t="s">
-        <v>526</v>
-      </c>
-      <c r="AO49" s="1" t="s">
+      <c r="AO49" t="s">
         <v>527</v>
       </c>
       <c r="AP49" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="AQ49" s="1"/>
-      <c r="AR49" s="1" t="s">
+      <c r="AQ49" s="1" t="s">
         <v>529</v>
       </c>
+      <c r="AR49" s="1"/>
       <c r="AS49" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="AT49" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B50" t="s">
         <v>97</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
@@ -7928,10 +7935,10 @@
         <v>28</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -7946,68 +7953,68 @@
       <c r="T50" t="s">
         <v>118</v>
       </c>
-      <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
-      <c r="Y50" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="Z50" s="1"/>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1" t="s">
+        <v>533</v>
+      </c>
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
-      <c r="AD50" s="1"/>
+      <c r="AC50" s="1"/>
       <c r="AE50" s="1"/>
-      <c r="AF50" t="s">
+      <c r="AF50" s="1"/>
+      <c r="AG50" t="s">
         <v>69</v>
       </c>
-      <c r="AG50" t="s">
+      <c r="AH50" t="s">
         <v>143</v>
       </c>
-      <c r="AH50">
+      <c r="AI50">
         <v>14</v>
-      </c>
-      <c r="AI50" t="s">
-        <v>524</v>
       </c>
       <c r="AJ50" t="s">
         <v>525</v>
       </c>
-      <c r="AK50">
+      <c r="AK50" t="s">
+        <v>526</v>
+      </c>
+      <c r="AL50">
         <v>8</v>
       </c>
-      <c r="AL50">
+      <c r="AM50">
         <v>24000</v>
       </c>
-      <c r="AM50" t="s">
+      <c r="AN50" t="s">
         <v>92</v>
       </c>
-      <c r="AN50" t="s">
-        <v>526</v>
-      </c>
-      <c r="AO50" s="1" t="s">
-        <v>533</v>
+      <c r="AO50" t="s">
+        <v>527</v>
       </c>
       <c r="AP50" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="AQ50" s="1"/>
-      <c r="AR50" s="1" t="s">
-        <v>529</v>
-      </c>
+      <c r="AQ50" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="AR50" s="1"/>
       <c r="AS50" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="AT50" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B51" t="s">
         <v>97</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
@@ -8016,10 +8023,10 @@
         <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -8034,68 +8041,68 @@
       <c r="T51" t="s">
         <v>118</v>
       </c>
-      <c r="U51" s="1"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
-      <c r="Y51" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="Z51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1" t="s">
+        <v>538</v>
+      </c>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
-      <c r="AD51" s="1"/>
+      <c r="AC51" s="1"/>
       <c r="AE51" s="1"/>
-      <c r="AF51" t="s">
+      <c r="AF51" s="1"/>
+      <c r="AG51" t="s">
         <v>69</v>
       </c>
-      <c r="AG51" t="s">
+      <c r="AH51" t="s">
         <v>143</v>
       </c>
-      <c r="AH51">
+      <c r="AI51">
         <v>26</v>
-      </c>
-      <c r="AI51" t="s">
-        <v>524</v>
       </c>
       <c r="AJ51" t="s">
         <v>525</v>
       </c>
-      <c r="AK51">
+      <c r="AK51" t="s">
+        <v>526</v>
+      </c>
+      <c r="AL51">
         <v>16</v>
       </c>
-      <c r="AL51">
+      <c r="AM51">
         <v>48000</v>
       </c>
-      <c r="AM51" t="s">
+      <c r="AN51" t="s">
         <v>92</v>
       </c>
-      <c r="AN51" t="s">
-        <v>526</v>
-      </c>
-      <c r="AO51" s="1" t="s">
-        <v>538</v>
+      <c r="AO51" t="s">
+        <v>527</v>
       </c>
       <c r="AP51" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="AQ51" s="1"/>
-      <c r="AR51" s="1" t="s">
-        <v>529</v>
-      </c>
+      <c r="AQ51" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="AR51" s="1"/>
       <c r="AS51" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="AT51" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B52" t="s">
         <v>97</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D52" t="s">
         <v>27</v>
@@ -8104,10 +8111,10 @@
         <v>28</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -8122,62 +8129,62 @@
       <c r="T52" t="s">
         <v>118</v>
       </c>
-      <c r="U52" s="1"/>
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
-      <c r="Y52" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="Z52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1" t="s">
+        <v>544</v>
+      </c>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
-      <c r="AD52" s="1"/>
+      <c r="AC52" s="1"/>
       <c r="AE52" s="1"/>
-      <c r="AF52" t="s">
+      <c r="AF52" s="1"/>
+      <c r="AG52" t="s">
         <v>44</v>
       </c>
-      <c r="AG52" t="s">
+      <c r="AH52" t="s">
         <v>137</v>
       </c>
-      <c r="AH52">
+      <c r="AI52">
         <v>2</v>
       </c>
-      <c r="AI52" t="s">
-        <v>544</v>
-      </c>
       <c r="AJ52" t="s">
-        <v>525</v>
-      </c>
-      <c r="AM52" t="s">
+        <v>545</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>526</v>
+      </c>
+      <c r="AN52" t="s">
         <v>92</v>
       </c>
-      <c r="AN52" t="s">
-        <v>545</v>
-      </c>
-      <c r="AO52" s="1" t="s">
+      <c r="AO52" t="s">
         <v>546</v>
       </c>
       <c r="AP52" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="AQ52" s="1"/>
-      <c r="AR52" s="1" t="s">
+      <c r="AQ52" s="1" t="s">
         <v>548</v>
       </c>
+      <c r="AR52" s="1"/>
       <c r="AS52" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="AT52" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B53" t="s">
         <v>97</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D53" t="s">
         <v>27</v>
@@ -8186,10 +8193,10 @@
         <v>28</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -8204,62 +8211,62 @@
       <c r="T53" t="s">
         <v>118</v>
       </c>
-      <c r="U53" s="1"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
-      <c r="Y53" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="Z53" s="1"/>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="1" t="s">
+        <v>552</v>
+      </c>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
-      <c r="AD53" s="1"/>
+      <c r="AC53" s="1"/>
       <c r="AE53" s="1"/>
-      <c r="AF53" t="s">
+      <c r="AF53" s="1"/>
+      <c r="AG53" t="s">
         <v>44</v>
       </c>
-      <c r="AG53" t="s">
+      <c r="AH53" t="s">
         <v>137</v>
       </c>
-      <c r="AH53">
+      <c r="AI53">
         <v>2</v>
-      </c>
-      <c r="AI53" t="s">
-        <v>552</v>
       </c>
       <c r="AJ53" t="s">
         <v>553</v>
       </c>
-      <c r="AM53" t="s">
+      <c r="AK53" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN53" t="s">
         <v>92</v>
       </c>
-      <c r="AN53" t="s">
-        <v>554</v>
-      </c>
-      <c r="AO53" s="1" t="s">
+      <c r="AO53" t="s">
         <v>555</v>
       </c>
       <c r="AP53" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="AQ53" s="1"/>
-      <c r="AR53" s="1" t="s">
+      <c r="AQ53" s="1" t="s">
         <v>557</v>
       </c>
+      <c r="AR53" s="1"/>
       <c r="AS53" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="AT53" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B54" t="s">
         <v>97</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D54" t="s">
         <v>27</v>
@@ -8268,10 +8275,10 @@
         <v>28</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -8286,62 +8293,62 @@
       <c r="T54" t="s">
         <v>118</v>
       </c>
-      <c r="U54" s="1"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
       <c r="X54" s="1"/>
-      <c r="Y54" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="Z54" s="1"/>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="1" t="s">
+        <v>562</v>
+      </c>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
-      <c r="AD54" s="1"/>
+      <c r="AC54" s="1"/>
       <c r="AE54" s="1"/>
-      <c r="AF54" t="s">
+      <c r="AF54" s="1"/>
+      <c r="AG54" t="s">
         <v>44</v>
       </c>
-      <c r="AG54" t="s">
+      <c r="AH54" t="s">
         <v>137</v>
       </c>
-      <c r="AH54">
+      <c r="AI54">
         <v>1</v>
       </c>
-      <c r="AI54" t="s">
-        <v>544</v>
-      </c>
       <c r="AJ54" t="s">
-        <v>525</v>
-      </c>
-      <c r="AM54" t="s">
+        <v>545</v>
+      </c>
+      <c r="AK54" t="s">
+        <v>526</v>
+      </c>
+      <c r="AN54" t="s">
         <v>92</v>
       </c>
-      <c r="AN54" t="s">
-        <v>545</v>
-      </c>
-      <c r="AO54" s="1" t="s">
-        <v>562</v>
+      <c r="AO54" t="s">
+        <v>546</v>
       </c>
       <c r="AP54" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="AQ54" s="1"/>
-      <c r="AR54" s="1" t="s">
-        <v>548</v>
-      </c>
+      <c r="AQ54" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="AR54" s="1"/>
       <c r="AS54" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="AT54" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B55" t="s">
         <v>97</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -8350,10 +8357,10 @@
         <v>28</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -8368,62 +8375,62 @@
       <c r="T55" t="s">
         <v>118</v>
       </c>
-      <c r="U55" s="1"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
-      <c r="Y55" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="Z55" s="1"/>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1" t="s">
+        <v>567</v>
+      </c>
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
-      <c r="AD55" s="1"/>
+      <c r="AC55" s="1"/>
       <c r="AE55" s="1"/>
-      <c r="AF55" t="s">
+      <c r="AF55" s="1"/>
+      <c r="AG55" t="s">
         <v>44</v>
       </c>
-      <c r="AG55" t="s">
+      <c r="AH55" t="s">
         <v>137</v>
       </c>
-      <c r="AH55">
+      <c r="AI55">
         <v>1</v>
       </c>
-      <c r="AI55" t="s">
-        <v>544</v>
-      </c>
       <c r="AJ55" t="s">
-        <v>525</v>
-      </c>
-      <c r="AM55" t="s">
+        <v>545</v>
+      </c>
+      <c r="AK55" t="s">
+        <v>526</v>
+      </c>
+      <c r="AN55" t="s">
         <v>92</v>
       </c>
-      <c r="AN55" t="s">
-        <v>545</v>
-      </c>
-      <c r="AO55" s="1" t="s">
-        <v>567</v>
+      <c r="AO55" t="s">
+        <v>546</v>
       </c>
       <c r="AP55" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="AQ55" s="1"/>
-      <c r="AR55" s="1" t="s">
-        <v>548</v>
-      </c>
+      <c r="AQ55" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="AR55" s="1"/>
       <c r="AS55" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="AT55" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B56" t="s">
         <v>97</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -8432,10 +8439,10 @@
         <v>28</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -8450,62 +8457,62 @@
       <c r="T56" t="s">
         <v>118</v>
       </c>
-      <c r="U56" s="1"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
       <c r="X56" s="1"/>
-      <c r="Y56" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="Z56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1" t="s">
+        <v>572</v>
+      </c>
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
-      <c r="AD56" s="1"/>
+      <c r="AC56" s="1"/>
       <c r="AE56" s="1"/>
-      <c r="AF56" t="s">
+      <c r="AF56" s="1"/>
+      <c r="AG56" t="s">
         <v>44</v>
       </c>
-      <c r="AG56" t="s">
+      <c r="AH56" t="s">
         <v>137</v>
       </c>
-      <c r="AH56">
+      <c r="AI56">
         <v>1</v>
-      </c>
-      <c r="AI56" t="s">
-        <v>552</v>
       </c>
       <c r="AJ56" t="s">
         <v>553</v>
       </c>
-      <c r="AM56" t="s">
+      <c r="AK56" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN56" t="s">
         <v>92</v>
       </c>
-      <c r="AN56" t="s">
-        <v>545</v>
-      </c>
-      <c r="AO56" s="1" t="s">
-        <v>572</v>
+      <c r="AO56" t="s">
+        <v>546</v>
       </c>
       <c r="AP56" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="AQ56" s="1"/>
-      <c r="AR56" s="1" t="s">
-        <v>548</v>
-      </c>
+      <c r="AQ56" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="AR56" s="1"/>
       <c r="AS56" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="AT56" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B57" t="s">
         <v>97</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -8514,10 +8521,10 @@
         <v>28</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -8532,62 +8539,62 @@
       <c r="T57" t="s">
         <v>118</v>
       </c>
-      <c r="U57" s="1"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
-      <c r="Y57" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="Z57" s="1"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1" t="s">
+        <v>572</v>
+      </c>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
-      <c r="AD57" s="1"/>
+      <c r="AC57" s="1"/>
       <c r="AE57" s="1"/>
-      <c r="AF57" t="s">
+      <c r="AF57" s="1"/>
+      <c r="AG57" t="s">
         <v>44</v>
       </c>
-      <c r="AG57" t="s">
+      <c r="AH57" t="s">
         <v>137</v>
       </c>
-      <c r="AH57">
+      <c r="AI57">
         <v>1</v>
-      </c>
-      <c r="AI57" t="s">
-        <v>552</v>
       </c>
       <c r="AJ57" t="s">
         <v>553</v>
       </c>
-      <c r="AM57" t="s">
+      <c r="AK57" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN57" t="s">
         <v>92</v>
       </c>
-      <c r="AN57" t="s">
-        <v>545</v>
-      </c>
-      <c r="AO57" s="1" t="s">
-        <v>576</v>
+      <c r="AO57" t="s">
+        <v>546</v>
       </c>
       <c r="AP57" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="AQ57" s="1"/>
-      <c r="AR57" s="1" t="s">
-        <v>548</v>
-      </c>
+      <c r="AQ57" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="AR57" s="1"/>
       <c r="AS57" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="AT57" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B58" t="s">
         <v>97</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D58" t="s">
         <v>27</v>
@@ -8596,10 +8603,10 @@
         <v>28</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -8614,62 +8621,62 @@
       <c r="T58" t="s">
         <v>118</v>
       </c>
-      <c r="U58" s="1"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
-      <c r="Y58" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="Z58" s="1"/>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1" t="s">
+        <v>582</v>
+      </c>
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
-      <c r="AD58" s="1"/>
+      <c r="AC58" s="1"/>
       <c r="AE58" s="1"/>
-      <c r="AF58" t="s">
+      <c r="AF58" s="1"/>
+      <c r="AG58" t="s">
         <v>44</v>
       </c>
-      <c r="AG58" t="s">
-        <v>582</v>
-      </c>
-      <c r="AH58">
+      <c r="AH58" t="s">
+        <v>583</v>
+      </c>
+      <c r="AI58">
         <v>1</v>
-      </c>
-      <c r="AI58" t="s">
-        <v>583</v>
       </c>
       <c r="AJ58" t="s">
         <v>584</v>
       </c>
-      <c r="AM58" t="s">
+      <c r="AK58" t="s">
+        <v>585</v>
+      </c>
+      <c r="AN58" t="s">
         <v>92</v>
       </c>
-      <c r="AN58" t="s">
-        <v>585</v>
-      </c>
-      <c r="AO58" s="1" t="s">
+      <c r="AO58" t="s">
         <v>586</v>
       </c>
       <c r="AP58" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="AQ58" s="1"/>
-      <c r="AR58" s="1" t="s">
+      <c r="AQ58" s="1" t="s">
         <v>588</v>
       </c>
+      <c r="AR58" s="1"/>
       <c r="AS58" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="AT58" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B59" t="s">
         <v>97</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
@@ -8678,10 +8685,10 @@
         <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -8696,44 +8703,41 @@
       <c r="T59" t="s">
         <v>103</v>
       </c>
-      <c r="U59" s="1"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
-      <c r="Y59" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="Z59" s="1"/>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1" t="s">
+        <v>592</v>
+      </c>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
-      <c r="AD59" s="1"/>
+      <c r="AC59" s="1"/>
       <c r="AE59" s="1"/>
-      <c r="AF59" t="s">
+      <c r="AF59" s="1"/>
+      <c r="AG59" t="s">
         <v>44</v>
       </c>
-      <c r="AG59" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH59">
+      <c r="AH59" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI59">
         <v>1</v>
-      </c>
-      <c r="AI59" t="s">
-        <v>280</v>
       </c>
       <c r="AJ59" t="s">
         <v>281</v>
       </c>
-      <c r="AL59">
+      <c r="AK59" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM59">
         <v>12800</v>
       </c>
-      <c r="AM59" t="s">
+      <c r="AN59" t="s">
         <v>103</v>
       </c>
-      <c r="AN59" t="s">
+      <c r="AO59" t="s">
         <v>50</v>
-      </c>
-      <c r="AO59" s="1" t="s">
-        <v>592</v>
       </c>
       <c r="AP59" s="1" t="s">
         <v>593</v>
@@ -8745,18 +8749,21 @@
         <v>595</v>
       </c>
       <c r="AS59" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="AT59" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B60" t="s">
         <v>97</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -8765,10 +8772,10 @@
         <v>28</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -8783,44 +8790,41 @@
       <c r="T60" t="s">
         <v>103</v>
       </c>
-      <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
-      <c r="Y60" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="Z60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1" t="s">
+        <v>592</v>
+      </c>
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
-      <c r="AD60" s="1"/>
+      <c r="AC60" s="1"/>
       <c r="AE60" s="1"/>
-      <c r="AF60" t="s">
+      <c r="AF60" s="1"/>
+      <c r="AG60" t="s">
         <v>44</v>
       </c>
-      <c r="AG60" t="s">
-        <v>422</v>
-      </c>
-      <c r="AH60">
+      <c r="AH60" t="s">
+        <v>423</v>
+      </c>
+      <c r="AI60">
         <v>1</v>
       </c>
-      <c r="AI60" t="s">
-        <v>597</v>
-      </c>
       <c r="AJ60" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL60">
+        <v>598</v>
+      </c>
+      <c r="AK60" t="s">
+        <v>282</v>
+      </c>
+      <c r="AM60">
         <v>12800</v>
       </c>
-      <c r="AM60" t="s">
+      <c r="AN60" t="s">
         <v>103</v>
       </c>
-      <c r="AN60" t="s">
+      <c r="AO60" t="s">
         <v>50</v>
-      </c>
-      <c r="AO60" s="1" t="s">
-        <v>598</v>
       </c>
       <c r="AP60" s="1" t="s">
         <v>599</v>
@@ -8832,18 +8836,21 @@
         <v>601</v>
       </c>
       <c r="AS60" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="AT60" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B61" t="s">
         <v>97</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
@@ -8852,10 +8859,10 @@
         <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -8870,41 +8877,38 @@
       <c r="T61" t="s">
         <v>103</v>
       </c>
-      <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
-      <c r="Y61" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="Z61" s="1"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1" t="s">
+        <v>592</v>
+      </c>
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
-      <c r="AD61" s="1"/>
+      <c r="AC61" s="1"/>
       <c r="AE61" s="1"/>
-      <c r="AF61" t="s">
+      <c r="AF61" s="1"/>
+      <c r="AG61" t="s">
         <v>44</v>
       </c>
-      <c r="AG61" t="s">
-        <v>316</v>
-      </c>
-      <c r="AH61">
+      <c r="AH61" t="s">
+        <v>317</v>
+      </c>
+      <c r="AI61">
         <v>2</v>
-      </c>
-      <c r="AI61" t="s">
-        <v>317</v>
       </c>
       <c r="AJ61" t="s">
         <v>318</v>
       </c>
-      <c r="AL61">
+      <c r="AK61" t="s">
+        <v>319</v>
+      </c>
+      <c r="AM61">
         <v>51200</v>
       </c>
-      <c r="AM61" t="s">
+      <c r="AN61" t="s">
         <v>103</v>
-      </c>
-      <c r="AO61" s="1" t="s">
-        <v>603</v>
       </c>
       <c r="AP61" s="1" t="s">
         <v>604</v>
@@ -8916,16 +8920,19 @@
         <v>606</v>
       </c>
       <c r="AS61" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="AT61" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS1"/>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Use yes or no." sqref="AC2:AC2000">
+  <autoFilter ref="A1:AT1"/>
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Use yes or no." sqref="AD2:AD2000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Pick a value from the dc_device_type list." sqref="AF2:AF2000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Pick a value from the dc_device_type list." sqref="AG2:AG2000">
       <formula1>_vocab!$T$2:$T$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Pick a value from the family list." sqref="B2:B2000">
@@ -8941,6 +8948,9 @@
       <formula1>_vocab!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Use yes or no." sqref="R2:R2000">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Value not allowed" error="Use yes or no." sqref="U2:U2000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8978,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -8993,10 +9003,10 @@
         <v>241</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>6</v>
@@ -9026,36 +9036,36 @@
         <v>251</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B2" t="s">
         <v>97</v>
@@ -9070,16 +9080,16 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H2">
         <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -9092,20 +9102,20 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
@@ -9120,16 +9130,16 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H3">
         <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -9142,20 +9152,20 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B4" t="s">
         <v>97</v>
@@ -9170,16 +9180,16 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H4">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -9192,20 +9202,20 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B5" t="s">
         <v>97</v>
@@ -9220,10 +9230,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -9236,20 +9246,20 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B6" t="s">
         <v>97</v>
@@ -9264,10 +9274,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -9280,20 +9290,20 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B7" t="s">
         <v>97</v>
@@ -9308,10 +9318,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -9324,20 +9334,20 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B8" t="s">
         <v>97</v>
@@ -9352,10 +9362,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -9368,20 +9378,20 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B9" t="s">
         <v>97</v>
@@ -9396,16 +9406,16 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H9">
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -9418,20 +9428,20 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B10" t="s">
         <v>97</v>
@@ -9446,16 +9456,16 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H10">
         <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -9468,20 +9478,20 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B11" t="s">
         <v>97</v>
@@ -9496,53 +9506,53 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H11">
         <v>36</v>
       </c>
       <c r="I11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K11" t="s">
         <v>54</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="P11" s="1"/>
       <c r="R11" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B12" t="s">
         <v>97</v>
@@ -9557,55 +9567,55 @@
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H12">
         <v>32</v>
       </c>
       <c r="I12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K12" t="s">
         <v>54</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="P12" s="1"/>
       <c r="R12" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B13" t="s">
         <v>97</v>
@@ -9620,16 +9630,16 @@
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H13">
         <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -9642,20 +9652,20 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B14" t="s">
         <v>97</v>
@@ -9670,16 +9680,16 @@
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H14">
         <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -9692,20 +9702,20 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B15" t="s">
         <v>97</v>
@@ -9720,16 +9730,16 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H15">
         <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -9742,20 +9752,20 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B16" t="s">
         <v>97</v>
@@ -9770,16 +9780,16 @@
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H16">
         <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -9792,20 +9802,20 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B17" t="s">
         <v>97</v>
@@ -9820,16 +9830,16 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H17">
         <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -9842,20 +9852,20 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B18" t="s">
         <v>97</v>
@@ -9870,16 +9880,16 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H18">
         <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -9892,20 +9902,20 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B19" t="s">
         <v>97</v>
@@ -9920,16 +9930,16 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H19">
         <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -9942,20 +9952,20 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B20" t="s">
         <v>97</v>
@@ -9970,10 +9980,10 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -9986,20 +9996,20 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B21" t="s">
         <v>97</v>
@@ -10014,10 +10024,10 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -10030,20 +10040,20 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B22" t="s">
         <v>97</v>
@@ -10058,10 +10068,10 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -10074,20 +10084,20 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
@@ -10102,10 +10112,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -10118,20 +10128,20 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
@@ -10146,10 +10156,10 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -10162,20 +10172,20 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B25" t="s">
         <v>97</v>
@@ -10190,10 +10200,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -10206,20 +10216,20 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B26" t="s">
         <v>97</v>
@@ -10234,10 +10244,10 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -10250,20 +10260,20 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
@@ -10278,10 +10288,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -10294,20 +10304,20 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B28" t="s">
         <v>97</v>
@@ -10322,10 +10332,10 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -10338,20 +10348,20 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B29" t="s">
         <v>97</v>
@@ -10366,10 +10376,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -10382,20 +10392,20 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B30" t="s">
         <v>97</v>
@@ -10410,16 +10420,16 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H30">
         <v>8</v>
       </c>
       <c r="I30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -10432,20 +10442,20 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B31" t="s">
         <v>97</v>
@@ -10460,16 +10470,16 @@
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H31">
         <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -10482,20 +10492,20 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B32" t="s">
         <v>97</v>
@@ -10510,16 +10520,16 @@
         <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H32">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -10532,20 +10542,20 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
@@ -10560,16 +10570,16 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H33">
         <v>24</v>
       </c>
       <c r="I33" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -10582,20 +10592,20 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B34" t="s">
         <v>97</v>
@@ -10610,16 +10620,16 @@
         <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H34">
         <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -10632,20 +10642,20 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B35" t="s">
         <v>97</v>
@@ -10660,16 +10670,16 @@
         <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H35">
         <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -10682,20 +10692,20 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
@@ -10710,16 +10720,16 @@
         <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H36">
         <v>48</v>
       </c>
       <c r="I36" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -10732,20 +10742,20 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B37" t="s">
         <v>97</v>
@@ -10760,16 +10770,16 @@
         <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H37">
         <v>48</v>
       </c>
       <c r="I37" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -10782,20 +10792,20 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B38" t="s">
         <v>97</v>
@@ -10810,10 +10820,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -10826,20 +10836,20 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B39" t="s">
         <v>97</v>
@@ -10854,10 +10864,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -10870,20 +10880,20 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
@@ -10898,10 +10908,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -10914,15 +10924,15 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -10963,827 +10973,827 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
   </sheetData>
@@ -11818,10 +11828,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11829,7 +11839,7 @@
         <v>97</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -11845,7 +11855,7 @@
         <v>97</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -11861,7 +11871,7 @@
         <v>97</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -11877,7 +11887,7 @@
         <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
@@ -11893,7 +11903,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -11909,7 +11919,7 @@
         <v>97</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -11925,7 +11935,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
@@ -11941,7 +11951,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -11957,7 +11967,7 @@
         <v>97</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -11973,7 +11983,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -11989,7 +11999,7 @@
         <v>97</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -12005,7 +12015,7 @@
         <v>97</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -12021,7 +12031,7 @@
         <v>97</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
@@ -12037,7 +12047,7 @@
         <v>97</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -12053,7 +12063,7 @@
         <v>97</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
@@ -12069,7 +12079,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -12085,7 +12095,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -12101,7 +12111,7 @@
         <v>97</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
@@ -12117,7 +12127,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
@@ -12133,7 +12143,7 @@
         <v>97</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -12149,7 +12159,7 @@
         <v>97</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>

--- a/data/catalog/datacenter.xlsx
+++ b/data/catalog/datacenter.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="759">
   <si>
     <t>family</t>
   </si>
@@ -146,148 +146,151 @@
     <t>small</t>
   </si>
   <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>fixed</t>
+  </si>
+  <si>
+    <t>leaf</t>
+  </si>
+  <si>
+    <t>nx_os</t>
+  </si>
+  <si>
+    <t>dc_power</t>
+  </si>
+  <si>
+    <t>air_marshal</t>
+  </si>
+  <si>
+    <t>32_way_ecmp</t>
+  </si>
+  <si>
+    <t>108_mb_shared_buffer</t>
+  </si>
+  <si>
+    <t>wireless</t>
+  </si>
+  <si>
+    <t>ready</t>
+  </si>
+  <si>
+    <t>excluded</t>
+  </si>
+  <si>
+    <t>eos_announced</t>
+  </si>
+  <si>
+    <t>cloud</t>
+  </si>
+  <si>
+    <t>line_card</t>
+  </si>
+  <si>
+    <t>fiber</t>
+  </si>
+  <si>
+    <t>6e</t>
+  </si>
+  <si>
+    <t>outdoor</t>
+  </si>
+  <si>
+    <t>internal_directional</t>
+  </si>
+  <si>
+    <t>at</t>
+  </si>
+  <si>
+    <t>desktop</t>
+  </si>
+  <si>
+    <t>distribution</t>
+  </si>
+  <si>
+    <t>poe_plus</t>
+  </si>
+  <si>
+    <t>partial</t>
+  </si>
+  <si>
+    <t>basic_l3</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
     <t>embedded</t>
   </si>
   <si>
-    <t>fixed</t>
-  </si>
-  <si>
-    <t>leaf</t>
-  </si>
-  <si>
-    <t>nx_os</t>
-  </si>
-  <si>
-    <t>dc_power</t>
-  </si>
-  <si>
-    <t>air_marshal</t>
-  </si>
-  <si>
-    <t>32_way_ecmp</t>
-  </si>
-  <si>
-    <t>108_mb_shared_buffer</t>
-  </si>
-  <si>
-    <t>wireless</t>
-  </si>
-  <si>
-    <t>ready</t>
-  </si>
-  <si>
-    <t>excluded</t>
-  </si>
-  <si>
-    <t>eos_announced</t>
-  </si>
-  <si>
-    <t>cloud</t>
-  </si>
-  <si>
-    <t>line_card</t>
-  </si>
-  <si>
-    <t>fiber</t>
-  </si>
-  <si>
-    <t>6e</t>
-  </si>
-  <si>
-    <t>outdoor</t>
-  </si>
-  <si>
-    <t>internal_directional</t>
-  </si>
-  <si>
-    <t>at</t>
-  </si>
-  <si>
-    <t>desktop</t>
-  </si>
-  <si>
-    <t>distribution</t>
-  </si>
-  <si>
-    <t>poe_plus</t>
-  </si>
-  <si>
-    <t>partial</t>
-  </si>
-  <si>
-    <t>basic_l3</t>
-  </si>
-  <si>
-    <t>medium</t>
+    <t>modular_chassis</t>
+  </si>
+  <si>
+    <t>spine</t>
+  </si>
+  <si>
+    <t>aci</t>
+  </si>
+  <si>
+    <t>fan</t>
+  </si>
+  <si>
+    <t>bluetooth_5</t>
+  </si>
+  <si>
+    <t>3_level_h_qos</t>
+  </si>
+  <si>
+    <t>64_mb_buffer</t>
+  </si>
+  <si>
+    <t>routing</t>
+  </si>
+  <si>
+    <t>eos</t>
+  </si>
+  <si>
+    <t>cisco_business</t>
+  </si>
+  <si>
+    <t>supervisor</t>
+  </si>
+  <si>
+    <t>hybrid</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>indoor_outdoor</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>bt</t>
+  </si>
+  <si>
+    <t>rugged</t>
+  </si>
+  <si>
+    <t>core</t>
+  </si>
+  <si>
+    <t>upoe</t>
+  </si>
+  <si>
+    <t>full_l3</t>
+  </si>
+  <si>
+    <t>chassis</t>
+  </si>
+  <si>
+    <t>large</t>
   </si>
   <si>
     <t>pluggable</t>
-  </si>
-  <si>
-    <t>modular_chassis</t>
-  </si>
-  <si>
-    <t>spine</t>
-  </si>
-  <si>
-    <t>aci</t>
-  </si>
-  <si>
-    <t>fan</t>
-  </si>
-  <si>
-    <t>bluetooth_5</t>
-  </si>
-  <si>
-    <t>3_level_h_qos</t>
-  </si>
-  <si>
-    <t>64_mb_buffer</t>
-  </si>
-  <si>
-    <t>routing</t>
-  </si>
-  <si>
-    <t>eos</t>
-  </si>
-  <si>
-    <t>cisco_business</t>
-  </si>
-  <si>
-    <t>supervisor</t>
-  </si>
-  <si>
-    <t>hybrid</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>indoor_outdoor</t>
-  </si>
-  <si>
-    <t>internal</t>
-  </si>
-  <si>
-    <t>bt</t>
-  </si>
-  <si>
-    <t>rugged</t>
-  </si>
-  <si>
-    <t>core</t>
-  </si>
-  <si>
-    <t>upoe</t>
-  </si>
-  <si>
-    <t>full_l3</t>
-  </si>
-  <si>
-    <t>chassis</t>
-  </si>
-  <si>
-    <t>large</t>
   </si>
   <si>
     <t>super_spine</t>
@@ -2968,531 +2971,534 @@
       <c r="R4" t="s">
         <v>90</v>
       </c>
+      <c r="S4" t="s">
+        <v>91</v>
+      </c>
       <c r="U4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="X4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Z4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s">
         <v>89</v>
       </c>
       <c r="N5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q5" t="s">
         <v>85</v>
       </c>
       <c r="R5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U5" t="s">
         <v>38</v>
       </c>
       <c r="V5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="W5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="X5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Z5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="5:26" x14ac:dyDescent="0.25">
       <c r="E6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="V6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="W6" t="s">
         <v>39</v>
       </c>
       <c r="X6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Y6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="5:26" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="W7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="X7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Z7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="5:26" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="U8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W8" t="s">
         <v>85</v>
       </c>
       <c r="X8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Y8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Z8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="6:26" x14ac:dyDescent="0.25">
       <c r="F9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="W9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="X9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Y9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="6:26" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="U10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="W10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="X10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Y10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Z10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="6:26" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="U11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="W11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Y11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="21:26" x14ac:dyDescent="0.25">
       <c r="U12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="W12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="23:26" x14ac:dyDescent="0.25">
       <c r="W13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Y13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Z14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Z15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Z17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Z19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Z21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Z24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Z25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="25:26" x14ac:dyDescent="0.25">
       <c r="Y26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y29" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y30" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y32" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y43" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y44" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y45" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y46" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y47" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y48" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y49" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="50" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y50" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y53" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y54" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y55" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y56" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y57" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y58" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y59" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y60" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y62" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y63" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" spans="25:25" x14ac:dyDescent="0.25">
@@ -3502,122 +3508,122 @@
     </row>
     <row r="65" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y65" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="68" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="69" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="71" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="72" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y72" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="73" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y73" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y74" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y75" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="76" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="77" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y77" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="78" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y78" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y79" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="80" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y80" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y81" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y82" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y83" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y84" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="85" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y85" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y86" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="87" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y87" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="88" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y88" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="89" spans="25:25" x14ac:dyDescent="0.25">
@@ -3627,12 +3633,12 @@
     </row>
     <row r="90" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y90" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91" spans="25:25" x14ac:dyDescent="0.25">
       <c r="Y91" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3675,13 +3681,13 @@
   <sheetData>
     <row r="1" spans="1:46" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -3690,22 +3696,22 @@
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>3</v>
@@ -3714,114 +3720,114 @@
         <v>54</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AJ1" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AK1" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL1" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="AO1" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -3830,10 +3836,10 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -3846,14 +3852,14 @@
       <c r="Q2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
@@ -3864,16 +3870,16 @@
         <v>69</v>
       </c>
       <c r="AH2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AI2">
         <v>16</v>
       </c>
       <c r="AJ2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AK2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL2">
         <v>8</v>
@@ -3885,17 +3891,17 @@
         <v>46</v>
       </c>
       <c r="AO2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AR2" s="1"/>
       <c r="AS2" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AT2" s="1" t="s">
         <v>3</v>
@@ -3903,13 +3909,13 @@
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
@@ -3918,10 +3924,10 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -3934,14 +3940,14 @@
       <c r="Q3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
@@ -3952,16 +3958,16 @@
         <v>69</v>
       </c>
       <c r="AH3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AI3">
         <v>10</v>
       </c>
       <c r="AJ3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AK3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL3">
         <v>4</v>
@@ -3973,17 +3979,17 @@
         <v>46</v>
       </c>
       <c r="AO3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AQ3" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AR3" s="1"/>
       <c r="AS3" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AT3" s="1" t="s">
         <v>3</v>
@@ -3991,13 +3997,13 @@
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D4" t="s">
         <v>27</v>
@@ -4006,10 +4012,10 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -4022,14 +4028,14 @@
       <c r="Q4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
@@ -4046,29 +4052,29 @@
         <v>7</v>
       </c>
       <c r="AJ4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AK4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL4">
         <v>4</v>
       </c>
       <c r="AN4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP4" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AQ4" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AR4" s="1"/>
       <c r="AS4" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AT4" s="1" t="s">
         <v>3</v>
@@ -4076,13 +4082,13 @@
     </row>
     <row r="5" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D5" t="s">
         <v>27</v>
@@ -4091,10 +4097,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -4107,14 +4113,14 @@
       <c r="Q5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
@@ -4131,29 +4137,29 @@
         <v>13</v>
       </c>
       <c r="AJ5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AK5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL5">
         <v>8</v>
       </c>
       <c r="AN5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP5" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ5" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AR5" s="1"/>
       <c r="AS5" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AT5" s="1" t="s">
         <v>3</v>
@@ -4161,13 +4167,13 @@
     </row>
     <row r="6" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
@@ -4176,10 +4182,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -4192,14 +4198,14 @@
       <c r="Q6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
@@ -4216,10 +4222,10 @@
         <v>21</v>
       </c>
       <c r="AJ6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AK6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL6">
         <v>16</v>
@@ -4228,20 +4234,20 @@
         <v>172800</v>
       </c>
       <c r="AN6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP6" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AQ6" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AR6" s="1"/>
       <c r="AS6" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AT6" s="1" t="s">
         <v>3</v>
@@ -4249,13 +4255,13 @@
     </row>
     <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -4264,10 +4270,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -4280,14 +4286,14 @@
       <c r="Q7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
@@ -4298,16 +4304,16 @@
         <v>69</v>
       </c>
       <c r="AH7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AI7">
         <v>4</v>
       </c>
       <c r="AJ7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AK7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AL7">
         <v>8</v>
@@ -4316,20 +4322,20 @@
         <v>25600</v>
       </c>
       <c r="AN7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ7" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AR7" s="1"/>
       <c r="AS7" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AT7" s="1" t="s">
         <v>3</v>
@@ -4337,13 +4343,13 @@
     </row>
     <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
@@ -4352,10 +4358,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -4368,14 +4374,14 @@
       <c r="Q8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
@@ -4386,16 +4392,16 @@
         <v>44</v>
       </c>
       <c r="AH8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI8">
         <v>2</v>
       </c>
       <c r="AJ8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM8">
         <v>51200</v>
@@ -4404,17 +4410,17 @@
         <v>46</v>
       </c>
       <c r="AO8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP8" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AQ8" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AR8" s="1"/>
       <c r="AS8" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AT8" s="1" t="s">
         <v>3</v>
@@ -4422,13 +4428,13 @@
     </row>
     <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
@@ -4437,10 +4443,10 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -4453,14 +4459,14 @@
       <c r="Q9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
@@ -4471,16 +4477,16 @@
         <v>44</v>
       </c>
       <c r="AH9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI9">
         <v>2</v>
       </c>
       <c r="AJ9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM9">
         <v>51200</v>
@@ -4489,17 +4495,17 @@
         <v>46</v>
       </c>
       <c r="AO9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP9" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ9" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR9" s="1"/>
       <c r="AS9" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AT9" s="1" t="s">
         <v>3</v>
@@ -4507,13 +4513,13 @@
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D10" t="s">
         <v>27</v>
@@ -4522,10 +4528,10 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -4538,14 +4544,14 @@
       <c r="Q10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
@@ -4556,16 +4562,16 @@
         <v>44</v>
       </c>
       <c r="AH10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI10">
         <v>2</v>
       </c>
       <c r="AJ10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM10">
         <v>51200</v>
@@ -4574,19 +4580,19 @@
         <v>46</v>
       </c>
       <c r="AO10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP10" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AQ10" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AR10" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AS10" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AT10" s="1" t="s">
         <v>3</v>
@@ -4594,13 +4600,13 @@
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D11" t="s">
         <v>27</v>
@@ -4609,10 +4615,10 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -4625,14 +4631,14 @@
       <c r="Q11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
@@ -4643,16 +4649,16 @@
         <v>44</v>
       </c>
       <c r="AH11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI11">
         <v>2</v>
       </c>
       <c r="AJ11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM11">
         <v>51200</v>
@@ -4661,19 +4667,19 @@
         <v>46</v>
       </c>
       <c r="AO11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP11" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AQ11" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AR11" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AS11" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AT11" s="1" t="s">
         <v>3</v>
@@ -4681,13 +4687,13 @@
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
@@ -4696,10 +4702,10 @@
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -4712,14 +4718,14 @@
       <c r="Q12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
       <c r="Z12" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
@@ -4736,10 +4742,10 @@
         <v>3</v>
       </c>
       <c r="AJ12" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM12">
         <v>102400</v>
@@ -4748,17 +4754,17 @@
         <v>46</v>
       </c>
       <c r="AO12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP12" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ12" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AR12" s="1"/>
       <c r="AS12" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AT12" s="1" t="s">
         <v>3</v>
@@ -4766,13 +4772,13 @@
     </row>
     <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
@@ -4781,10 +4787,10 @@
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -4797,14 +4803,14 @@
       <c r="Q13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
@@ -4821,10 +4827,10 @@
         <v>3</v>
       </c>
       <c r="AJ13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM13">
         <v>102400</v>
@@ -4833,17 +4839,17 @@
         <v>46</v>
       </c>
       <c r="AO13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP13" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AQ13" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AR13" s="1"/>
       <c r="AS13" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AT13" s="1" t="s">
         <v>3</v>
@@ -4851,13 +4857,13 @@
     </row>
     <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D14" t="s">
         <v>27</v>
@@ -4866,10 +4872,10 @@
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -4882,14 +4888,14 @@
       <c r="Q14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
@@ -4900,16 +4906,16 @@
         <v>44</v>
       </c>
       <c r="AH14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI14">
         <v>2</v>
       </c>
       <c r="AJ14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM14">
         <v>51200</v>
@@ -4918,17 +4924,17 @@
         <v>46</v>
       </c>
       <c r="AO14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AP14" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AQ14" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AR14" s="1"/>
       <c r="AS14" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AT14" s="1" t="s">
         <v>3</v>
@@ -4936,13 +4942,13 @@
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
@@ -4951,10 +4957,10 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -4967,14 +4973,14 @@
       <c r="Q15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
@@ -4985,35 +4991,35 @@
         <v>44</v>
       </c>
       <c r="AH15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI15">
         <v>1</v>
       </c>
       <c r="AJ15" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AK15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM15">
         <v>25600</v>
       </c>
       <c r="AN15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO15" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP15" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AQ15" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AR15" s="1"/>
       <c r="AS15" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT15" s="1" t="s">
         <v>3</v>
@@ -5021,13 +5027,13 @@
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
@@ -5036,10 +5042,10 @@
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -5052,14 +5058,14 @@
       <c r="Q16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
@@ -5070,35 +5076,35 @@
         <v>44</v>
       </c>
       <c r="AH16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI16">
         <v>1</v>
       </c>
       <c r="AJ16" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AK16" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM16">
         <v>25600</v>
       </c>
       <c r="AN16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP16" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ16" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AR16" s="1"/>
       <c r="AS16" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT16" s="1" t="s">
         <v>3</v>
@@ -5106,13 +5112,13 @@
     </row>
     <row r="17" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D17" t="s">
         <v>27</v>
@@ -5121,10 +5127,10 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -5137,14 +5143,14 @@
       <c r="Q17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
@@ -5155,35 +5161,35 @@
         <v>44</v>
       </c>
       <c r="AH17" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI17">
         <v>2</v>
       </c>
       <c r="AJ17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AK17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM17">
         <v>38400</v>
       </c>
       <c r="AN17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP17" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AQ17" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AR17" s="1"/>
       <c r="AS17" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT17" s="1" t="s">
         <v>3</v>
@@ -5191,13 +5197,13 @@
     </row>
     <row r="18" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D18" t="s">
         <v>27</v>
@@ -5206,10 +5212,10 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -5222,14 +5228,14 @@
       <c r="Q18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
@@ -5240,35 +5246,35 @@
         <v>44</v>
       </c>
       <c r="AH18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI18">
         <v>2</v>
       </c>
       <c r="AJ18" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AK18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM18">
         <v>51200</v>
       </c>
       <c r="AN18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP18" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AQ18" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AR18" s="1"/>
       <c r="AS18" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT18" s="1" t="s">
         <v>3</v>
@@ -5276,13 +5282,13 @@
     </row>
     <row r="19" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D19" t="s">
         <v>27</v>
@@ -5291,10 +5297,10 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -5307,14 +5313,14 @@
       <c r="Q19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
@@ -5325,35 +5331,35 @@
         <v>44</v>
       </c>
       <c r="AH19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI19">
         <v>1</v>
       </c>
       <c r="AJ19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AK19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM19">
         <v>12800</v>
       </c>
       <c r="AN19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP19" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AQ19" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AR19" s="1"/>
       <c r="AS19" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT19" s="1" t="s">
         <v>3</v>
@@ -5361,13 +5367,13 @@
     </row>
     <row r="20" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
@@ -5376,10 +5382,10 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -5392,14 +5398,14 @@
       <c r="Q20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
@@ -5410,35 +5416,35 @@
         <v>44</v>
       </c>
       <c r="AH20" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI20">
         <v>1</v>
       </c>
       <c r="AJ20" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AK20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM20">
         <v>12000</v>
       </c>
       <c r="AN20" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP20" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AQ20" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AR20" s="1"/>
       <c r="AS20" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT20" s="1" t="s">
         <v>3</v>
@@ -5446,13 +5452,13 @@
     </row>
     <row r="21" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
@@ -5461,10 +5467,10 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -5477,14 +5483,14 @@
       <c r="Q21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
@@ -5495,35 +5501,35 @@
         <v>44</v>
       </c>
       <c r="AH21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI21">
         <v>2</v>
       </c>
       <c r="AJ21" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AK21" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM21">
         <v>12800</v>
       </c>
       <c r="AN21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO21" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP21" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AQ21" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AR21" s="1"/>
       <c r="AS21" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT21" s="1" t="s">
         <v>3</v>
@@ -5531,13 +5537,13 @@
     </row>
     <row r="22" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D22" t="s">
         <v>27</v>
@@ -5546,10 +5552,10 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -5562,14 +5568,14 @@
       <c r="Q22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
@@ -5580,16 +5586,16 @@
         <v>44</v>
       </c>
       <c r="AH22" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI22">
         <v>1</v>
       </c>
       <c r="AJ22" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AK22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM22">
         <v>25600</v>
@@ -5598,17 +5604,17 @@
         <v>46</v>
       </c>
       <c r="AO22" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP22" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AQ22" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AR22" s="1"/>
       <c r="AS22" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AT22" s="1" t="s">
         <v>3</v>
@@ -5616,13 +5622,13 @@
     </row>
     <row r="23" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
@@ -5631,10 +5637,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -5647,14 +5653,14 @@
       <c r="Q23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
@@ -5671,26 +5677,26 @@
         <v>1</v>
       </c>
       <c r="AJ23" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AK23" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN23" t="s">
         <v>46</v>
       </c>
       <c r="AO23" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP23" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ23" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AR23" s="1"/>
       <c r="AS23" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AT23" s="1" t="s">
         <v>3</v>
@@ -5698,13 +5704,13 @@
     </row>
     <row r="24" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
@@ -5713,10 +5719,10 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -5729,14 +5735,14 @@
       <c r="Q24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
@@ -5747,16 +5753,16 @@
         <v>44</v>
       </c>
       <c r="AH24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI24">
         <v>2</v>
       </c>
       <c r="AJ24" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AK24" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM24">
         <v>12800</v>
@@ -5765,17 +5771,17 @@
         <v>46</v>
       </c>
       <c r="AO24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP24" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AQ24" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AR24" s="1"/>
       <c r="AS24" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AT24" s="1" t="s">
         <v>3</v>
@@ -5783,13 +5789,13 @@
     </row>
     <row r="25" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
@@ -5798,10 +5804,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -5814,14 +5820,14 @@
       <c r="Q25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
@@ -5832,16 +5838,16 @@
         <v>44</v>
       </c>
       <c r="AH25" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AI25">
         <v>1</v>
       </c>
       <c r="AJ25" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AK25" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM25">
         <v>7200</v>
@@ -5850,17 +5856,17 @@
         <v>46</v>
       </c>
       <c r="AO25" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP25" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AQ25" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AR25" s="1"/>
       <c r="AS25" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AT25" s="1" t="s">
         <v>3</v>
@@ -5868,13 +5874,13 @@
     </row>
     <row r="26" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D26" t="s">
         <v>27</v>
@@ -5883,10 +5889,10 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -5899,14 +5905,14 @@
       <c r="Q26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
@@ -5923,10 +5929,10 @@
         <v>1</v>
       </c>
       <c r="AJ26" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AK26" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM26">
         <v>5600</v>
@@ -5935,17 +5941,17 @@
         <v>46</v>
       </c>
       <c r="AO26" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP26" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AQ26" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AR26" s="1"/>
       <c r="AS26" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AT26" s="1" t="s">
         <v>3</v>
@@ -5953,13 +5959,13 @@
     </row>
     <row r="27" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D27" t="s">
         <v>27</v>
@@ -5968,10 +5974,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -5984,14 +5990,14 @@
       <c r="Q27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
@@ -6008,10 +6014,10 @@
         <v>2</v>
       </c>
       <c r="AJ27" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AK27" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM27">
         <v>9600</v>
@@ -6020,17 +6026,17 @@
         <v>46</v>
       </c>
       <c r="AO27" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP27" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AQ27" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AR27" s="1"/>
       <c r="AS27" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AT27" s="1" t="s">
         <v>3</v>
@@ -6038,13 +6044,13 @@
     </row>
     <row r="28" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D28" t="s">
         <v>27</v>
@@ -6053,10 +6059,10 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -6069,14 +6075,14 @@
       <c r="Q28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
@@ -6093,10 +6099,10 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AK28" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM28">
         <v>4200</v>
@@ -6105,17 +6111,17 @@
         <v>46</v>
       </c>
       <c r="AO28" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AP28" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AQ28" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AR28" s="1"/>
       <c r="AS28" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AT28" s="1" t="s">
         <v>3</v>
@@ -6123,13 +6129,13 @@
     </row>
     <row r="29" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D29" t="s">
         <v>27</v>
@@ -6138,10 +6144,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -6154,14 +6160,14 @@
       <c r="Q29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
@@ -6172,16 +6178,16 @@
         <v>44</v>
       </c>
       <c r="AH29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AI29">
         <v>1</v>
       </c>
       <c r="AJ29" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AK29" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM29">
         <v>5600</v>
@@ -6190,19 +6196,19 @@
         <v>46</v>
       </c>
       <c r="AO29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AP29" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AQ29" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AR29" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AS29" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AT29" s="1" t="s">
         <v>3</v>
@@ -6210,13 +6216,13 @@
     </row>
     <row r="30" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D30" t="s">
         <v>27</v>
@@ -6225,10 +6231,10 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -6241,14 +6247,14 @@
       <c r="Q30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
@@ -6259,37 +6265,37 @@
         <v>44</v>
       </c>
       <c r="AH30" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AI30">
         <v>1</v>
       </c>
       <c r="AJ30" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AK30" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM30">
         <v>2400</v>
       </c>
       <c r="AN30" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO30" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AP30" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AQ30" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AR30" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AS30" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AT30" s="1" t="s">
         <v>3</v>
@@ -6297,13 +6303,13 @@
     </row>
     <row r="31" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D31" t="s">
         <v>27</v>
@@ -6312,10 +6318,10 @@
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -6328,14 +6334,14 @@
       <c r="Q31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -6346,37 +6352,37 @@
         <v>44</v>
       </c>
       <c r="AH31" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AI31">
         <v>1</v>
       </c>
       <c r="AJ31" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AK31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM31">
         <v>3800</v>
       </c>
       <c r="AN31" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO31" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AP31" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AQ31" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AR31" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AS31" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AT31" s="1" t="s">
         <v>3</v>
@@ -6384,13 +6390,13 @@
     </row>
     <row r="32" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
@@ -6399,10 +6405,10 @@
         <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -6415,14 +6421,14 @@
       <c r="Q32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
@@ -6433,37 +6439,37 @@
         <v>44</v>
       </c>
       <c r="AH32" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AI32">
         <v>1</v>
       </c>
       <c r="AJ32" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AK32" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM32">
         <v>3600</v>
       </c>
       <c r="AN32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO32" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP32" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ32" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR32" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AS32" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT32" s="1" t="s">
         <v>3</v>
@@ -6471,13 +6477,13 @@
     </row>
     <row r="33" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
@@ -6486,10 +6492,10 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -6502,14 +6508,14 @@
       <c r="Q33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -6520,35 +6526,35 @@
         <v>44</v>
       </c>
       <c r="AH33" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AI33">
         <v>1</v>
       </c>
       <c r="AJ33" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AK33" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM33">
         <v>2160</v>
       </c>
       <c r="AN33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO33" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP33" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AQ33" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AR33" s="1"/>
       <c r="AS33" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT33" s="1" t="s">
         <v>3</v>
@@ -6556,13 +6562,13 @@
     </row>
     <row r="34" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -6571,10 +6577,10 @@
         <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -6587,14 +6593,14 @@
       <c r="Q34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
@@ -6605,35 +6611,35 @@
         <v>44</v>
       </c>
       <c r="AH34" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AI34">
         <v>1</v>
       </c>
       <c r="AJ34" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AK34" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM34">
         <v>2160</v>
       </c>
       <c r="AN34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO34" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP34" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AQ34" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AR34" s="1"/>
       <c r="AS34" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AT34" s="1" t="s">
         <v>3</v>
@@ -6641,13 +6647,13 @@
     </row>
     <row r="35" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -6656,10 +6662,10 @@
         <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -6672,14 +6678,14 @@
       <c r="Q35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
@@ -6690,35 +6696,35 @@
         <v>44</v>
       </c>
       <c r="AH35" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AI35">
         <v>1</v>
       </c>
       <c r="AJ35" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AK35" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM35">
         <v>3600</v>
       </c>
       <c r="AN35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP35" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AQ35" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AR35" s="1"/>
       <c r="AS35" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AT35" s="1" t="s">
         <v>3</v>
@@ -6726,13 +6732,13 @@
     </row>
     <row r="36" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D36" t="s">
         <v>27</v>
@@ -6741,10 +6747,10 @@
         <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -6757,14 +6763,14 @@
       <c r="Q36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
@@ -6775,35 +6781,35 @@
         <v>44</v>
       </c>
       <c r="AH36" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AI36">
         <v>1</v>
       </c>
       <c r="AJ36" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AK36" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM36">
         <v>2160</v>
       </c>
       <c r="AN36" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO36" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP36" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AQ36" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AR36" s="1"/>
       <c r="AS36" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT36" s="1" t="s">
         <v>3</v>
@@ -6811,13 +6817,13 @@
     </row>
     <row r="37" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D37" t="s">
         <v>27</v>
@@ -6826,10 +6832,10 @@
         <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -6842,14 +6848,14 @@
       <c r="Q37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
@@ -6866,10 +6872,10 @@
         <v>1</v>
       </c>
       <c r="AJ37" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AK37" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM37">
         <v>696</v>
@@ -6878,17 +6884,17 @@
         <v>46</v>
       </c>
       <c r="AO37" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP37" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AQ37" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AR37" s="1"/>
       <c r="AS37" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT37" s="1" t="s">
         <v>3</v>
@@ -6896,13 +6902,13 @@
     </row>
     <row r="38" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D38" t="s">
         <v>27</v>
@@ -6911,10 +6917,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -6927,14 +6933,14 @@
       <c r="Q38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
@@ -6951,10 +6957,10 @@
         <v>1</v>
       </c>
       <c r="AJ38" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AK38" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM38">
         <v>696</v>
@@ -6963,17 +6969,17 @@
         <v>46</v>
       </c>
       <c r="AO38" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP38" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AQ38" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AR38" s="1"/>
       <c r="AS38" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AT38" s="1" t="s">
         <v>3</v>
@@ -6981,13 +6987,13 @@
     </row>
     <row r="39" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D39" t="s">
         <v>27</v>
@@ -6996,10 +7002,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -7012,14 +7018,14 @@
       <c r="Q39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
@@ -7030,35 +7036,35 @@
         <v>44</v>
       </c>
       <c r="AH39" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AI39">
         <v>1</v>
       </c>
       <c r="AJ39" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AK39" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM39">
         <v>7200</v>
       </c>
       <c r="AN39" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO39" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP39" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AQ39" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AR39" s="1"/>
       <c r="AS39" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT39" s="1" t="s">
         <v>3</v>
@@ -7066,13 +7072,13 @@
     </row>
     <row r="40" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D40" t="s">
         <v>27</v>
@@ -7081,10 +7087,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -7097,14 +7103,14 @@
       <c r="Q40" s="1"/>
       <c r="S40" s="1"/>
       <c r="T40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
@@ -7115,35 +7121,35 @@
         <v>44</v>
       </c>
       <c r="AH40" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AI40">
         <v>1</v>
       </c>
       <c r="AJ40" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AK40" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM40">
         <v>7200</v>
       </c>
       <c r="AN40" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO40" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP40" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AQ40" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AR40" s="1"/>
       <c r="AS40" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT40" s="1" t="s">
         <v>3</v>
@@ -7151,13 +7157,13 @@
     </row>
     <row r="41" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D41" t="s">
         <v>27</v>
@@ -7166,10 +7172,10 @@
         <v>28</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -7182,14 +7188,14 @@
       <c r="Q41" s="1"/>
       <c r="S41" s="1"/>
       <c r="T41" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
@@ -7206,29 +7212,29 @@
         <v>2</v>
       </c>
       <c r="AJ41" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AK41" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM41">
         <v>7200</v>
       </c>
       <c r="AN41" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO41" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP41" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AQ41" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AR41" s="1"/>
       <c r="AS41" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT41" s="1" t="s">
         <v>3</v>
@@ -7236,13 +7242,13 @@
     </row>
     <row r="42" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D42" t="s">
         <v>27</v>
@@ -7251,10 +7257,10 @@
         <v>28</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -7267,14 +7273,14 @@
       <c r="Q42" s="1"/>
       <c r="S42" s="1"/>
       <c r="T42" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
@@ -7291,29 +7297,29 @@
         <v>1.2</v>
       </c>
       <c r="AJ42" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AK42" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM42">
         <v>4800</v>
       </c>
       <c r="AN42" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO42" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP42" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ42" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AR42" s="1"/>
       <c r="AS42" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AT42" s="1" t="s">
         <v>3</v>
@@ -7321,13 +7327,13 @@
     </row>
     <row r="43" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D43" t="s">
         <v>27</v>
@@ -7336,10 +7342,10 @@
         <v>28</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -7352,14 +7358,14 @@
       <c r="Q43" s="1"/>
       <c r="S43" s="1"/>
       <c r="T43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
       <c r="Z43" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
@@ -7376,29 +7382,29 @@
         <v>2</v>
       </c>
       <c r="AJ43" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AK43" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM43">
         <v>4320</v>
       </c>
       <c r="AN43" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO43" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP43" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AQ43" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AR43" s="1"/>
       <c r="AS43" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AT43" s="1" t="s">
         <v>3</v>
@@ -7406,13 +7412,13 @@
     </row>
     <row r="44" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D44" t="s">
         <v>27</v>
@@ -7421,10 +7427,10 @@
         <v>28</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -7437,14 +7443,14 @@
       <c r="Q44" s="1"/>
       <c r="S44" s="1"/>
       <c r="T44" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
@@ -7461,10 +7467,10 @@
         <v>1</v>
       </c>
       <c r="AJ44" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AK44" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM44">
         <v>696</v>
@@ -7473,17 +7479,17 @@
         <v>46</v>
       </c>
       <c r="AO44" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AP44" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AQ44" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AR44" s="1"/>
       <c r="AS44" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AT44" s="1" t="s">
         <v>3</v>
@@ -7491,13 +7497,13 @@
     </row>
     <row r="45" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D45" t="s">
         <v>27</v>
@@ -7506,10 +7512,10 @@
         <v>28</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -7520,27 +7526,27 @@
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q45" s="1"/>
       <c r="S45" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="T45" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
@@ -7557,41 +7563,41 @@
         <v>2</v>
       </c>
       <c r="AJ45" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AK45" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM45">
         <v>12800</v>
       </c>
       <c r="AN45" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO45" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AP45" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AQ45" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AR45" s="1"/>
       <c r="AS45" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AT45" s="1"/>
     </row>
     <row r="46" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D46" t="s">
         <v>27</v>
@@ -7600,10 +7606,10 @@
         <v>28</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -7616,14 +7622,14 @@
       <c r="Q46" s="1"/>
       <c r="S46" s="1"/>
       <c r="T46" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
@@ -7634,16 +7640,16 @@
         <v>44</v>
       </c>
       <c r="AH46" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AI46">
         <v>1</v>
       </c>
       <c r="AJ46" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AK46" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AM46">
         <v>3600</v>
@@ -7652,17 +7658,17 @@
         <v>46</v>
       </c>
       <c r="AO46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AP46" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ46" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AR46" s="1"/>
       <c r="AS46" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AT46" s="1" t="s">
         <v>3</v>
@@ -7670,13 +7676,13 @@
     </row>
     <row r="47" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D47" t="s">
         <v>27</v>
@@ -7685,10 +7691,10 @@
         <v>28</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -7704,14 +7710,14 @@
       <c r="Q47" s="1"/>
       <c r="S47" s="1"/>
       <c r="T47" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
@@ -7728,10 +7734,10 @@
         <v>1</v>
       </c>
       <c r="AJ47" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AK47" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM47">
         <v>960</v>
@@ -7740,10 +7746,10 @@
         <v>46</v>
       </c>
       <c r="AP47" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AQ47" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AR47" s="1"/>
       <c r="AS47" s="1"/>
@@ -7751,13 +7757,13 @@
     </row>
     <row r="48" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D48" t="s">
         <v>27</v>
@@ -7766,10 +7772,10 @@
         <v>28</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -7785,14 +7791,14 @@
       <c r="Q48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
@@ -7809,10 +7815,10 @@
         <v>1</v>
       </c>
       <c r="AJ48" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AK48" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM48">
         <v>480</v>
@@ -7821,10 +7827,10 @@
         <v>46</v>
       </c>
       <c r="AP48" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AQ48" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AR48" s="1"/>
       <c r="AS48" s="1"/>
@@ -7832,13 +7838,13 @@
     </row>
     <row r="49" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D49" t="s">
         <v>27</v>
@@ -7847,10 +7853,10 @@
         <v>28</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -7863,14 +7869,14 @@
       <c r="Q49" s="1"/>
       <c r="S49" s="1"/>
       <c r="T49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
@@ -7881,16 +7887,16 @@
         <v>69</v>
       </c>
       <c r="AH49" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AI49">
         <v>9</v>
       </c>
       <c r="AJ49" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AK49" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AL49">
         <v>4</v>
@@ -7899,20 +7905,20 @@
         <v>12000</v>
       </c>
       <c r="AN49" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO49" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP49" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AQ49" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AR49" s="1"/>
       <c r="AS49" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AT49" s="1" t="s">
         <v>3</v>
@@ -7920,13 +7926,13 @@
     </row>
     <row r="50" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D50" t="s">
         <v>27</v>
@@ -7935,10 +7941,10 @@
         <v>28</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -7951,14 +7957,14 @@
       <c r="Q50" s="1"/>
       <c r="S50" s="1"/>
       <c r="T50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
@@ -7969,16 +7975,16 @@
         <v>69</v>
       </c>
       <c r="AH50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AI50">
         <v>14</v>
       </c>
       <c r="AJ50" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AK50" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AL50">
         <v>8</v>
@@ -7987,20 +7993,20 @@
         <v>24000</v>
       </c>
       <c r="AN50" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO50" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP50" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AQ50" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AR50" s="1"/>
       <c r="AS50" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AT50" s="1" t="s">
         <v>3</v>
@@ -8008,13 +8014,13 @@
     </row>
     <row r="51" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D51" t="s">
         <v>27</v>
@@ -8023,10 +8029,10 @@
         <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -8039,14 +8045,14 @@
       <c r="Q51" s="1"/>
       <c r="S51" s="1"/>
       <c r="T51" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
@@ -8057,16 +8063,16 @@
         <v>69</v>
       </c>
       <c r="AH51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AI51">
         <v>26</v>
       </c>
       <c r="AJ51" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AK51" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AL51">
         <v>16</v>
@@ -8075,20 +8081,20 @@
         <v>48000</v>
       </c>
       <c r="AN51" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO51" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP51" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AQ51" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AR51" s="1"/>
       <c r="AS51" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AT51" s="1" t="s">
         <v>3</v>
@@ -8096,13 +8102,13 @@
     </row>
     <row r="52" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D52" t="s">
         <v>27</v>
@@ -8111,10 +8117,10 @@
         <v>28</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -8127,14 +8133,14 @@
       <c r="Q52" s="1"/>
       <c r="S52" s="1"/>
       <c r="T52" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
@@ -8145,32 +8151,32 @@
         <v>44</v>
       </c>
       <c r="AH52" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AI52">
         <v>2</v>
       </c>
       <c r="AJ52" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AK52" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN52" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO52" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AP52" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AQ52" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AR52" s="1"/>
       <c r="AS52" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AT52" s="1" t="s">
         <v>3</v>
@@ -8178,13 +8184,13 @@
     </row>
     <row r="53" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D53" t="s">
         <v>27</v>
@@ -8193,10 +8199,10 @@
         <v>28</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -8209,14 +8215,14 @@
       <c r="Q53" s="1"/>
       <c r="S53" s="1"/>
       <c r="T53" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
@@ -8227,32 +8233,32 @@
         <v>44</v>
       </c>
       <c r="AH53" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AI53">
         <v>2</v>
       </c>
       <c r="AJ53" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AK53" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN53" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO53" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AP53" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AQ53" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AR53" s="1"/>
       <c r="AS53" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AT53" s="1" t="s">
         <v>3</v>
@@ -8260,13 +8266,13 @@
     </row>
     <row r="54" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D54" t="s">
         <v>27</v>
@@ -8275,10 +8281,10 @@
         <v>28</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -8291,14 +8297,14 @@
       <c r="Q54" s="1"/>
       <c r="S54" s="1"/>
       <c r="T54" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
@@ -8309,32 +8315,32 @@
         <v>44</v>
       </c>
       <c r="AH54" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AI54">
         <v>1</v>
       </c>
       <c r="AJ54" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AK54" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO54" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AP54" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AQ54" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AR54" s="1"/>
       <c r="AS54" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AT54" s="1" t="s">
         <v>3</v>
@@ -8342,13 +8348,13 @@
     </row>
     <row r="55" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B55" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D55" t="s">
         <v>27</v>
@@ -8357,10 +8363,10 @@
         <v>28</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -8373,14 +8379,14 @@
       <c r="Q55" s="1"/>
       <c r="S55" s="1"/>
       <c r="T55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
@@ -8391,32 +8397,32 @@
         <v>44</v>
       </c>
       <c r="AH55" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AI55">
         <v>1</v>
       </c>
       <c r="AJ55" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AK55" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN55" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO55" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AP55" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AQ55" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AR55" s="1"/>
       <c r="AS55" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AT55" s="1" t="s">
         <v>3</v>
@@ -8424,13 +8430,13 @@
     </row>
     <row r="56" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B56" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D56" t="s">
         <v>27</v>
@@ -8439,10 +8445,10 @@
         <v>28</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -8455,14 +8461,14 @@
       <c r="Q56" s="1"/>
       <c r="S56" s="1"/>
       <c r="T56" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
@@ -8473,32 +8479,32 @@
         <v>44</v>
       </c>
       <c r="AH56" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AI56">
         <v>1</v>
       </c>
       <c r="AJ56" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AK56" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN56" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO56" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AP56" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AQ56" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AR56" s="1"/>
       <c r="AS56" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AT56" s="1" t="s">
         <v>3</v>
@@ -8506,13 +8512,13 @@
     </row>
     <row r="57" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B57" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D57" t="s">
         <v>27</v>
@@ -8521,10 +8527,10 @@
         <v>28</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -8537,14 +8543,14 @@
       <c r="Q57" s="1"/>
       <c r="S57" s="1"/>
       <c r="T57" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
@@ -8555,32 +8561,32 @@
         <v>44</v>
       </c>
       <c r="AH57" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AI57">
         <v>1</v>
       </c>
       <c r="AJ57" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AK57" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN57" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO57" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AP57" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AQ57" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AR57" s="1"/>
       <c r="AS57" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AT57" s="1" t="s">
         <v>3</v>
@@ -8588,13 +8594,13 @@
     </row>
     <row r="58" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B58" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D58" t="s">
         <v>27</v>
@@ -8603,10 +8609,10 @@
         <v>28</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -8619,14 +8625,14 @@
       <c r="Q58" s="1"/>
       <c r="S58" s="1"/>
       <c r="T58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
@@ -8637,32 +8643,32 @@
         <v>44</v>
       </c>
       <c r="AH58" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI58">
         <v>1</v>
       </c>
       <c r="AJ58" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AK58" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN58" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO58" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AP58" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AQ58" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AR58" s="1"/>
       <c r="AS58" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AT58" s="1" t="s">
         <v>3</v>
@@ -8670,13 +8676,13 @@
     </row>
     <row r="59" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B59" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D59" t="s">
         <v>27</v>
@@ -8685,10 +8691,10 @@
         <v>28</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -8701,14 +8707,14 @@
       <c r="Q59" s="1"/>
       <c r="S59" s="1"/>
       <c r="T59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
@@ -8719,37 +8725,37 @@
         <v>44</v>
       </c>
       <c r="AH59" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI59">
         <v>1</v>
       </c>
       <c r="AJ59" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AK59" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM59">
         <v>12800</v>
       </c>
       <c r="AN59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO59" t="s">
         <v>50</v>
       </c>
       <c r="AP59" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AQ59" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AR59" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AS59" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AT59" s="1" t="s">
         <v>3</v>
@@ -8757,13 +8763,13 @@
     </row>
     <row r="60" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B60" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D60" t="s">
         <v>27</v>
@@ -8772,10 +8778,10 @@
         <v>28</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -8788,14 +8794,14 @@
       <c r="Q60" s="1"/>
       <c r="S60" s="1"/>
       <c r="T60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
@@ -8806,37 +8812,37 @@
         <v>44</v>
       </c>
       <c r="AH60" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AI60">
         <v>1</v>
       </c>
       <c r="AJ60" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AK60" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AM60">
         <v>12800</v>
       </c>
       <c r="AN60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO60" t="s">
         <v>50</v>
       </c>
       <c r="AP60" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AQ60" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AR60" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AS60" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AT60" s="1" t="s">
         <v>3</v>
@@ -8844,13 +8850,13 @@
     </row>
     <row r="61" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B61" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D61" t="s">
         <v>27</v>
@@ -8859,10 +8865,10 @@
         <v>28</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -8875,14 +8881,14 @@
       <c r="Q61" s="1"/>
       <c r="S61" s="1"/>
       <c r="T61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
@@ -8893,34 +8899,34 @@
         <v>44</v>
       </c>
       <c r="AH61" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AI61">
         <v>2</v>
       </c>
       <c r="AJ61" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AK61" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM61">
         <v>51200</v>
       </c>
       <c r="AN61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AP61" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AQ61" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AR61" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AS61" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AT61" s="1" t="s">
         <v>3</v>
@@ -8982,13 +8988,13 @@
   <sheetData>
     <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -8997,16 +9003,16 @@
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>6</v>
@@ -9018,57 +9024,57 @@
         <v>54</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
         <v>56</v>
@@ -9080,16 +9086,16 @@
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H2">
         <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -9102,23 +9108,23 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
         <v>56</v>
@@ -9130,16 +9136,16 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H3">
         <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -9152,23 +9158,23 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
         <v>56</v>
@@ -9180,16 +9186,16 @@
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H4">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -9202,23 +9208,23 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
         <v>79</v>
@@ -9230,10 +9236,10 @@
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -9246,23 +9252,23 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
         <v>79</v>
@@ -9274,10 +9280,10 @@
         <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -9290,26 +9296,26 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
       <c r="AA6" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -9318,10 +9324,10 @@
         <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -9334,26 +9340,26 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
       <c r="AA7" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
@@ -9362,10 +9368,10 @@
         <v>28</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -9378,23 +9384,23 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
       <c r="AA8" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
         <v>56</v>
@@ -9406,16 +9412,16 @@
         <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H9">
         <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -9428,23 +9434,23 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
       <c r="AA9" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
         <v>56</v>
@@ -9456,16 +9462,16 @@
         <v>28</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H10">
         <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -9478,23 +9484,23 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
       <c r="AA10" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
         <v>56</v>
@@ -9506,56 +9512,56 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H11">
         <v>36</v>
       </c>
       <c r="I11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K11" t="s">
         <v>54</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P11" s="1"/>
       <c r="R11" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
       <c r="AA11" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
         <v>56</v>
@@ -9567,58 +9573,58 @@
         <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H12">
         <v>32</v>
       </c>
       <c r="I12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K12" t="s">
         <v>54</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P12" s="1"/>
       <c r="R12" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="Z12" s="1"/>
       <c r="AA12" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
         <v>56</v>
@@ -9630,16 +9636,16 @@
         <v>28</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H13">
         <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -9652,23 +9658,23 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
       <c r="AA13" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
         <v>56</v>
@@ -9680,16 +9686,16 @@
         <v>28</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H14">
         <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -9702,23 +9708,23 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
       <c r="AA14" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
         <v>56</v>
@@ -9730,16 +9736,16 @@
         <v>28</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H15">
         <v>24</v>
       </c>
       <c r="I15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -9752,23 +9758,23 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
       <c r="AA15" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
         <v>56</v>
@@ -9780,16 +9786,16 @@
         <v>28</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H16">
         <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -9802,23 +9808,23 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
       <c r="AA16" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
         <v>56</v>
@@ -9830,16 +9836,16 @@
         <v>28</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H17">
         <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -9852,23 +9858,23 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
       <c r="AA17" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
         <v>56</v>
@@ -9880,16 +9886,16 @@
         <v>28</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H18">
         <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -9902,23 +9908,23 @@
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
       <c r="AA18" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
         <v>56</v>
@@ -9930,16 +9936,16 @@
         <v>28</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H19">
         <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -9952,26 +9958,26 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
       <c r="AA19" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
         <v>27</v>
@@ -9980,10 +9986,10 @@
         <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -9996,26 +10002,26 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
       <c r="AA20" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
@@ -10024,10 +10030,10 @@
         <v>28</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -10040,26 +10046,26 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>27</v>
@@ -10068,10 +10074,10 @@
         <v>28</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -10084,26 +10090,26 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
       <c r="AA22" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
         <v>27</v>
@@ -10112,10 +10118,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -10128,26 +10134,26 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
       <c r="AA23" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
         <v>27</v>
@@ -10156,10 +10162,10 @@
         <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -10172,26 +10178,26 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
       <c r="AA24" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
@@ -10200,10 +10206,10 @@
         <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -10216,26 +10222,26 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
       <c r="AA25" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
         <v>27</v>
@@ -10244,10 +10250,10 @@
         <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -10260,26 +10266,26 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
         <v>27</v>
@@ -10288,10 +10294,10 @@
         <v>28</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -10304,23 +10310,23 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
         <v>79</v>
@@ -10332,10 +10338,10 @@
         <v>28</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -10348,23 +10354,23 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
         <v>79</v>
@@ -10376,10 +10382,10 @@
         <v>28</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -10392,26 +10398,26 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D30" t="s">
         <v>27</v>
@@ -10420,16 +10426,16 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H30">
         <v>8</v>
       </c>
       <c r="I30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -10442,26 +10448,26 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s">
         <v>27</v>
@@ -10470,16 +10476,16 @@
         <v>28</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H31">
         <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -10492,26 +10498,26 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
@@ -10520,16 +10526,16 @@
         <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H32">
         <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -10542,26 +10548,26 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
@@ -10570,16 +10576,16 @@
         <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H33">
         <v>24</v>
       </c>
       <c r="I33" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -10592,26 +10598,26 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
@@ -10620,16 +10626,16 @@
         <v>28</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H34">
         <v>48</v>
       </c>
       <c r="I34" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -10642,26 +10648,26 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D35" t="s">
         <v>27</v>
@@ -10670,16 +10676,16 @@
         <v>28</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H35">
         <v>48</v>
       </c>
       <c r="I35" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -10692,26 +10698,26 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D36" t="s">
         <v>27</v>
@@ -10720,16 +10726,16 @@
         <v>28</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H36">
         <v>48</v>
       </c>
       <c r="I36" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -10742,26 +10748,26 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D37" t="s">
         <v>27</v>
@@ -10770,16 +10776,16 @@
         <v>28</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H37">
         <v>48</v>
       </c>
       <c r="I37" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -10792,26 +10798,26 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D38" t="s">
         <v>27</v>
@@ -10820,10 +10826,10 @@
         <v>28</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -10836,26 +10842,26 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
         <v>27</v>
@@ -10864,10 +10870,10 @@
         <v>28</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -10880,26 +10886,26 @@
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D40" t="s">
         <v>27</v>
@@ -10908,10 +10914,10 @@
         <v>28</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -10924,15 +10930,15 @@
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -10973,827 +10979,827 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
   </sheetData>
@@ -11819,7 +11825,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -11828,18 +11834,18 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
@@ -11852,10 +11858,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -11868,10 +11874,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -11884,10 +11890,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
@@ -11900,10 +11906,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -11916,10 +11922,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -11932,10 +11938,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
@@ -11948,10 +11954,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
@@ -11964,10 +11970,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -11980,10 +11986,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -11996,10 +12002,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -12012,10 +12018,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -12028,10 +12034,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
@@ -12044,10 +12050,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -12060,10 +12066,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
@@ -12076,10 +12082,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -12092,10 +12098,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -12108,10 +12114,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
@@ -12124,10 +12130,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
@@ -12140,10 +12146,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -12156,10 +12162,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
